--- a/02_TRAVAIL/Lot1_Hostaway/MASTER_FACT_HA_ReservationDetails.xlsx
+++ b/02_TRAVAIL/Lot1_Hostaway/MASTER_FACT_HA_ReservationDetails.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D87"/>
+  <dimension ref="A1:D114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,1719 +452,2259 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>60539937</v>
+        <v>63603419</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{"id": 60539937, "listingMapId": 493047, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6567109043", "hostawayReservationId": "60539937", "channelReservationId": "6567109043", "externalPropertyId": "15480052", "externalUnitId": "1548005201", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "FZ6CvPYV", "guestPortalUrl": "https://guest-portal.hostaway.com/60539937/FZ6CvPYV", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-06-06 08:44:27", "pendingExpireDate": null, "guestName": "Aldo SINAWE", "guestFirstName": "Aldo", "guestLastName": "SINAWE", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": "", "guestCountry": "FR", "guestEmail": "asinaw.444897@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 1, "adults": 1, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-06-06", "departureDate": "2026-06-08", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 2, "phone": "+33754720522", "totalPrice": 99.77, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 16.34, "hostawayCommissionAmount": null, "cleaningFee": 40, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nBOOKING NOTE : Payment charge is EUR 1.3454", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 86084809, "accountId": 181258, "listingMapId": 493047, "reservationId": 60539937, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 40, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-06-06 08:45:52", "updatedOn": "2026-06-06 08:45:52"}, {"id": 86084810, "accountId": 181258, "listingMapId": 493047, "reservationId": 60539937, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 5.1, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-06-06 08:45:52", "updatedOn": "2026-06-06 08:45:52"}, {"id": 86084811, "accountId": 181258, "listingMapId": 493047, "reservationId": 60539937, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 3.67, "currency": "EUR", "percentage": 7.2, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-06-06 08:45:52", "updatedOn": "2026-06-06 08:45:52"}, {"id": 86084812, "accoun</t>
+          <t>{"id": 63603419, "listingMapId": 480140, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6040938679", "hostawayReservationId": "63603419", "channelReservationId": "6040938679", "externalPropertyId": "15500360", "externalUnitId": "1550036001", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "obXUnwg8", "guestPortalUrl": "https://guest-portal.hostaway.com/63603419/obXUnwg8", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-07-28 11:34:16", "pendingExpireDate": null, "guestName": "Dawid Styszynski", "guestFirstName": "Dawid", "guestLastName": "Styszynski", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": "", "guestCountry": "PL", "guestEmail": "dstysz.662416@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 3, "adults": 2, "children": 1, "infants": null, "pets": null, "arrivalDate": "2026-08-17", "departureDate": "2026-08-19", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 2, "phone": null, "totalPrice": 225.32, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 37.09, "hostawayCommissionAmount": null, "cleaningFee": 55, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nBOOKING NOTE : Payment charge is EUR 3.0548\nApproximate time of arrival: between 21:00 and 22:00\nWe will be arriving by car, so we will need a parking space.", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "There is no meal option with this room.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": "37", "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": {"name": null, "channelId": 2005, "channelSpecificCode": "37", "longTerm": false, "cancellationPolicyItem": [{"refundAmount": 100, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": -612000, "event": "arrival"}, {"refundAmount": 50, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": 0, "event": "arrival"}]}, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 91016203, "accountId": 181258, "listingMapId": 480140, "reservationId": 63603419, "name": "Cleaning fee", "feeType": "guest", "externalReservationUnitId": null, "amount": 55, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-07-28 11:37:20", "updatedOn": "2026-07-28 11:37:20"}, {"id": 91016204, "accountId": 181258, "listingMapId": 480140, "reservationId": 63603419, "name": "VAT", "feeType": "guest", "externalReservationUnitId": null, "amount": 14.84, "curre</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-06-08T11:42:59+00:00</t>
+          <t>2026-08-17T05:24:52+00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>828148afb8e19205</t>
+          <t>837c5c194cba4993</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>60438998</v>
+        <v>63998963</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{"id": 60438998, "listingMapId": 493047, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5024614275", "hostawayReservationId": "60438998", "channelReservationId": "5024614275", "externalPropertyId": "15480052", "externalUnitId": "1548005201", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "TJPf3N4D", "guestPortalUrl": "https://guest-portal.hostaway.com/60438998/TJPf3N4D", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-06-04 09:48:50", "pendingExpireDate": null, "guestName": "Emmanuel Benard", "guestFirstName": "Emmanuel", "guestLastName": "Benard", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "FR", "guestEmail": "ebenar.495719@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 1, "adults": 1, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-06-08", "departureDate": "2026-06-11", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 3, "phone": "+33688761250", "totalPrice": 146.87, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 23.85, "hostawayCommissionAmount": null, "cleaningFee": 40, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\n\nBOOKING NOTE : Payment charge is EUR 1.9642", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 85918298, "accountId": 181258, "listingMapId": 493047, "reservationId": 60438998, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 40, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-06-04 09:52:40", "updatedOn": "2026-06-04 09:52:40"}, {"id": 85918299, "accountId": 181258, "listingMapId": 493047, "reservationId": 60438998, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 9.12, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-06-04 09:52:40", "updatedOn": "2026-06-04 09:52:40"}, {"id": 85918300, "accountId": 181258, "listingMapId": 493047, "reservationId": 60438998, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 6.57, "currency": "EUR", "percentage": 7.21, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-06-04 09:52:40", "updatedOn": "2026-06-04 09:52:40"}, {"id": 859</t>
+          <t>{"id": 63998963, "listingMapId": 480137, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6622877727", "hostawayReservationId": "63998963", "channelReservationId": "6622877727", "externalPropertyId": "15950709", "externalUnitId": "1595070901", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "F5_RXxnq", "guestPortalUrl": "https://guest-portal.hostaway.com/63998963/F5_RXxnq", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-08-02 18:34:39", "pendingExpireDate": null, "guestName": "Matteo Tilocca", "guestFirstName": "Matteo", "guestLastName": "Tilocca", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": "", "guestCountry": "IT", "guestEmail": "mtiloc.361049@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 5, "adults": 5, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-08-17", "departureDate": "2026-08-21", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 4, "phone": "+393313837760", "totalPrice": 369.06, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 59.59, "hostawayCommissionAmount": null, "cleaningFee": 67, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nReservation has a cancellation grace period. Do not charge if cancelled before 2026-08-03 20:34:39\nBOOKING NOTE : Payment charge is EUR 5.16684\nApproximate time of arrival: between 20:00 and 21:00", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": "1", "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": {"name": null, "channelId": 2005, "channelSpecificCode": "1", "longTerm": false, "cancellationPolicyItem": [{"refundAmount": 100, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": -1142721, "event": "arrival"}, {"refundAmount": 0, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": 0, "event": "arrival"}]}, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 91508248, "accountId": 181258, "listingMapId": 480137, "reservationId": 63998963, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 67, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-08-02 18:36:06", "updatedOn": "2026-08-02 18:36:06"}, {"id": 91508249, "accountId": 181258, "listingMapId": 480137, "reservationId": 63998963, "name": "TVA", "feeType"</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-06-08T11:43:00+00:00</t>
+          <t>2026-08-17T05:24:53+00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>249fa21942c28ccd</t>
+          <t>b44be04ce9067eba</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>60550389</v>
+        <v>63081294</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{"id": 60550389, "listingMapId": 493047, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5566472242", "hostawayReservationId": "60550389", "channelReservationId": "5566472242", "externalPropertyId": "15480052", "externalUnitId": "1548005201", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "dY8FibiL", "guestPortalUrl": "https://guest-portal.hostaway.com/60550389/dY8FibiL", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-06-06 15:12:58", "pendingExpireDate": null, "guestName": "Hugues Eric LEDOT", "guestFirstName": "Hugues", "guestLastName": "Eric LEDOT", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "FR", "guestEmail": "hledot.933397@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 2, "adults": 2, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-06-11", "departureDate": "2026-06-13", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 2, "phone": "+33651754934", "totalPrice": 110.64, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 18.07, "hostawayCommissionAmount": null, "cleaningFee": 40, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nBOOKING NOTE : Payment charge is EUR 1.4882", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 86109993, "accountId": 181258, "listingMapId": 493047, "reservationId": 60550389, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 40, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-06-06 15:14:29", "updatedOn": "2026-06-06 15:14:29"}, {"id": 86109994, "accountId": 181258, "listingMapId": 493047, "reservationId": 60550389, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 6.03, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-06-06 15:14:29", "updatedOn": "2026-06-06 15:14:29"}, {"id": 86109995, "accountId": 181258, "listingMapId": 493047, "reservationId": 60550389, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 4.34, "currency": "EUR", "percentage": 7.2, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-06-06 15:14:29", "updatedOn": "2026-06-06 15:14:29"}, {"id": 86</t>
+          <t>{"id": 63081294, "listingMapId": 480137, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6741620909", "hostawayReservationId": "63081294", "channelReservationId": "6741620909", "externalPropertyId": "15950709", "externalUnitId": "1595070901", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "xEUoDAAf", "guestPortalUrl": "https://guest-portal.hostaway.com/63081294/xEUoDAAf", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-07-17 15:03:41", "pendingExpireDate": null, "guestName": "Jurgita Podlipskiene", "guestFirstName": "Jurgita", "guestLastName": "Podlipskiene", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "LT", "guestEmail": "jpodli.532474@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 6, "adults": 4, "children": 2, "infants": null, "pets": null, "arrivalDate": "2026-08-14", "departureDate": "2026-08-17", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 3, "phone": "+37062010545", "totalPrice": 355.36, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 58.36, "hostawayCommissionAmount": null, "cleaningFee": 67, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nBOOKING NOTE : Payment charge is EUR 4.97504", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": "38", "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": {"name": null, "channelId": 2005, "channelSpecificCode": "38", "longTerm": false, "cancellationPolicyItem": [{"refundAmount": 100, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": -93600, "event": "arrival"}, {"refundAmount": 0, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": 0, "event": "arrival"}]}, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 89959991, "accountId": 181258, "listingMapId": 480137, "reservationId": 63081294, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 67, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-07-17 15:10:02", "updatedOn": "2026-07-17 15:10:02"}, {"id": 89959993, "accountId": 181258, "listingMapId": 480137, "reservationId": 63081294, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 25.12, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerso</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-06-08T11:43:01+00:00</t>
+          <t>2026-08-17T05:24:54+00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>9662fad81c8052e4</t>
+          <t>6834a47a5b97f781</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>58132903</v>
+        <v>58438124</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{"id": 58132903, "listingMapId": 493047, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5364586891", "hostawayReservationId": "58132903", "channelReservationId": "5364586891", "externalPropertyId": "15480052", "externalUnitId": "1548005201", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "NksQNUyb", "guestPortalUrl": "https://guest-portal.hostaway.com/58132903/NksQNUyb", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-04-21 15:09:00", "pendingExpireDate": null, "guestName": "Takahiro Sasaki", "guestFirstName": "Takahiro", "guestLastName": "Sasaki", "guestExternalAccountId": null, "guestZipCode": "049712", "guestAddress": "30 08 Prudential Tower, 19 Cecil St", "guestCity": "bangkok", "guestCountry": "JP", "guestEmail": "tsasak.194672@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 1, "adults": 1, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-05-31", "departureDate": "2026-06-06", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 6, "phone": "+812035640799", "totalPrice": 273.65, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 44.08, "hostawayCommissionAmount": null, "cleaningFee": 40, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nBOOKING NOTE : Payment charge is EUR 3.6302\nArrivalTime: 23 00 - 24 00", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 82118118, "accountId": 181258, "listingMapId": 493047, "reservationId": 58132903, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 40, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-21 15:10:27", "updatedOn": "2026-04-21 15:10:27"}, {"id": 82118119, "accountId": 181258, "listingMapId": 493047, "reservationId": 58132903, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 19.94, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-21 15:10:27", "updatedOn": "2026-04-21 15:10:27"}, {"id": 82118120, "accountId": 181258, "listingMapId": 493047, "reservationId": 58132903, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 14.35, "currency": "EUR", "percentage": 7.2, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "inserted</t>
+          <t>{"id": 58438124, "listingMapId": 480139, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6669176297", "hostawayReservationId": "58438124", "channelReservationId": "6669176297", "externalPropertyId": "15499360", "externalUnitId": "1549936001", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "A1kNVcIQ", "guestPortalUrl": "https://guest-portal.hostaway.com/58438124/A1kNVcIQ", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-04-28 09:53:40", "pendingExpireDate": null, "guestName": "Olfa Ben Hassine", "guestFirstName": "Olfa", "guestLastName": "Ben Hassine", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "FR", "guestEmail": "ohassi.659128@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 6, "adults": 2, "children": 4, "infants": null, "pets": null, "arrivalDate": "2026-08-13", "departureDate": "2026-08-19", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 6, "phone": null, "totalPrice": 590.02, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 98.36, "hostawayCommissionAmount": null, "cleaningFee": 55, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nBOOKING NOTE : Payment charge is EUR 8.4203", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "There is no meal option with this room.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": "16", "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": {"name": "Moderate", "channelId": 2005, "channelSpecificCode": "16", "longTerm": false, "cancellationPolicyItem": [{"refundAmount": 100, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": -432000, "event": "arrival"}]}, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 82677563, "accountId": 181258, "listingMapId": 480139, "reservationId": 58438124, "name": "Cleaning fee", "feeType": "guest", "externalReservationUnitId": null, "amount": 55, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-28 09:54:59", "updatedOn": "2026-04-28 09:54:59"}, {"id": 82677564, "accountId": 181258, "listingMapId": 480139, "reservationId": 58438124, "name": "VAT", "feeType": "guest", "externalReservationUnitId": null, "amount": 47.6, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-28 09:54:59", "updatedOn": "2026-04-28 09:54:59"}, {"id": 82677565, "accountId": 181258, "listingMapId</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-06-08T11:43:02+00:00</t>
+          <t>2026-08-17T05:24:54+00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>f7d24d1af8342e1f</t>
+          <t>92cb9c71e9a5ae23</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>59977743</v>
+        <v>57636469</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{"id": 59977743, "listingMapId": 480140, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5304346991", "hostawayReservationId": "59977743", "channelReservationId": "5304346991", "externalPropertyId": "15500360", "externalUnitId": "1550036001", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "fUb0eqVA", "guestPortalUrl": "https://guest-portal.hostaway.com/59977743/fUb0eqVA", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-05-26 10:58:58", "pendingExpireDate": null, "guestName": "Arsinoe BERNARD-BRUNEL", "guestFirstName": "Arsinoe", "guestLastName": "BERNARD-BRUNEL", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": "", "guestCountry": "FR", "guestEmail": "aberna.109417@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 3, "adults": 3, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-06-01", "departureDate": "2026-06-05", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 4, "phone": "+33672232083", "totalPrice": 406.39, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 65.42, "hostawayCommissionAmount": null, "cleaningFee": 55, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nReservation has a cancellation grace period. Do not charge if cancelled before 2026-05-27 12:58:58\nApproximate time of arrival: between 19:00 and 20:00\nBOOKING NOTE : Payment charge is EUR 5.3872", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "There is no meal option with this room.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 85119741, "accountId": 181258, "listingMapId": 480140, "reservationId": 59977743, "name": "Cleaning fee", "feeType": "guest", "externalReservationUnitId": null, "amount": 55, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-05-26 11:01:35", "updatedOn": "2026-05-26 11:01:35"}, {"id": 85119742, "accountId": 181258, "listingMapId": 480140, "reservationId": 59977743, "name": "VAT", "feeType": "guest", "externalReservationUnitId": null, "amount": 29.98, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-05-26 11:01:35", "updatedOn": "2026-05-26 11:01:35"}, {"id": 85119743, "accountId": 181258, "listingMapId": 480140, "reservationId": 59977743, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 21.59, "currency": "EUR", "percentage": 7.2, "isInclud</t>
+          <t>{"id": 57636469, "listingMapId": 480140, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6089684943", "hostawayReservationId": "57636469", "channelReservationId": "6089684943", "externalPropertyId": "15500360", "externalUnitId": "1550036001", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "SEb6gkAK", "guestPortalUrl": "https://guest-portal.hostaway.com/57636469/SEb6gkAK", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-04-12 21:01:18", "pendingExpireDate": null, "guestName": "Jose Manuel Herrera", "guestFirstName": "Jose", "guestLastName": "Manuel Herrera", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "ES", "guestEmail": "jherre.706373@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 4, "adults": 3, "children": 1, "infants": null, "pets": null, "arrivalDate": "2026-08-20", "departureDate": "2026-08-26", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 6, "phone": null, "totalPrice": 614.11, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 99.95, "hostawayCommissionAmount": null, "cleaningFee": 55, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nBOOKING NOTE : Payment charge is EUR 8.597582", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "There is no meal option with this room.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": "16", "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": {"name": "Moderate", "channelId": 2005, "channelSpecificCode": "16", "longTerm": false, "cancellationPolicyItem": [{"refundAmount": 100, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": -432000, "event": "arrival"}]}, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 80885084, "accountId": 181258, "listingMapId": 480140, "reservationId": 57636469, "name": "Cleaning fee", "feeType": "guest", "externalReservationUnitId": null, "amount": 55, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-12 21:02:55", "updatedOn": "2026-04-12 21:02:55"}, {"id": 80885085, "accountId": 181258, "listingMapId": 480140, "reservationId": 57636469, "name": "VAT", "feeType": "guest", "externalReservationUnitId": null, "amount": 48.45, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-12 21:02:55", "updatedOn": "2026-04-12 21:02:55"}, {"id": 80885086, "accountId": 181258, "lis</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-06-08T11:43:03+00:00</t>
+          <t>2026-08-17T05:24:55+00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>538de935abc7f712</t>
+          <t>1f665f168ddcfd12</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>58796697</v>
+        <v>63317671</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{"id": 58796697, "listingMapId": 493047, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6507378886", "hostawayReservationId": "58796697", "channelReservationId": "6507378886", "externalPropertyId": "15480052", "externalUnitId": "1548005201", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "YsKIXD29", "guestPortalUrl": "https://guest-portal.hostaway.com/58796697/YsKIXD29", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-05-05 09:16:45", "pendingExpireDate": null, "guestName": "Blanc Amelie", "guestFirstName": "Blanc", "guestLastName": "Amelie", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "FR", "guestEmail": "bameli.717823@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 1, "adults": 1, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-06-22", "departureDate": "2026-06-25", "isDatesUnspecified": 0, "previousArrivalDate": "2026-06-15", "previousDepartureDate": "2026-06-26", "checkInTime": 16, "checkOutTime": 11, "nights": 3, "phone": "+33633570128", "totalPrice": 164.07, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 26.6, "hostawayCommissionAmount": null, "cleaningFee": 40, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "modified", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\n\nBOOKING NOTE : Payment charge is EUR 6.51", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 85993856, "accountId": 181258, "listingMapId": 493047, "reservationId": 58796697, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 40, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-06-05 05:43:59", "updatedOn": "2026-06-05 05:43:59"}, {"id": 85993857, "accountId": 181258, "listingMapId": 493047, "reservationId": 58796697, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 10.59, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-06-05 05:43:59", "updatedOn": "2026-06-05 05:43:59"}, {"id": 85993858, "accountId": 181258, "listingMapId": 493047, "reservationId": 58796697, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 7.62, "currency": "EUR", "percentage": 7.2, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-06-05 05:43:59", "updatedOn": "2026-06-05 05:43:59"}</t>
+          <t>{"id": 63317671, "listingMapId": 480137, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5834263051", "hostawayReservationId": "63317671", "channelReservationId": "5834263051", "externalPropertyId": "15950709", "externalUnitId": "1595070901", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "b_Erfyyc", "guestPortalUrl": "https://guest-portal.hostaway.com/63317671/b_Erfyyc", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-07-22 16:25:30", "pendingExpireDate": null, "guestName": "Guillermo Andrada Garcia", "guestFirstName": "Guillermo", "guestLastName": "Andrada Garcia", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": "", "guestCountry": "ES", "guestEmail": "ggarci.972744@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 5, "adults": 2, "children": 3, "infants": null, "pets": null, "arrivalDate": "2026-08-10", "departureDate": "2026-08-13", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 3, "phone": "+34635310128", "totalPrice": 287.73, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 47.96, "hostawayCommissionAmount": null, "cleaningFee": 67, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nBOOKING NOTE : Payment charge is EUR 4.02822\nApproximate time of arrival: between 21:00 and 22:00", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": "38", "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": {"name": null, "channelId": 2005, "channelSpecificCode": "38", "longTerm": false, "cancellationPolicyItem": [{"refundAmount": 100, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": -93600, "event": "arrival"}, {"refundAmount": 0, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": 0, "event": "arrival"}]}, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 90451534, "accountId": 181258, "listingMapId": 480137, "reservationId": 63317671, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 67, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-07-22 16:27:26", "updatedOn": "2026-07-22 16:27:26"}, {"id": 90451537, "accountId": 181258, "listingMapId": 480137, "reservationId": 63317671, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 19.55, "currency": "EUR", "p</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-06-08T11:43:04+00:00</t>
+          <t>2026-08-17T05:24:56+00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>71236ac819d026c7</t>
+          <t>641bef4f1ee002de</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>60438654</v>
+        <v>62814553</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{"id": 60438654, "listingMapId": 493047, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5532532701", "hostawayReservationId": "60438654", "channelReservationId": "5532532701", "externalPropertyId": "15480052", "externalUnitId": "1548005201", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "ev3og2Gc", "guestPortalUrl": "https://guest-portal.hostaway.com/60438654/ev3og2Gc", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-06-04 09:42:39", "pendingExpireDate": null, "guestName": "El Mehdi Lotfi", "guestFirstName": "El", "guestLastName": "Mehdi Lotfi", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "MA", "guestEmail": "elotfi.234464@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 1, "adults": 1, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-09-29", "departureDate": "2026-10-16", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 17, "phone": "+212652629697", "totalPrice": 761.79, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 121.97, "hostawayCommissionAmount": null, "cleaningFee": 40, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nBOOKING NOTE : Payment charge is EUR 10.0443", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 85917741, "accountId": 181258, "listingMapId": 493047, "reservationId": 60438654, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 40, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-06-04 09:44:11", "updatedOn": "2026-06-04 09:44:11"}, {"id": 85917742, "accountId": 181258, "listingMapId": 493047, "reservationId": 60438654, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 61.59, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-06-04 09:44:11", "updatedOn": "2026-06-04 09:44:11"}, {"id": 85917743, "accountId": 181258, "listingMapId": 493047, "reservationId": 60438654, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 44.34, "currency": "EUR", "percentage": 7.2, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-06-04 09:44:11", "updatedOn": "2026-06-04 09:44:11"}, {"id": 85</t>
+          <t>{"id": 62814553, "listingMapId": 480139, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5702620235", "hostawayReservationId": "62814553", "channelReservationId": "5702620235", "externalPropertyId": "15499360", "externalUnitId": "1549936001", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "ggN_rNGO", "guestPortalUrl": "https://guest-portal.hostaway.com/62814553/ggN_rNGO", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-07-12 08:36:20", "pendingExpireDate": null, "guestName": "Wellington Usuanlele", "guestFirstName": "Wellington", "guestLastName": "Usuanlele", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": "", "guestCountry": "GB", "guestEmail": "wusuan.260194@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 3, "adults": 3, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-09-19", "departureDate": "2026-09-24", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 5, "phone": null, "totalPrice": 449.86, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 72.35, "hostawayCommissionAmount": null, "cleaningFee": 55, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nApproximate time of arrival: between 12:00 and 13:00\nMy wife and I are both based in london and we are planning a trip to Toulouse to explore the city, enjoy the local culture, and spend some quality time together. We'll also be staying with my younger brother, who works as a teacher in Beaumont-de-Lomagne, so your flat would be a great base for our stay. We look forward to the opportunity to stay at your place and hope to be your guests. It is our first time in france so we will appreciate any and every support we can get to make our stay as peaceful as possible.\nBest regards,\nBOOKING NOTE : Payment charge is EUR 5.9584", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "There is no meal option with this room.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": "60", "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": {"name": null, "channelId": 2005, "channelSpecificCode": "60", "longTerm": false, "cancellationPolicyItem": [{"refundAmount": 100, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": -439200, "event": "arrival"}, {"refundAmount": 79, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": 0, "event": "arrival"}]}, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 89376043, "accountId": 181258, "listingMapId": 480139, "</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-06-08T11:43:05+00:00</t>
+          <t>2026-08-17T05:24:57+00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1eb93e2694c97049</t>
+          <t>5be66d54bcfa21c0</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>60330887</v>
+        <v>63982399</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{"id": 60330887, "listingMapId": 480137, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6940784720", "hostawayReservationId": "60330887", "channelReservationId": "6940784720", "externalPropertyId": "15950709", "externalUnitId": "1595070901", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "xGpwHPEM", "guestPortalUrl": "https://guest-portal.hostaway.com/60330887/xGpwHPEM", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-06-02 12:51:58", "pendingExpireDate": null, "guestName": "Thierry OLLIVIER", "guestFirstName": "Thierry", "guestLastName": "OLLIVIER", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": "", "guestCountry": "FR", "guestEmail": "tolliv.187487@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 3, "adults": 3, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-06-10", "departureDate": "2026-06-15", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 5, "phone": "+33781244870", "totalPrice": 460.15, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 74.12, "hostawayCommissionAmount": null, "cleaningFee": 67, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nReservation has a cancellation grace period. Do not charge if cancelled before 2026-06-03 14:51:58\nApproximate time of arrival: between 19:00 and 20:00\nBOOKING NOTE : Payment charge is EUR 6.4421", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 85749347, "accountId": 181258, "listingMapId": 480137, "reservationId": 60330887, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 67, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-06-02 12:53:46", "updatedOn": "2026-06-02 12:53:46"}, {"id": 85749348, "accountId": 181258, "listingMapId": 480137, "reservationId": 60330887, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 33.55, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-06-02 12:53:46", "updatedOn": "2026-06-02 12:53:46"}, {"id": 85749349, "accountId": 181258, "listingMapId": 480137, "reservationId": 60330887, "name": "taxe de séjour", "feeType": "guest", "externalReservationUnitId": null, "amount": 24.15, "currency": "EUR", "percentage": 7.2, "isInclu</t>
+          <t>{"id": 63982399, "listingMapId": 480140, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5228577194", "hostawayReservationId": "63982399", "channelReservationId": "5228577194", "externalPropertyId": "15500360", "externalUnitId": "1550036001", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "tEGwdqJN", "guestPortalUrl": "https://guest-portal.hostaway.com/63982399/tEGwdqJN", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-08-02 10:44:53", "pendingExpireDate": null, "guestName": "Paloma Vicente Vives", "guestFirstName": "Paloma", "guestLastName": "Vicente Vives", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": "", "guestCountry": "ES", "guestEmail": "pvives.939654@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 4, "adults": 2, "children": 2, "infants": null, "pets": null, "arrivalDate": "2026-08-08", "departureDate": "2026-08-11", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 3, "phone": "+34651049945", "totalPrice": 294.64, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 48.8, "hostawayCommissionAmount": null, "cleaningFee": 55, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nReservation has a cancellation grace period. Do not charge if cancelled before 2026-08-03 12:44:53\n\nBOOKING NOTE : Payment charge is EUR 4.0187", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "There is no meal option with this room.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": "1", "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": {"name": null, "channelId": 2005, "channelSpecificCode": "1", "longTerm": false, "cancellationPolicyItem": [{"refundAmount": 100, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": -393307, "event": "arrival"}, {"refundAmount": 0, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": 0, "event": "arrival"}]}, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 91468887, "accountId": 181258, "listingMapId": 480140, "reservationId": 63982399, "name": "Cleaning fee", "feeType": "guest", "externalReservationUnitId": null, "amount": 55, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-08-02 10:46:21", "updatedOn": "2026-08-02 10:46:21"}, {"id": 91468888, "accountId": 181258, "listingMapId": 480140, "reservationId": 63982399, "name": "VAT", "feeType": "guest", "externalReservationUnitId": null, "amount": 21.1, "curren</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-06-08T11:43:06+00:00</t>
+          <t>2026-08-17T05:24:58+00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>f7f8fa109a23ab06</t>
+          <t>45959fbf20dd2012</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>60299082</v>
+        <v>55943028</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"id": 60299082, "listingMapId": 480137, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5843937748", "hostawayReservationId": "60299082", "channelReservationId": "5843937748", "externalPropertyId": "15950709", "externalUnitId": "1595070901", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "HqQHlU8d", "guestPortalUrl": "https://guest-portal.hostaway.com/60299082/HqQHlU8d", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-06-01 21:16:46", "pendingExpireDate": null, "guestName": "Sonia Naomi Vazquez Valdes", "guestFirstName": "Sonia", "guestLastName": "Naomi Vazquez Valdes", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": "", "guestCountry": "ES", "guestEmail": "svalde.190088@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 3, "adults": 3, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-06-23", "departureDate": "2026-06-25", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 2, "phone": "+341819580", "totalPrice": 230.97, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 37.55, "hostawayCommissionAmount": null, "cleaningFee": 67, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nBOOKING NOTE : Payment charge is EUR 3.23358", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 85699110, "accountId": 181258, "listingMapId": 480137, "reservationId": 60299082, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 67, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-06-01 21:18:26", "updatedOn": "2026-06-01 21:18:26"}, {"id": 85699111, "accountId": 181258, "listingMapId": 480137, "reservationId": 60299082, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 13.99, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-06-01 21:18:26", "updatedOn": "2026-06-01 21:18:26"}, {"id": 85699112, "accountId": 181258, "listingMapId": 480137, "reservationId": 60299082, "name": "taxe de séjour", "feeType": "guest", "externalReservationUnitId": null, "amount": 10.07, "currency": "EUR", "percentage": 7.2, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-06-01 21:18:26", "updatedOn": "2026-06-01 21:18:26"}, </t>
+          <t>{"id": 55943028, "listingMapId": 480139, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5851160347", "hostawayReservationId": "55943028", "channelReservationId": "5851160347", "externalPropertyId": "15499360", "externalUnitId": "1549936001", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "nYmZ4gpP", "guestPortalUrl": "https://guest-portal.hostaway.com/55943028/nYmZ4gpP", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-03-12 13:21:47", "pendingExpireDate": null, "guestName": "Sikharulidze zaza", "guestFirstName": "Sikharulidze", "guestLastName": "zaza", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "FR", "guestEmail": "msikha.130294@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 6, "adults": 4, "children": 2, "infants": null, "pets": null, "arrivalDate": "2026-08-06", "departureDate": "2026-08-11", "isDatesUnspecified": 0, "previousArrivalDate": "2026-08-06", "previousDepartureDate": "2026-08-12", "checkInTime": 16, "checkOutTime": 11, "nights": 5, "phone": "+33780178390", "totalPrice": 519.84, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 85.07, "hostawayCommissionAmount": null, "cleaningFee": 55, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "modified", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nBOOKING NOTE : Payment charge is EUR 9.848489", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "There is no meal option with this room.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": "16", "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": {"name": "Moderate", "channelId": 2005, "channelSpecificCode": "16", "longTerm": false, "cancellationPolicyItem": [{"refundAmount": 100, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": -432000, "event": "arrival"}]}, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 88927933, "accountId": 181258, "listingMapId": 480139, "reservationId": 55943028, "name": "Cleaning fee", "feeType": "guest", "externalReservationUnitId": null, "amount": 55, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-07-07 12:42:40", "updatedOn": "2026-07-07 12:42:40"}, {"id": 88927934, "accountId": 181258, "listingMapId": 480139, "reservationId": 55943028, "name": "VAT", "feeType": "guest", "externalReservationUnitId": null, "amount": 40.49, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-07-07 12:42:41", "updatedOn": "2026-07-07 12:42:41"}, {"id": 88927935</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-06-08T11:43:07+00:00</t>
+          <t>2026-08-17T05:24:59+00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8c578665dc59b421</t>
+          <t>683b4e6ef641d0f3</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>60296863</v>
+        <v>64485769</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{"id": 60296863, "listingMapId": 480140, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5075416435", "hostawayReservationId": "60296863", "channelReservationId": "5075416435", "externalPropertyId": "15500360", "externalUnitId": "1550036001", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "lmwP56yj", "guestPortalUrl": "https://guest-portal.hostaway.com/60296863/lmwP56yj", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-06-01 20:34:45", "pendingExpireDate": null, "guestName": "Rossen Ploskov", "guestFirstName": "Rossen", "guestLastName": "Ploskov", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "BG", "guestEmail": "rplosk.904645@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 3, "adults": 3, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-06-14", "departureDate": "2026-06-21", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 7, "phone": "+359896700987", "totalPrice": 638.23, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 102.41, "hostawayCommissionAmount": null, "cleaningFee": 55, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nBOOKING NOTE : Payment charge is EUR 8.4336", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "There is no meal option with this room.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 85695206, "accountId": 181258, "listingMapId": 480140, "reservationId": 60296863, "name": "Cleaning fee", "feeType": "guest", "externalReservationUnitId": null, "amount": 55, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-06-01 20:36:25", "updatedOn": "2026-06-01 20:36:25"}, {"id": 85695207, "accountId": 181258, "listingMapId": 480140, "reservationId": 60296863, "name": "VAT", "feeType": "guest", "externalReservationUnitId": null, "amount": 49.76, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-06-01 20:36:25", "updatedOn": "2026-06-01 20:36:25"}, {"id": 85695208, "accountId": 181258, "listingMapId": 480140, "reservationId": 60296863, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 35.83, "currency": "EUR", "percentage": 7.2, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-06-01 20:36:25", "updatedOn": "2026-06-01 20:36:25"}, {"id": 85695209, "accountId": 181</t>
+          <t>{"id": 64485769, "listingMapId": 480139, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6925281420", "hostawayReservationId": "64485769", "channelReservationId": "6925281420", "externalPropertyId": "15499360", "externalUnitId": "1549936001", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "mF75zzxQ", "guestPortalUrl": "https://guest-portal.hostaway.com/64485769/mF75zzxQ", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-08-10 22:29:58", "pendingExpireDate": null, "guestName": "Lucia Guzun", "guestFirstName": "Lucia", "guestLastName": "Guzun", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "CA", "guestEmail": "lguzun.879642@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 2, "adults": 2, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-09-14", "departureDate": "2026-09-19", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 5, "phone": null, "totalPrice": 411.82, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 66.28, "hostawayCommissionAmount": null, "cleaningFee": 55, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nBOOKING NOTE : Payment charge is EUR 5.4586", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "There is no meal option with this room.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": "37", "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": {"name": null, "channelId": 2005, "channelSpecificCode": "37", "longTerm": false, "cancellationPolicyItem": [{"refundAmount": 100, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": -612000, "event": "arrival"}, {"refundAmount": 81, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": 0, "event": "arrival"}]}, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 92265341, "accountId": 181258, "listingMapId": 480139, "reservationId": 64485769, "name": "Cleaning fee", "feeType": "guest", "externalReservationUnitId": null, "amount": 55, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-08-10 22:31:27", "updatedOn": "2026-08-10 22:31:27"}, {"id": 92265342, "accountId": 181258, "listingMapId": 480139, "reservationId": 64485769, "name": "VAT", "feeType": "guest", "externalReservationUnitId": null, "amount": 30.45, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-08</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-06-08T11:43:08+00:00</t>
+          <t>2026-08-17T05:24:59+00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>d8cac24f80105f44</t>
+          <t>8ea7f8a8d99c02c1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>60290392</v>
+        <v>64375423</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{"id": 60290392, "listingMapId": 480140, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6637658696", "hostawayReservationId": "60290392", "channelReservationId": "6637658696", "externalPropertyId": "15500360", "externalUnitId": "1550036001", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "vRzwemTt", "guestPortalUrl": "https://guest-portal.hostaway.com/60290392/vRzwemTt", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-06-01 18:31:20", "pendingExpireDate": null, "guestName": "Uwe Stolzenburg", "guestFirstName": "Uwe", "guestLastName": "Stolzenburg", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": "", "guestCountry": "DE", "guestEmail": "ustolz.279753@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 2, "adults": 2, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-07-05", "departureDate": "2026-07-07", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 2, "phone": null, "totalPrice": 240.66, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 38.97, "hostawayCommissionAmount": null, "cleaningFee": 55, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nApproximate time of arrival: between 14:00 and 15:00\nBOOKING NOTE : Payment charge is EUR 3.2095", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "There is no meal option with this room.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 85682976, "accountId": 181258, "listingMapId": 480140, "reservationId": 60290392, "name": "Cleaning fee", "feeType": "guest", "externalReservationUnitId": null, "amount": 55, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-06-01 18:33:31", "updatedOn": "2026-06-01 18:33:31"}, {"id": 85682977, "accountId": 181258, "listingMapId": 480140, "reservationId": 60290392, "name": "VAT", "feeType": "guest", "externalReservationUnitId": null, "amount": 15.84, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-06-01 18:33:32", "updatedOn": "2026-06-01 18:33:32"}, {"id": 85682978, "accountId": 181258, "listingMapId": 480140, "reservationId": 60290392, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 11.41, "currency": "EUR", "percentage": 7.2, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-06-01 18:33:32", "updatedOn": "2026-06-01 18</t>
+          <t>{"id": 64375423, "listingMapId": 480137, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5463406743", "hostawayReservationId": "64375423", "channelReservationId": "5463406743", "externalPropertyId": "15950709", "externalUnitId": "1595070901", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "js4X2y3f", "guestPortalUrl": "https://guest-portal.hostaway.com/64375423/js4X2y3f", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-08-08 18:36:09", "pendingExpireDate": null, "guestName": "Karam Fallouk", "guestFirstName": "Karam", "guestLastName": "Fallouk", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "FR", "guestEmail": "kfallo.736682@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 2, "adults": 2, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-08-08", "departureDate": "2026-08-10", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 2, "phone": "+33777513650", "totalPrice": 199.33, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 32.5, "hostawayCommissionAmount": null, "cleaningFee": 67, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nBOOKING NOTE : Payment charge is EUR 2.79062", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": "1", "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": {"name": null, "channelId": 2005, "channelSpecificCode": "1", "longTerm": false, "cancellationPolicyItem": [{"refundAmount": 0, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": 0, "event": "arrival"}]}, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 92060574, "accountId": 181258, "listingMapId": 480137, "reservationId": 64375423, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 67, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-08-08 18:37:35", "updatedOn": "2026-08-08 18:37:35"}, {"id": 92060575, "accountId": 181258, "listingMapId": 480137, "reservationId": 64375423, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 11.29, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-08-08 18:37:35", "updatedOn": "2026-08-08 18:37:35"}, {"id": 92060576, "accountId": 181258,</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-06-08T11:43:09+00:00</t>
+          <t>2026-08-17T05:25:00+00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>530c1934e0b138af</t>
+          <t>0c49b2accc2e491a</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>56445297</v>
+        <v>63041555</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{"id": 56445297, "listingMapId": 480139, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5331465465", "hostawayReservationId": "56445297", "channelReservationId": "5331465465", "externalPropertyId": "15499360", "externalUnitId": "1549936001", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "QwtvUoF1", "guestPortalUrl": "https://guest-portal.hostaway.com/56445297/QwtvUoF1", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-03-21 10:34:33", "pendingExpireDate": null, "guestName": "Jean-Pierre GOURAUD", "guestFirstName": "Jean-Pierre", "guestLastName": "GOURAUD", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": "", "guestCountry": "FR", "guestEmail": "jgoura.517236@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 5, "adults": 5, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-05-29", "departureDate": "2026-06-01", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 3, "phone": "+33787279502", "totalPrice": 366.54, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 59.06, "hostawayCommissionAmount": null, "cleaningFee": 55, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\n\nBOOKING NOTE : Payment charge is EUR 5.1315446", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "There is no meal option with this room.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 78324438, "accountId": 181258, "listingMapId": 480139, "reservationId": 56445297, "name": "Cleaning fee", "feeType": "guest", "externalReservationUnitId": null, "amount": 55, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-21 10:35:55", "updatedOn": "2026-03-21 10:35:55"}, {"id": 78324439, "accountId": 181258, "listingMapId": 480139, "reservationId": 56445297, "name": "VAT", "feeType": "guest", "externalReservationUnitId": null, "amount": 26.58, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-21 10:35:55", "updatedOn": "2026-03-21 10:35:55"}, {"id": 78324440, "accountId": 181258, "listingMapId": 480139, "reservationId": 56445297, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 19.14, "currency": "EUR", "percentage": 7.2, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-21 10:35:55", "updatedOn": "2026-03-21 10:35:55"}, {"id": 78324441, "acc</t>
+          <t>{"id": 63041555, "listingMapId": 480137, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6892801792", "hostawayReservationId": "63041555", "channelReservationId": "6892801792", "externalPropertyId": "15950709", "externalUnitId": "1595070901", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "32Do3sXF", "guestPortalUrl": "https://guest-portal.hostaway.com/63041555/32Do3sXF", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-07-16 18:03:27", "pendingExpireDate": null, "guestName": "Judit Alonso", "guestFirstName": "Judit", "guestLastName": "Alonso", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "ES", "guestEmail": "jalons.756857@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 5, "adults": 2, "children": 3, "infants": null, "pets": null, "arrivalDate": "2026-08-06", "departureDate": "2026-08-08", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 2, "phone": "+34617318435", "totalPrice": 226.78, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 37.86, "hostawayCommissionAmount": null, "cleaningFee": 67, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nBOOKING NOTE : Payment charge is EUR 3.17492", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": "38", "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": {"name": null, "channelId": 2005, "channelSpecificCode": "38", "longTerm": false, "cancellationPolicyItem": [{"refundAmount": 100, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": -93600, "event": "arrival"}, {"refundAmount": 0, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": 0, "event": "arrival"}]}, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 89875657, "accountId": 181258, "listingMapId": 480137, "reservationId": 63041555, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 67, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-07-16 18:08:47", "updatedOn": "2026-07-16 18:08:47"}, {"id": 89875658, "accountId": 181258, "listingMapId": 480137, "reservationId": 63041555, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 14.15, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImport</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-06-08T11:43:10+00:00</t>
+          <t>2026-08-17T05:25:01+00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>6f53b74dd01c1755</t>
+          <t>65c0f016d1409527</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>55377365</v>
+        <v>61234357</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"id": 55377365, "listingMapId": 493047, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5742761102", "hostawayReservationId": "55377365", "channelReservationId": "5742761102", "externalPropertyId": "15480052", "externalUnitId": "1548005201", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "l_qoqGTo", "guestPortalUrl": "https://guest-portal.hostaway.com/55377365/l_qoqGTo", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 1, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-01-14 21:19:48", "pendingExpireDate": null, "guestName": "DANILA DALL&amp;#39;OPPIO", "guestFirstName": "DANILA", "guestLastName": "DALL&amp;#39;OPPIO", "guestExternalAccountId": null, "guestZipCode": null, "guestAddress": null, "guestCity": null, "guestCountry": null, "guestEmail": null, "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 2, "adults": 2, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-05-28", "departureDate": "2026-05-31", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 3, "phone": null, "totalPrice": 145.8, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": null, "hostawayCommissionAmount": null, "cleaningFee": null, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Unknown", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": null, "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [], "reservationUnit": [], "insertedOn": "2026-03-02 23:46:45", "updatedOn": "2026-05-31 07:06:52", "latestActivityOn": "2026-05-31 07:06:52", "customerUserId": null, "guestLocale": null, "localeForMessaging": null, "localeForMessagingSource": null, "listingCustomFields": null, "rentalAgreementFileUrl": null, "reservationAgreement": "not_required", "financeField": [{"id": 226915513, "units": 1, "listingFeeSettingId": null, "type": "accommodation", "name": "baseRate", "title": "Base rate", "alias": null, "quantity": null, "value": 145.8, "isIncludedInTotalPrice": 1, "isOverriddenByUser": 0, "isMandatory": 1, "isQuantitySelectable": 0, "isDeleted": 0, "total": 145.8}, {"id": 226915514, "units": 1, "listingFeeSettingId": null, "type": "totals", "name": "totalPriceFromChannel", "title": "Total price from channel", "alias": null, "quantity": null, "value": 145.8, "isIncludedInTotalPrice": 0, "isOverriddenByUser": 0, "isMandatory": 0, "isQuantitySelectable": 0, "isDeleted": 0, "total": 145.8}], "guestPaymentCardIsVirtual": null, "insuranceStatus": "not_eligible", "claimStatus": null, "insurancePolicyId": null, "insuranceCoverageStart": null, "insuranceCoverageEnd": null, "cancellationPolicyId": null, </t>
+          <t>{"id": 61234357, "listingMapId": 480140, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6272874008", "hostawayReservationId": "61234357", "channelReservationId": "6272874008", "externalPropertyId": "15500360", "externalUnitId": "1550036001", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "wanmYkSc", "guestPortalUrl": "https://guest-portal.hostaway.com/61234357/wanmYkSc", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-06-20 18:51:53", "pendingExpireDate": null, "guestName": "Maria Pilar Manzano Negro", "guestFirstName": "Maria", "guestLastName": "Pilar Manzano Negro", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": "", "guestCountry": "ES", "guestEmail": "mnegro.571563@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 3, "adults": 3, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-08-03", "departureDate": "2026-08-08", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 5, "phone": null, "totalPrice": 489.71, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 78.71, "hostawayCommissionAmount": null, "cleaningFee": 55, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nBOOKING NOTE : Payment charge is EUR 6.482\nWe would need parking", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "There is no meal option with this room.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": "16", "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": {"name": "Moderate", "channelId": 2005, "channelSpecificCode": "16", "longTerm": false, "cancellationPolicyItem": [{"refundAmount": 100, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": -432000, "event": "arrival"}]}, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 87397477, "accountId": 181258, "listingMapId": 480140, "reservationId": 61234357, "name": "Cleaning fee", "feeType": "guest", "externalReservationUnitId": null, "amount": 55, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-06-20 18:54:55", "updatedOn": "2026-06-20 18:54:55"}, {"id": 87397478, "accountId": 181258, "listingMapId": 480140, "reservationId": 61234357, "name": "VAT", "feeType": "guest", "externalReservationUnitId": null, "amount": 37.09, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-06-20 18:54:55", "updatedOn": "2026-06-20 18:54:55"}, {"id": 8</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-06-08T11:43:11+00:00</t>
+          <t>2026-08-17T05:25:02+00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>5afeb3fb2c183bbd</t>
+          <t>78c022995b791ab5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>55733615</v>
+        <v>64268943</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{"id": 55733615, "listingMapId": 480139, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5970827724", "hostawayReservationId": "55733615", "channelReservationId": "5970827724", "externalPropertyId": "15499360", "externalUnitId": "1549936001", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "pJ5qPBKG", "guestPortalUrl": "https://guest-portal.hostaway.com/55733615/pJ5qPBKG", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-03-08 20:40:04", "pendingExpireDate": null, "guestName": "Mateusz Daniol", "guestFirstName": "Mateusz", "guestLastName": "Daniol", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": "", "guestCountry": "PL", "guestEmail": "mdanio.200875@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 5, "adults": 5, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-04-15", "departureDate": "2026-04-20", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 5, "phone": "+48603760773", "totalPrice": 595.19, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 95.54, "hostawayCommissionAmount": null, "cleaningFee": 55, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\n\nBOOKING NOTE : Payment charge is EUR 8.332597", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "There is no meal option with this room.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 77133527, "accountId": 181258, "listingMapId": 480139, "reservationId": 55733615, "name": "Cleaning fee", "feeType": "guest", "externalReservationUnitId": null, "amount": 55, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-08 20:41:43", "updatedOn": "2026-03-08 20:41:43"}, {"id": 77133528, "accountId": 181258, "listingMapId": 480139, "reservationId": 55733615, "name": "VAT", "feeType": "guest", "externalReservationUnitId": null, "amount": 46.09, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-08 20:41:43", "updatedOn": "2026-03-08 20:41:43"}, {"id": 77133529, "accountId": 181258, "listingMapId": 480139, "reservationId": 55733615, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 33.19, "currency": "EUR", "percentage": 7.2, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-08 20:41:43", "updatedOn": "2026-03-08 20:41:43"}, {"id": 77133530, "accountId": 18</t>
+          <t>{"id": 64268943, "listingMapId": 493047, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5603613188", "hostawayReservationId": "64268943", "channelReservationId": "5603613188", "externalPropertyId": "15480052", "externalUnitId": "1548005201", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "biAA7ceD", "guestPortalUrl": "https://guest-portal.hostaway.com/64268943/biAA7ceD", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-08-07 19:59:46", "pendingExpireDate": null, "guestName": "Pristina HELMANY PAYET", "guestFirstName": "Pristina", "guestLastName": "HELMANY PAYET", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "MQ", "guestEmail": "ppayet.776039@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 2, "adults": 2, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-09-02", "departureDate": "2026-09-05", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 3, "phone": "+596696089122", "totalPrice": 154.11, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 25.01, "hostawayCommissionAmount": null, "cleaningFee": 40, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nBOOKING NOTE : Payment charge is EUR 2.0594", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": "38", "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": {"name": null, "channelId": 2005, "channelSpecificCode": "38", "longTerm": false, "cancellationPolicyItem": [{"refundAmount": 100, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": -93600, "event": "arrival"}, {"refundAmount": 0, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": 0, "event": "arrival"}]}, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 91985665, "accountId": 181258, "listingMapId": 493047, "reservationId": 64268943, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 40, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-08-07 20:01:13", "updatedOn": "2026-08-07 20:01:13"}, {"id": 91985666, "accountId": 181258, "listingMapId": 493047, "reservationId": 64268943, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 9.74, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPe</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-06-08T11:43:12+00:00</t>
+          <t>2026-08-17T05:25:02+00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2545d37d80f8571d</t>
+          <t>fec9036e3b949abe</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>59804583</v>
+        <v>63939953</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{"id": 59804583, "listingMapId": 493047, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6485129999", "hostawayReservationId": "59804583", "channelReservationId": "6485129999", "externalPropertyId": "15480052", "externalUnitId": "1548005201", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "TfW0bbA3", "guestPortalUrl": "https://guest-portal.hostaway.com/59804583/TfW0bbA3", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-05-22 13:43:17", "pendingExpireDate": null, "guestName": "Helena Goncalves", "guestFirstName": "Helena", "guestLastName": "Goncalves", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "FR", "guestEmail": "hgonca.795365@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 2, "adults": 2, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-05-22", "departureDate": "2026-05-28", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 6, "phone": "+33782297497", "totalPrice": 251.92, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 40.61, "hostawayCommissionAmount": null, "cleaningFee": 40, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\n\nBOOKING NOTE : Payment charge is EUR 3.5268646", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 84793966, "accountId": 181258, "listingMapId": 493047, "reservationId": 59804583, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 40, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-05-22 13:44:45", "updatedOn": "2026-05-22 13:44:45"}, {"id": 84793967, "accountId": 181258, "listingMapId": 493047, "reservationId": 59804583, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 18.08, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-05-22 13:44:45", "updatedOn": "2026-05-22 13:44:45"}, {"id": 84793968, "accountId": 181258, "listingMapId": 493047, "reservationId": 59804583, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 13.02, "currency": "EUR", "percentage": 7.2, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-05-22 13:44:45", "updatedOn": "2026-05-22 13:44:45"}, {"id</t>
+          <t>{"id": 63939953, "listingMapId": 480137, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5090384006", "hostawayReservationId": "63939953", "channelReservationId": "5090384006", "externalPropertyId": "15950709", "externalUnitId": "1595070901", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "uoZHLOZo", "guestPortalUrl": "https://guest-portal.hostaway.com/63939953/uoZHLOZo", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-08-01 09:15:47", "pendingExpireDate": null, "guestName": "Ivan Garcia", "guestFirstName": "Ivan", "guestLastName": "Garcia", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "ES", "guestEmail": "igarci.239568@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 5, "adults": 3, "children": 2, "infants": null, "pets": null, "arrivalDate": "2026-08-03", "departureDate": "2026-08-05", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 2, "phone": "+34630492014", "totalPrice": 196.08, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 32.5, "hostawayCommissionAmount": null, "cleaningFee": 67, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nYou have a booker that would like free parking. (based on availability)\nBOOKING NOTE : Payment charge is EUR 2.74512", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": "38", "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": {"name": null, "channelId": 2005, "channelSpecificCode": "38", "longTerm": false, "cancellationPolicyItem": [{"refundAmount": 100, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": -93600, "event": "arrival"}, {"refundAmount": 0, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": 0, "event": "arrival"}]}, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 91382371, "accountId": 181258, "listingMapId": 480137, "reservationId": 63939953, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 67, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-08-01 09:17:16", "updatedOn": "2026-08-01 09:17:16"}, {"id": 91382372, "accountId": 181258, "listingMapId": 480137, "reservationId": 63939953, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 11.29, "currency": "EUR", "percenta</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-06-08T11:43:13+00:00</t>
+          <t>2026-08-17T05:25:03+00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>95a5de6beeccad3f</t>
+          <t>e9655f9794ef2df5</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>59334748</v>
+        <v>64109345</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{"id": 59334748, "listingMapId": 480137, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5206720926", "hostawayReservationId": "59334748", "channelReservationId": "5206720926", "externalPropertyId": "15950709", "externalUnitId": "1595070901", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "43pRRoGg", "guestPortalUrl": "https://guest-portal.hostaway.com/59334748/43pRRoGg", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-05-15 14:16:05", "pendingExpireDate": null, "guestName": "Julien Catala", "guestFirstName": "Julien", "guestLastName": "Catala", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": "", "guestCountry": "FR", "guestEmail": "jcatal.461010@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 3, "adults": 3, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-06-19", "departureDate": "2026-06-21", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 2, "phone": "+33666203757", "totalPrice": 254.95, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 41.38, "hostawayCommissionAmount": null, "cleaningFee": 67, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nBOOKING NOTE : Payment charge is EUR 3.5693\nApproximate time of arrival: between 16:00 and 17:00", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 84175606, "accountId": 181258, "listingMapId": 480137, "reservationId": 59334748, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 67, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-05-15 14:17:36", "updatedOn": "2026-05-15 14:17:36"}, {"id": 84175607, "accountId": 181258, "listingMapId": 480137, "reservationId": 59334748, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 16.04, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-05-15 14:17:36", "updatedOn": "2026-05-15 14:17:36"}, {"id": 84175608, "accountId": 181258, "listingMapId": 480137, "reservationId": 59334748, "name": "taxe de séjour", "feeType": "guest", "externalReservationUnitId": null, "amount": 11.55, "currency": "EUR", "percentage": 7.2, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-05-15 14:17:36", "updated</t>
+          <t>{"id": 64109345, "listingMapId": 480139, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6018359789", "hostawayReservationId": "64109345", "channelReservationId": "6018359789", "externalPropertyId": "15499360", "externalUnitId": "1549936001", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "AIhQ4EuY", "guestPortalUrl": "https://guest-portal.hostaway.com/64109345/AIhQ4EuY", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-08-04 20:59:21", "pendingExpireDate": null, "guestName": "ANGELA MARIA OVIEDO SABOGAL", "guestFirstName": "ANGELA", "guestLastName": "MARIA OVIEDO SABOGAL", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": "", "guestCountry": "FR", "guestEmail": "asabog.323408@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 5, "adults": 2, "children": 3, "infants": null, "pets": null, "arrivalDate": "2026-08-21", "departureDate": "2026-08-23", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 2, "phone": null, "totalPrice": 189.33, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 31.6, "hostawayCommissionAmount": null, "cleaningFee": 55, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nReservation has a cancellation grace period. Do not charge if cancelled before 2026-08-05 22:59:21\nApproximate time of arrival: between 18:00 and 19:00\nBOOKING NOTE : Payment charge is EUR 2.6026", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "There is no meal option with this room.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": "1", "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": {"name": null, "channelId": 2005, "channelSpecificCode": "1", "longTerm": false, "cancellationPolicyItem": [{"refundAmount": 100, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": -1306839, "event": "arrival"}, {"refundAmount": 0, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": 0, "event": "arrival"}]}, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 91714865, "accountId": 181258, "listingMapId": 480139, "reservationId": 64109345, "name": "Cleaning fee", "feeType": "guest", "externalReservationUnitId": null, "amount": 55, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-08-04 21:00:46", "updatedOn": "2026-08-04 21:00:46"}, {"id": 91714866, "accountId": 181258, "listingMapId": 480139, "reservationId": 64109345, "name": "VAT", "feeType": "guest", "</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-06-08T11:43:16+00:00</t>
+          <t>2026-08-17T05:25:04+00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>3ce64a5cebfbdf38</t>
+          <t>a55153ec1a56b2e4</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>58720999</v>
+        <v>64003964</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{"id": 58720999, "listingMapId": 480137, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6413954681", "hostawayReservationId": "58720999", "channelReservationId": "6413954681", "externalPropertyId": "15950709", "externalUnitId": "1595070901", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "vMSmLUAw", "guestPortalUrl": "https://guest-portal.hostaway.com/58720999/vMSmLUAw", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-05-03 23:57:44", "pendingExpireDate": null, "guestName": "Ianko Jose Perea", "guestFirstName": "Ianko", "guestLastName": "Jose Perea", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": "", "guestCountry": "AR", "guestEmail": "iperea.465062@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 4, "adults": 4, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-05-24", "departureDate": "2026-05-26", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 2, "phone": "+5491154730938", "totalPrice": 235.77, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 38.32, "hostawayCommissionAmount": null, "cleaningFee": 67, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\n\nBOOKING NOTE : Payment charge is EUR 3.30078", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 83151493, "accountId": 181258, "listingMapId": 480137, "reservationId": 58720999, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 67, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-05-03 23:59:04", "updatedOn": "2026-05-03 23:59:04"}, {"id": 83151494, "accountId": 181258, "listingMapId": 480137, "reservationId": 58720999, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 14.4, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-05-03 23:59:04", "updatedOn": "2026-05-03 23:59:04"}, {"id": 83151495, "accountId": 181258, "listingMapId": 480137, "reservationId": 58720999, "name": "taxe de séjour", "feeType": "guest", "externalReservationUnitId": null, "amount": 10.37, "currency": "EUR", "percentage": 7.2, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-05-03 23:59:04", "updatedOn": "2026-05-03 23:59:04"}, {"id": 83151496</t>
+          <t>{"id": 64003964, "listingMapId": 493047, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6284000380", "hostawayReservationId": "64003964", "channelReservationId": "6284000380", "externalPropertyId": "15480052", "externalUnitId": "1548005201", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "pvOJl7Y0", "guestPortalUrl": "https://guest-portal.hostaway.com/64003964/pvOJl7Y0", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-08-02 20:27:21", "pendingExpireDate": null, "guestName": "Cedric GUJDA", "guestFirstName": "Cedric", "guestLastName": "GUJDA", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "FR", "guestEmail": "cgujda.163576@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 2, "adults": 1, "children": 1, "infants": null, "pets": null, "arrivalDate": "2026-12-16", "departureDate": "2026-12-27", "isDatesUnspecified": 0, "previousArrivalDate": "2026-12-16", "previousDepartureDate": "2026-12-28", "checkInTime": 16, "checkOutTime": 11, "nights": 11, "phone": "+33749212634", "totalPrice": 437.65, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 72.26, "hostawayCommissionAmount": null, "cleaningFee": 40, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "modified", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\n\nBOOKING NOTE : Payment charge is EUR 6.4148", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": "38", "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": {"name": null, "channelId": 2005, "channelSpecificCode": "38", "longTerm": false, "cancellationPolicyItem": [{"refundAmount": 100, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": -90000, "event": "arrival"}, {"refundAmount": 0, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": 0, "event": "arrival"}]}, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 91600510, "accountId": 181258, "listingMapId": 493047, "reservationId": 64003964, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 40, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-08-03 18:01:15", "updatedOn": "2026-08-03 18:01:15"}, {"id": 91600511, "accountId": 181258, "listingMapId": 493047, "reservationId": 64003964, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 35, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerP</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-06-08T11:43:17+00:00</t>
+          <t>2026-08-17T05:25:05+00:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2f46dd1900cb2584</t>
+          <t>58a081f3ab641a22</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>59144154</v>
+        <v>63847012</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{"id": 59144154, "listingMapId": 480139, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6057496813", "hostawayReservationId": "59144154", "channelReservationId": "6057496813", "externalPropertyId": "15499360", "externalUnitId": "1549936001", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "c82qy9Vz", "guestPortalUrl": "https://guest-portal.hostaway.com/59144154/c82qy9Vz", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-05-12 05:50:37", "pendingExpireDate": null, "guestName": "Leyla Oualichane", "guestFirstName": "Leyla", "guestLastName": "Oualichane", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "FR", "guestEmail": "louali.122874@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 6, "adults": 1, "children": 5, "infants": null, "pets": null, "arrivalDate": "2026-05-22", "departureDate": "2026-05-25", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 3, "phone": "+33773681838", "totalPrice": 317.94, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 53.57, "hostawayCommissionAmount": null, "cleaningFee": 55, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nReservation has a cancellation grace period. Do not charge if cancelled before 2026-05-13 07:50:37\nBOOKING NOTE : Payment charge is EUR 4.4114", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "There is no meal option with this room.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 83854533, "accountId": 181258, "listingMapId": 480139, "reservationId": 59144154, "name": "Cleaning fee", "feeType": "guest", "externalReservationUnitId": null, "amount": 55, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-05-12 05:52:05", "updatedOn": "2026-05-12 05:52:05"}, {"id": 83854534, "accountId": 181258, "listingMapId": 480139, "reservationId": 59144154, "name": "VAT", "feeType": "guest", "externalReservationUnitId": null, "amount": 23.65, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-05-12 05:52:05", "updatedOn": "2026-05-12 05:52:05"}, {"id": 83854535, "accountId": 181258, "listingMapId": 480139, "reservationId": 59144154, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 2.84, "currency": "EUR", "percentage": 7.21, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "inserte</t>
+          <t>{"id": 63847012, "listingMapId": 493047, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6800562532", "hostawayReservationId": "63847012", "channelReservationId": "6800562532", "externalPropertyId": "15480052", "externalUnitId": "1548005201", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "AJx5pahz", "guestPortalUrl": "https://guest-portal.hostaway.com/63847012/AJx5pahz", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-07-30 12:34:58", "pendingExpireDate": null, "guestName": "Samirdine MADI", "guestFirstName": "Samirdine", "guestLastName": "MADI", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "FR", "guestEmail": "smadi.241630@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 2, "adults": 2, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-08-01", "departureDate": "2026-08-19", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 18, "phone": "+262262693325216", "totalPrice": 712.89, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 114.16, "hostawayCommissionAmount": null, "cleaningFee": 40, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nBOOKING NOTE : Payment charge is EUR 9.9804292", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": "38", "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": {"name": null, "channelId": 2005, "channelSpecificCode": "38", "longTerm": false, "cancellationPolicyItem": [{"refundAmount": 100, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": -93600, "event": "arrival"}, {"refundAmount": 0, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": 0, "event": "arrival"}]}, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 91222612, "accountId": 181258, "listingMapId": 493047, "reservationId": 63847012, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 40, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-07-30 12:36:24", "updatedOn": "2026-07-30 12:36:24"}, {"id": 91222613, "accountId": 181258, "listingMapId": 493047, "reservationId": 63847012, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 57.41, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson"</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-06-08T11:43:18+00:00</t>
+          <t>2026-08-17T05:25:06+00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>74b220848c2d3c4f</t>
+          <t>1478cc38991e6c3d</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>59896419</v>
+        <v>61381400</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{"id": 59896419, "listingMapId": 493047, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5465637304", "hostawayReservationId": "59896419", "channelReservationId": "5465637304", "externalPropertyId": "15480052", "externalUnitId": "1548005201", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "Kpbawjz1", "guestPortalUrl": "https://guest-portal.hostaway.com/59896419/Kpbawjz1", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-05-24 18:15:22", "pendingExpireDate": null, "guestName": "SAHAR ECHAJEI", "guestFirstName": "SAHAR", "guestLastName": "ECHAJEI", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": "", "guestCountry": "MA", "guestEmail": "sechaj.919813@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 1, "adults": 1, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-09-03", "departureDate": "2026-09-14", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 11, "phone": "+212700081243", "totalPrice": 522.7, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 83.82, "hostawayCommissionAmount": null, "cleaningFee": 40, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nBOOKING NOTE : Payment charge is EUR 6.9027", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 84973280, "accountId": 181258, "listingMapId": 493047, "reservationId": 59896419, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 40, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-05-24 18:16:57", "updatedOn": "2026-05-24 18:16:57"}, {"id": 84973281, "accountId": 181258, "listingMapId": 493047, "reservationId": 59896419, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 41.19, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-05-24 18:16:57", "updatedOn": "2026-05-24 18:16:57"}, {"id": 84973282, "accountId": 181258, "listingMapId": 493047, "reservationId": 59896419, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 29.65, "currency": "EUR", "percentage": 7.2, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-05-24 18:16:57", "updatedOn": "2026-05-24 18:16:57"}, {"id": 84973283</t>
+          <t>{"id": 61381400, "listingMapId": 480137, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6701344578", "hostawayReservationId": "61381400", "channelReservationId": "6701344578", "externalPropertyId": "15950709", "externalUnitId": "1595070901", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "ONqjVXJS", "guestPortalUrl": "https://guest-portal.hostaway.com/61381400/ONqjVXJS", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-06-23 14:58:43", "pendingExpireDate": null, "guestName": "Thorsten Mall", "guestFirstName": "Thorsten", "guestLastName": "Mall", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "DE", "guestEmail": "tmall.529234@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 2, "adults": 2, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-07-26", "departureDate": "2026-08-01", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 6, "phone": "+491716574261", "totalPrice": 590.56, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 94.93, "hostawayCommissionAmount": null, "cleaningFee": 67, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\n\nBOOKING NOTE : Payment charge is EUR 8.26784", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": "16", "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": {"name": "Moderate", "channelId": 2005, "channelSpecificCode": "16", "longTerm": false, "cancellationPolicyItem": [{"refundAmount": 100, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": -432000, "event": "arrival"}]}, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 87635283, "accountId": 181258, "listingMapId": 480137, "reservationId": 61381400, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 67, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-06-23 14:59:59", "updatedOn": "2026-06-23 14:59:59"}, {"id": 87635284, "accountId": 181258, "listingMapId": 480137, "reservationId": 61381400, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 44.67, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-06-23 14:59:59", "updatedOn": "2026-06-23 14:59:59"}, {"id": 87635285, "</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-06-08T11:43:19+00:00</t>
+          <t>2026-08-17T05:25:08+00:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>326350c60bc74917</t>
+          <t>693c04847f73d3ff</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>55377361</v>
+        <v>63842084</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{"id": 55377361, "listingMapId": 493047, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5381723020", "hostawayReservationId": "55377361", "channelReservationId": "5381723020", "externalPropertyId": "15480052", "externalUnitId": "1548005201", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "ztYU8i_E", "guestPortalUrl": "https://guest-portal.hostaway.com/55377361/ztYU8i_E", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 1, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-02-11 22:12:29", "pendingExpireDate": null, "guestName": "Rosa Goldie", "guestFirstName": "Rosa", "guestLastName": "Goldie", "guestExternalAccountId": null, "guestZipCode": "049712", "guestAddress": "30 08 Prudential Tower, 19 Cecil St", "guestCity": "bangkok", "guestCountry": "GB", "guestEmail": "rgoldi.406294@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 2, "adults": 2, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-05-18", "departureDate": "2026-05-22", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 4, "phone": "+442035640799", "totalPrice": 136.66, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": null, "hostawayCommissionAmount": null, "cleaningFee": null, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": null, "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 76637488, "accountId": 181258, "listingMapId": 493047, "reservationId": 55377361, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 40, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-02 23:58:26", "updatedOn": "2026-03-02 23:58:26"}, {"id": 76637489, "accountId": 181258, "listingMapId": 493047, "reservationId": 55377361, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 8.25, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-02 23:58:26", "updatedOn": "2026-03-02 23:58:26"}, {"id": 76637490, "accountId": 181258, "listingMapId": 493047, "reservationId": 55377361, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 5.94, "currency": "EUR", "percentage": 7.2, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-02 23:58:26", "updatedOn": "2026-03-02 23:58:26"}, {"id": 76637491, "accountId": 181258, "listingMapId": 4</t>
+          <t>{"id": 63842084, "listingMapId": 493047, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5773125178", "hostawayReservationId": "63842084", "channelReservationId": "5773125178", "externalPropertyId": "15480052", "externalUnitId": "1548005201", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "JYtzcZqJ", "guestPortalUrl": "https://guest-portal.hostaway.com/63842084/JYtzcZqJ", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-07-30 09:37:44", "pendingExpireDate": null, "guestName": "Yuliya Gritsevich", "guestFirstName": "Yuliya", "guestLastName": "Gritsevich", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "KZ", "guestEmail": "ygrits.474325@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 1, "adults": 1, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-09-15", "departureDate": "2026-09-25", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 10, "phone": "+77474053035", "totalPrice": 471.99, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 75.73, "hostawayCommissionAmount": null, "cleaningFee": 40, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nBOOKING NOTE : Payment charge is EUR 6.2363", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": "38", "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": {"name": null, "channelId": 2005, "channelSpecificCode": "38", "longTerm": false, "cancellationPolicyItem": [{"refundAmount": 100, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": -93600, "event": "arrival"}, {"refundAmount": 0, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": 0, "event": "arrival"}]}, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 91206888, "accountId": 181258, "listingMapId": 493047, "reservationId": 63842084, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 40, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-07-30 09:39:03", "updatedOn": "2026-07-30 09:39:03"}, {"id": 91206889, "accountId": 181258, "listingMapId": 493047, "reservationId": 63842084, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 36.86, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson":</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-06-08T11:43:20+00:00</t>
+          <t>2026-08-17T05:25:09+00:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ec83dca0dc86e082</t>
+          <t>c209bbb980178745</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>59747975</v>
+        <v>63473517</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{"id": 59747975, "listingMapId": 480137, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5962998458", "hostawayReservationId": "59747975", "channelReservationId": "5962998458", "externalPropertyId": "15950709", "externalUnitId": "1595070901", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "h1WagxBg", "guestPortalUrl": "https://guest-portal.hostaway.com/59747975/h1WagxBg", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-05-21 09:49:21", "pendingExpireDate": null, "guestName": "Saad MESLI", "guestFirstName": "Saad", "guestLastName": "MESLI", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "DZ", "guestEmail": "smesli.652699@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 5, "adults": 2, "children": 3, "infants": null, "pets": null, "arrivalDate": "2026-08-01", "departureDate": "2026-08-20", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 19, "phone": "+213773145710", "totalPrice": 1751.58, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 290.46, "hostawayCommissionAmount": null, "cleaningFee": 67, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\n\nBOOKING NOTE : Payment charge is EUR 24.52212", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 84697043, "accountId": 181258, "listingMapId": 480137, "reservationId": 59747975, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 67, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-05-21 09:51:10", "updatedOn": "2026-05-21 09:51:10"}, {"id": 84697044, "accountId": 181258, "listingMapId": 480137, "reservationId": 59747975, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 149.24, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-05-21 09:51:10", "updatedOn": "2026-05-21 09:51:10"}, {"id": 84697046, "accountId": 181258, "listingMapId": 480137, "reservationId": 59747975, "name": "taxe de séjour", "feeType": "guest", "externalReservationUnitId": null, "amount": 42.98, "currency": "EUR", "percentage": 7.2, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-05-21 09:51:10", "updatedOn": "2026-05-21 09:51:10"}, {"id": 84697048, "accoun</t>
+          <t>{"id": 63473517, "listingMapId": 480140, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5782622310", "hostawayReservationId": "63473517", "channelReservationId": "5782622310", "externalPropertyId": "15500360", "externalUnitId": "1550036001", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "5Pc34zus", "guestPortalUrl": "https://guest-portal.hostaway.com/63473517/5Pc34zus", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-07-25 17:35:05", "pendingExpireDate": null, "guestName": "Gerard Amoros", "guestFirstName": "Gerard", "guestLastName": "Amoros", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "ES", "guestEmail": "gamoro.323966@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 6, "adults": 2, "children": 4, "infants": null, "pets": null, "arrivalDate": "2026-07-26", "departureDate": "2026-07-28", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 2, "phone": "+34675210024", "totalPrice": 213.08, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 35.65, "hostawayCommissionAmount": null, "cleaningFee": 55, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nYou have a booker that would like free parking. (based on availability)\nBOOKING NOTE : Payment charge is EUR 2.9358", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "There is no meal option with this room.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": "1", "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": {"name": null, "channelId": 2005, "channelSpecificCode": "1", "longTerm": false, "cancellationPolicyItem": [{"refundAmount": 0, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": 0, "event": "arrival"}]}, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 90743867, "accountId": 181258, "listingMapId": 480140, "reservationId": 63473517, "name": "Cleaning fee", "feeType": "guest", "externalReservationUnitId": null, "amount": 55, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-07-25 17:36:24", "updatedOn": "2026-07-25 17:36:24"}, {"id": 90743868, "accountId": 181258, "listingMapId": 480140, "reservationId": 63473517, "name": "VAT", "feeType": "guest", "externalReservationUnitId": null, "amount": 14.06, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-07-25 17:36:25", "updatedOn": "2026-07-25 1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-06-08T11:43:21+00:00</t>
+          <t>2026-08-17T05:25:10+00:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>5c5357bc05c7abf5</t>
+          <t>719785ed5402df7c</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>59259973</v>
+        <v>62361211</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{"id": 59259973, "listingMapId": 480137, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5401750056", "hostawayReservationId": "59259973", "channelReservationId": "5401750056", "externalPropertyId": "15950709", "externalUnitId": "1595070901", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "MrSbsffa", "guestPortalUrl": "https://guest-portal.hostaway.com/59259973/MrSbsffa", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-05-14 13:55:33", "pendingExpireDate": null, "guestName": "Barraud Arthur", "guestFirstName": "Barraud", "guestLastName": "Arthur", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": "", "guestCountry": "FR", "guestEmail": "barthu.283998@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 2, "adults": 2, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-05-17", "departureDate": "2026-05-21", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 4, "phone": "+33780408841", "totalPrice": 332.62, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 53.77, "hostawayCommissionAmount": null, "cleaningFee": 67, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nJe voyage pour affaires et il est possible que j'utilise la carte de crédit de ma société.\nCe client souhaiterait avoir une facture pour son séjour.\n\nApproximate time of arrival: between 17:00 and 18:00\nBOOKING NOTE : Payment charge is EUR 4.65668", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 84084097, "accountId": 181258, "listingMapId": 480137, "reservationId": 59259973, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 67, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-05-14 14:00:40", "updatedOn": "2026-05-14 14:00:40"}, {"id": 84084098, "accountId": 181258, "listingMapId": 480137, "reservationId": 59259973, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 22.66, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-05-14 14:00:40", "updatedOn": "2026-05-14 14:00:40"}, {"id": 84084099, "accountId": 181258, "listingMapId": 480137, "reservationId": 59259973, "name": "taxe de séjour", "feeType": "guest", "externalReservationUnitId": null, "amount": 16.</t>
+          <t>{"id": 62361211, "listingMapId": 480140, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6156585573", "hostawayReservationId": "62361211", "channelReservationId": "6156585573", "externalPropertyId": "15500360", "externalUnitId": "1550036001", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "CXYY10Io", "guestPortalUrl": "https://guest-portal.hostaway.com/62361211/CXYY10Io", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-07-02 17:17:41", "pendingExpireDate": null, "guestName": "M Carmen Delgado Quero", "guestFirstName": "M", "guestLastName": "Carmen Delgado Quero", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": "", "guestCountry": "ES", "guestEmail": "mquero.601021@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 4, "adults": 4, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-07-24", "departureDate": "2026-07-26", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 2, "phone": null, "totalPrice": 219.83, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 35.65, "hostawayCommissionAmount": null, "cleaningFee": 55, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nReservation has a cancellation grace period. Do not charge if cancelled before 2026-07-03 19:17:41\nBOOKING NOTE : Payment charge is EUR 2.9358", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "There is no meal option with this room.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": "1", "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": {"name": null, "channelId": 2005, "channelSpecificCode": "1", "longTerm": false, "cancellationPolicyItem": [{"refundAmount": 100, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": -1752139, "event": "arrival"}, {"refundAmount": 0, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": 0, "event": "arrival"}]}, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 88465650, "accountId": 181258, "listingMapId": 480140, "reservationId": 62361211, "name": "Cleaning fee", "feeType": "guest", "externalReservationUnitId": null, "amount": 55, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-07-02 17:19:20", "updatedOn": "2026-07-02 17:19:20"}, {"id": 88465651, "accountId": 181258, "listingMapId": 480140, "reservationId": 62361211, "name": "VAT", "feeType": "guest", "externalReservationUnitId": null, "amount": 14.06, "currency</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-06-08T11:43:22+00:00</t>
+          <t>2026-08-17T05:25:10+00:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>40b62416f7081c19</t>
+          <t>0a9b8a1964f4ffb2</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>59544415</v>
+        <v>63211235</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{"id": 59544415, "listingMapId": 480139, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6496345089", "hostawayReservationId": "59544415", "channelReservationId": "6496345089", "externalPropertyId": "15499360", "externalUnitId": "1549936001", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "tOJ0MpZN", "guestPortalUrl": "https://guest-portal.hostaway.com/59544415/tOJ0MpZN", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-05-17 09:43:29", "pendingExpireDate": null, "guestName": "Olteanuu ELENA", "guestFirstName": "Olteanuu", "guestLastName": "ELENA", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "FR", "guestEmail": "oelena.333989@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 2, "adults": 2, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-05-17", "departureDate": "2026-05-19", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 2, "phone": "+393895344387", "totalPrice": 182.15, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 29.64, "hostawayCommissionAmount": null, "cleaningFee": 55, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\n\nBOOKING NOTE : Payment charge is EUR 2.44076", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "There is no meal option with this room.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 84328836, "accountId": 181258, "listingMapId": 480139, "reservationId": 59544415, "name": "Cleaning fee", "feeType": "guest", "externalReservationUnitId": null, "amount": 55, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-05-17 09:44:50", "updatedOn": "2026-05-17 09:44:50"}, {"id": 84328837, "accountId": 181258, "listingMapId": 480139, "reservationId": 59544415, "name": "VAT", "feeType": "guest", "externalReservationUnitId": null, "amount": 10.85, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-05-17 09:44:50", "updatedOn": "2026-05-17 09:44:50"}, {"id": 84328838, "accountId": 181258, "listingMapId": 480139, "reservationId": 59544415, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 7.81, "currency": "EUR", "percentage": 7.2, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-05-17 09:44:50", "updatedOn": "2026-05-17 09:44:50"}, {"id": 84328839, "accountId": 18</t>
+          <t>{"id": 63211235, "listingMapId": 480137, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6438445508", "hostawayReservationId": "63211235", "channelReservationId": "6438445508", "externalPropertyId": "15950709", "externalUnitId": "1595070901", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "Aqsbh-0L", "guestPortalUrl": "https://guest-portal.hostaway.com/63211235/Aqsbh-0L", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-07-20 13:59:17", "pendingExpireDate": null, "guestName": "David Vu", "guestFirstName": "David", "guestLastName": "Vu", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": "", "guestCountry": "FR", "guestEmail": "dvu.327459@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 5, "adults": 5, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-07-24", "departureDate": "2026-07-26", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 2, "phone": "+33777721960", "totalPrice": 200.29, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 32.66, "hostawayCommissionAmount": null, "cleaningFee": 67, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nBOOKING NOTE : Payment charge is EUR 2.80406\nbesoin de place de parking", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": "38", "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": {"name": null, "channelId": 2005, "channelSpecificCode": "38", "longTerm": false, "cancellationPolicyItem": [{"refundAmount": 100, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": -93600, "event": "arrival"}, {"refundAmount": 0, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": 0, "event": "arrival"}]}, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 90238868, "accountId": 181258, "listingMapId": 480137, "reservationId": 63211235, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 67, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-07-20 14:03:39", "updatedOn": "2026-07-20 14:03:39"}, {"id": 90238869, "accountId": 181258, "listingMapId": 480137, "reservationId": 63211235, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 11.37, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPe</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-06-08T11:43:23+00:00</t>
+          <t>2026-08-17T05:25:11+00:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>bbd03b1f0e834b21</t>
+          <t>4ea1ce3358395218</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>59599320</v>
+        <v>63474611</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{"id": 59599320, "listingMapId": 493047, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6920404227", "hostawayReservationId": "59599320", "channelReservationId": "6920404227", "externalPropertyId": "15480052", "externalUnitId": "1548005201", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "gQ1LWbUO", "guestPortalUrl": "https://guest-portal.hostaway.com/59599320/gQ1LWbUO", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-05-18 14:26:21", "pendingExpireDate": null, "guestName": "Joan Jordan Tejedor", "guestFirstName": "Joan", "guestLastName": "Jordan Tejedor", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "ES", "guestEmail": "jtejed.761022@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 1, "adults": 1, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-06-13", "departureDate": "2026-06-15", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 2, "phone": "+34630393387", "totalPrice": 124.22, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 20.24, "hostawayCommissionAmount": null, "cleaningFee": 40, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nBOOKING NOTE : Payment charge is EUR 1.6667", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 84444903, "accountId": 181258, "listingMapId": 493047, "reservationId": 59599320, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 40, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-05-18 14:29:13", "updatedOn": "2026-05-18 14:29:13"}, {"id": 84444904, "accountId": 181258, "listingMapId": 493047, "reservationId": 59599320, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 7.19, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-05-18 14:29:13", "updatedOn": "2026-05-18 14:29:13"}, {"id": 84444905, "accountId": 181258, "listingMapId": 493047, "reservationId": 59599320, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 5.17, "currency": "EUR", "percentage": 7.19, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-05-18 14:29:13", "updatedOn": "2026-05-18 14:29:13"}, {"id</t>
+          <t xml:space="preserve">{"id": 63474611, "listingMapId": 480139, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5473820925", "hostawayReservationId": "63474611", "channelReservationId": "5473820925", "externalPropertyId": "15499360", "externalUnitId": "1549936001", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "STuhdXGi", "guestPortalUrl": "https://guest-portal.hostaway.com/63474611/STuhdXGi", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-07-25 18:05:34", "pendingExpireDate": null, "guestName": "Maria Neus Bonet Estrany", "guestFirstName": "Maria", "guestLastName": "Neus Bonet Estrany", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "ES", "guestEmail": "mestra.168781@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 4, "adults": 4, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-10-08", "departureDate": "2026-10-13", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 5, "phone": null, "totalPrice": 475, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 76.36, "hostawayCommissionAmount": null, "cleaningFee": 55, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\n\nBOOKING NOTE : Payment charge is EUR 6.2888", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "There is no meal option with this room.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": "37", "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": {"name": null, "channelId": 2005, "channelSpecificCode": "37", "longTerm": false, "cancellationPolicyItem": [{"refundAmount": 100, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": -612000, "event": "arrival"}, {"refundAmount": 80, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": 0, "event": "arrival"}]}, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 90746495, "accountId": 181258, "listingMapId": 480139, "reservationId": 63474611, "name": "Cleaning fee", "feeType": "guest", "externalReservationUnitId": null, "amount": 55, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-07-25 18:08:25", "updatedOn": "2026-07-25 18:08:25"}, {"id": 90746496, "accountId": 181258, "listingMapId": 480139, "reservationId": 63474611, "name": "VAT", "feeType": "guest", "externalReservationUnitId": null, "amount": 35.84, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": </t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-06-08T11:43:23+00:00</t>
+          <t>2026-08-17T05:25:12+00:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>c63a8fcad76c1d54</t>
+          <t>bfabf9134ad68bae</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>57849428</v>
+        <v>63418354</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{"id": 57849428, "listingMapId": 480137, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6714515940", "hostawayReservationId": "57849428", "channelReservationId": "6714515940", "externalPropertyId": "15950709", "externalUnitId": "1595070901", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "NqEf5vmy", "guestPortalUrl": "https://guest-portal.hostaway.com/57849428/NqEf5vmy", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-04-17 13:05:14", "pendingExpireDate": null, "guestName": "Lydie FAUVEL", "guestFirstName": "Lydie", "guestLastName": "FAUVEL", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": "", "guestCountry": "FR", "guestEmail": "lfauve.203970@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 2, "adults": 2, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-06-16", "departureDate": "2026-06-19", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 3, "phone": "+3350021858", "totalPrice": 347.96, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 56.22, "hostawayCommissionAmount": null, "cleaningFee": 67, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nBOOKING NOTE : Payment charge is EUR 4.87144", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 81765458, "accountId": 181258, "listingMapId": 480137, "reservationId": 57849428, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 67, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-17 13:06:39", "updatedOn": "2026-04-17 13:06:39"}, {"id": 81765459, "accountId": 181258, "listingMapId": 480137, "reservationId": 57849428, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 23.97, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-17 13:06:39", "updatedOn": "2026-04-17 13:06:39"}, {"id": 81765460, "accountId": 181258, "listingMapId": 480137, "reservationId": 57849428, "name": "taxe de séjour", "feeType": "guest", "externalReservationUnitId": null, "amount": 17.26, "currency": "EUR", "percentage": 7.2, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-17 13:06:39", "updatedOn": "2026-04-17 13:06:39"}, {"id": 81765461, "accountId</t>
+          <t>{"id": 63418354, "listingMapId": 480140, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6244518323", "hostawayReservationId": "63418354", "channelReservationId": "6244518323", "externalPropertyId": "15500360", "externalUnitId": "1550036001", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "tNWOi448", "guestPortalUrl": "https://guest-portal.hostaway.com/63418354/tNWOi448", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-07-24 12:02:11", "pendingExpireDate": null, "guestName": "HAROLD AMALER JEANNINE HECKMANN ALEXANDRA AMALER", "guestFirstName": "HAROLD", "guestLastName": "AMALER JEANNINE HECKMANN ALEXANDRA AMALER", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": "", "guestCountry": "ZA", "guestEmail": "hamale.466878@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 3, "adults": 3, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-09-30", "departureDate": "2026-10-04", "isDatesUnspecified": 0, "previousArrivalDate": "2026-10-01", "previousDepartureDate": "2026-10-04", "checkInTime": 16, "checkOutTime": 11, "nights": 4, "phone": null, "totalPrice": 546.17, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 87.72, "hostawayCommissionAmount": null, "cleaningFee": 55, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "modified", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nBOOKING NOTE : Payment charge is EUR 5.642", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "There is no meal option with this room.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": "37", "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": {"name": null, "channelId": 2005, "channelSpecificCode": "37", "longTerm": false, "cancellationPolicyItem": [{"refundAmount": 100, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": -612000, "event": "arrival"}, {"refundAmount": 67, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": 0, "event": "arrival"}]}, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 90626920, "accountId": 181258, "listingMapId": 480140, "reservationId": 63418354, "name": "Cleaning fee", "feeType": "guest", "externalReservationUnitId": null, "amount": 55, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-07-24 12:20:15", "updatedOn": "2026-07-24 12:20:15"}, {"id": 90626921, "accountId": 181258, "listingMapId": 480140, "reservationId": 63418354, "name": "VAT", "feeType": "guest", "externalReservationUnitId": null, "amount": 41.91, "currency": "EUR", "percentage": 10</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-06-08T11:43:24+00:00</t>
+          <t>2026-08-17T05:25:13+00:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>b3044f913a497e92</t>
+          <t>4c09e9cb933d9e0a</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>58169437</v>
+        <v>59274706</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{"id": 58169437, "listingMapId": 480137, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6927414258", "hostawayReservationId": "58169437", "channelReservationId": "6927414258", "externalPropertyId": "15950709", "externalUnitId": "1595070901", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "l0wbpCDh", "guestPortalUrl": "https://guest-portal.hostaway.com/58169437/l0wbpCDh", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-04-22 10:37:47", "pendingExpireDate": null, "guestName": "Gwen Gwen", "guestFirstName": "Gwen", "guestLastName": "Gwen", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": "", "guestCountry": "FR", "guestEmail": "ggwen.980317@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 5, "adults": 2, "children": 3, "infants": null, "pets": null, "arrivalDate": "2026-05-14", "departureDate": "2026-05-17", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 3, "phone": "+33664108642", "totalPrice": 320.98, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 53.47, "hostawayCommissionAmount": null, "cleaningFee": 67, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nBOOKING NOTE : Payment charge is EUR 4.49372\nApproximate time of arrival: between 10:00 and 11:00", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 82183968, "accountId": 181258, "listingMapId": 480137, "reservationId": 58169437, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 67, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-22 10:39:38", "updatedOn": "2026-04-22 10:39:38"}, {"id": 82183969, "accountId": 181258, "listingMapId": 480137, "reservationId": 58169437, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 22.5, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-22 10:39:38", "updatedOn": "2026-04-22 10:39:38"}, {"id": 82183970, "accountId": 181258, "listingMapId": 480137, "reservationId": 58169437, "name": "taxe de séjour", "feeType": "guest", "externalReservationUnitId": null, "amount": 6.48, "currency": "EUR", "percentage": 7.2, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-22 10:39:38", "updatedOn": "2026-04</t>
+          <t>{"id": 59274706, "listingMapId": 480140, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5216606520", "hostawayReservationId": "59274706", "channelReservationId": "5216606520", "externalPropertyId": "15500360", "externalUnitId": "1550036001", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "qp5_LJfT", "guestPortalUrl": "https://guest-portal.hostaway.com/59274706/qp5_LJfT", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-05-14 18:36:39", "pendingExpireDate": null, "guestName": "Jerome BRIZARD", "guestFirstName": "Jerome", "guestLastName": "BRIZARD", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": "", "guestCountry": "FR", "guestEmail": "jbriza.397505@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 4, "adults": 4, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-07-20", "departureDate": "2026-07-24", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 4, "phone": "+33683849451", "totalPrice": 442.61, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 71.2, "hostawayCommissionAmount": null, "cleaningFee": 55, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\n\nBOOKING NOTE : Payment charge is EUR 5.8632", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "There is no meal option with this room.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": "16", "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": {"name": "Moderate", "channelId": 2005, "channelSpecificCode": "16", "longTerm": false, "cancellationPolicyItem": [{"refundAmount": 100, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": -432000, "event": "arrival"}]}, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 84106861, "accountId": 181258, "listingMapId": 480140, "reservationId": 59274706, "name": "Cleaning fee", "feeType": "guest", "externalReservationUnitId": null, "amount": 55, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-05-14 18:38:16", "updatedOn": "2026-05-14 18:38:16"}, {"id": 84106862, "accountId": 181258, "listingMapId": 480140, "reservationId": 59274706, "name": "VAT", "feeType": "guest", "externalReservationUnitId": null, "amount": 33.07, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-05-14 18:38:16", "updatedOn": "2026-05-14 18:38:16"}, {"id": 84106863, "accountId": 181258, "li</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-06-08T11:43:25+00:00</t>
+          <t>2026-08-17T05:25:14+00:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>17f315d38a1a5c18</t>
+          <t>8ae9fa0df77697b2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>59228822</v>
+        <v>63133336</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{"id": 59228822, "listingMapId": 493047, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5166918968", "hostawayReservationId": "59228822", "channelReservationId": "5166918968", "externalPropertyId": "15480052", "externalUnitId": "1548005201", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "TUPVuiZ1", "guestPortalUrl": "https://guest-portal.hostaway.com/59228822/TUPVuiZ1", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-05-13 21:18:55", "pendingExpireDate": null, "guestName": "Amadou Kane", "guestFirstName": "Amadou", "guestLastName": "Kane", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "FR", "guestEmail": "akane.595278@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 2, "adults": 2, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-05-14", "departureDate": "2026-05-17", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 3, "phone": "+33783712651", "totalPrice": 145.96, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 23.71, "hostawayCommissionAmount": null, "cleaningFee": 40, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\n\nBOOKING NOTE : Payment charge is EUR 1.9523", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 84027857, "accountId": 181258, "listingMapId": 493047, "reservationId": 59228822, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 40, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-05-13 21:20:21", "updatedOn": "2026-05-13 21:20:21"}, {"id": 84027858, "accountId": 181258, "listingMapId": 493047, "reservationId": 59228822, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 9.04, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-05-13 21:20:21", "updatedOn": "2026-05-13 21:20:21"}, {"id": 84027859, "accountId": 181258, "listingMapId": 493047, "reservationId": 59228822, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 6.51, "currency": "EUR", "percentage": 7.2, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-05-13 21:20:21", "updatedOn": "2026-05-13 21:20:21"}, {"id": 84027860, "ac</t>
+          <t>{"id": 63133336, "listingMapId": 493047, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6917036968", "hostawayReservationId": "63133336", "channelReservationId": "6917036968", "externalPropertyId": "15480052", "externalUnitId": "1548005201", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "vM56GRIk", "guestPortalUrl": "https://guest-portal.hostaway.com/63133336/vM56GRIk", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-07-18 17:47:04", "pendingExpireDate": null, "guestName": "Helena Goncalves", "guestFirstName": "Helena", "guestLastName": "Goncalves", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "FR", "guestEmail": "hgonca.825030@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 1, "adults": 1, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-07-18", "departureDate": "2026-07-23", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 5, "phone": "+33782297497", "totalPrice": 216.6, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 34.98, "hostawayCommissionAmount": null, "cleaningFee": 40, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\n\nBOOKING NOTE : Payment charge is EUR 2.8805", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": "38", "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": {"name": null, "channelId": 2005, "channelSpecificCode": "38", "longTerm": false, "cancellationPolicyItem": [{"refundAmount": 0, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": 0, "event": "arrival"}]}, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 90064261, "accountId": 181258, "listingMapId": 493047, "reservationId": 63133336, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 40, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-07-18 17:51:52", "updatedOn": "2026-07-18 17:51:52"}, {"id": 90064262, "accountId": 181258, "listingMapId": 493047, "reservationId": 63133336, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 15.07, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-07-18 17:51:52", "updatedOn": "2026-07-18 17:51:52"}, {"id": 90064263, "accountId"</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-06-08T11:43:26+00:00</t>
+          <t>2026-08-17T05:25:15+00:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>3fa3be538da5ac11</t>
+          <t>8f37259eb77fe5e0</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>58503136</v>
+        <v>59804583</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{"id": 58503136, "listingMapId": 480139, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5792769705", "hostawayReservationId": "58503136", "channelReservationId": "5792769705", "externalPropertyId": "15499360", "externalUnitId": "1549936001", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "7PFGDvh5", "guestPortalUrl": "https://guest-portal.hostaway.com/58503136/7PFGDvh5", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-04-29 17:42:34", "pendingExpireDate": null, "guestName": "Pereira Ismael", "guestFirstName": "Pereira", "guestLastName": "Ismael", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": "", "guestCountry": "CL", "guestEmail": "pismae.413046@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 6, "adults": 2, "children": 4, "infants": null, "pets": null, "arrivalDate": "2026-05-15", "departureDate": "2026-05-17", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 2, "phone": null, "totalPrice": 232.18, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 38.83, "hostawayCommissionAmount": null, "cleaningFee": 55, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nReservation has a cancellation grace period. Do not charge if cancelled before 2026-04-30 19:42:34\nBOOKING NOTE : Payment charge is EUR 3.1976\nApproximate time of arrival: between 00:00 and 01:00", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "There is no meal option with this room.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 82811710, "accountId": 181258, "listingMapId": 480139, "reservationId": 58503136, "name": "Cleaning fee", "feeType": "guest", "externalReservationUnitId": null, "amount": 55, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-29 17:44:04", "updatedOn": "2026-04-29 17:44:04"}, {"id": 82811711, "accountId": 181258, "listingMapId": 480139, "reservationId": 58503136, "name": "VAT", "feeType": "guest", "externalReservationUnitId": null, "amount": 15.76, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-29 17:44:04", "updatedOn": "2026-04-29 17:44:04"}, {"id": 82811712, "accountId": 181258, "listingMapId": 480139, "reservationId": 58503136, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 3.78, "currency": "EUR", "percentage": 7.19, "isIncluded": 1, "isPerNight": 0, "isP</t>
+          <t>{"id": 59804583, "listingMapId": 493047, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6485129999", "hostawayReservationId": "59804583", "channelReservationId": "6485129999", "externalPropertyId": "15480052", "externalUnitId": "1548005201", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "TfW0bbA3", "guestPortalUrl": "https://guest-portal.hostaway.com/59804583/TfW0bbA3", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-05-22 13:43:17", "pendingExpireDate": null, "guestName": "Helena Goncalves", "guestFirstName": "Helena", "guestLastName": "Goncalves", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "FR", "guestEmail": "hgonca.795365@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 2, "adults": 2, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-05-22", "departureDate": "2026-05-28", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 6, "phone": "+33782297497", "totalPrice": 251.92, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 40.61, "hostawayCommissionAmount": null, "cleaningFee": 40, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\n\nBOOKING NOTE : Payment charge is EUR 3.5268646", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": null, "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 84793966, "accountId": 181258, "listingMapId": 493047, "reservationId": 59804583, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 40, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-05-22 13:44:45", "updatedOn": "2026-05-22 13:44:45"}, {"id": 84793967, "accountId": 181258, "listingMapId": 493047, "reservationId": 59804583, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 18.08, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-05-22 13:44:45", "updatedOn": "2026-05-22 13:44:45"}, {"id": 84793968, "accountId": 181258, "listingMapId": 493047, "reservationId": 59804583, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 13.02, "currency": "EUR", "percentage": 7.2, "isInclud</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-06-08T11:43:27+00:00</t>
+          <t>2026-08-17T05:25:15+00:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>08f28882fbcebee5</t>
+          <t>95a5de6beeccad3f</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>58992171</v>
+        <v>63089745</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{"id": 58992171, "listingMapId": 493047, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5092918242", "hostawayReservationId": "58992171", "channelReservationId": "5092918242", "externalPropertyId": "15480052", "externalUnitId": "1548005201", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "f5w9mPrJ", "guestPortalUrl": "https://guest-portal.hostaway.com/58992171/f5w9mPrJ", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-05-08 18:49:43", "pendingExpireDate": null, "guestName": "Amadou Kane", "guestFirstName": "Amadou", "guestLastName": "Kane", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "FR", "guestEmail": "akane.548585@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 2, "adults": 2, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-05-10", "departureDate": "2026-05-14", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 4, "phone": "+33783712651", "totalPrice": 181.28, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 29.34, "hostawayCommissionAmount": null, "cleaningFee": 40, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nBOOKING NOTE : Payment charge is EUR 2.4164", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 83571710, "accountId": 181258, "listingMapId": 493047, "reservationId": 58992171, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 40, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-05-08 18:51:09", "updatedOn": "2026-05-08 18:51:09"}, {"id": 83571711, "accountId": 181258, "listingMapId": 493047, "reservationId": 58992171, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 12.05, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-05-08 18:51:09", "updatedOn": "2026-05-08 18:51:09"}, {"id": 83571712, "accountId": 181258, "listingMapId": 493047, "reservationId": 58992171, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 8.68, "currency": "EUR", "percentage": 7.2, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-05-08 18:51:09", "updatedOn": "2026-05-08 18:51:09"}, {"id": 83571713, "acc</t>
+          <t>{"id": 63089745, "listingMapId": 480137, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5464610897", "hostawayReservationId": "63089745", "channelReservationId": "5464610897", "externalPropertyId": "15950709", "externalUnitId": "1595070901", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "7r3DjWh3", "guestPortalUrl": "https://guest-portal.hostaway.com/63089745/7r3DjWh3", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-07-17 17:34:13", "pendingExpireDate": null, "guestName": "Louis ORTOLI", "guestFirstName": "Louis", "guestLastName": "ORTOLI", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "FR", "guestEmail": "lortol.551070@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 2, "adults": 2, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-07-20", "departureDate": "2026-07-22", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 2, "phone": "+33647458956", "totalPrice": 199.33, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 32.5, "hostawayCommissionAmount": null, "cleaningFee": 67, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nBOOKING NOTE : Payment charge is EUR 2.79062", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": "38", "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": {"name": null, "channelId": 2005, "channelSpecificCode": "38", "longTerm": false, "cancellationPolicyItem": [{"refundAmount": 100, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": -93600, "event": "arrival"}, {"refundAmount": 0, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": 0, "event": "arrival"}]}, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 89973317, "accountId": 181258, "listingMapId": 480137, "reservationId": 63089745, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 67, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-07-17 17:35:50", "updatedOn": "2026-07-17 17:35:50"}, {"id": 89973318, "accountId": 181258, "listingMapId": 480137, "reservationId": 63089745, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 11.29, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImpo</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-06-08T11:43:28+00:00</t>
+          <t>2026-08-17T05:25:16+00:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>f3f99dc5d0e6cf88</t>
+          <t>1c0d8bdac61db2e1</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>59274706</v>
+        <v>63072098</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{"id": 59274706, "listingMapId": 480140, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5216606520", "hostawayReservationId": "59274706", "channelReservationId": "5216606520", "externalPropertyId": "15500360", "externalUnitId": "1550036001", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "qp5_LJfT", "guestPortalUrl": "https://guest-portal.hostaway.com/59274706/qp5_LJfT", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-05-14 18:36:39", "pendingExpireDate": null, "guestName": "Jerome BRIZARD", "guestFirstName": "Jerome", "guestLastName": "BRIZARD", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": "", "guestCountry": "FR", "guestEmail": "jbriza.397505@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 4, "adults": 4, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-07-20", "departureDate": "2026-07-24", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 4, "phone": "+33683849451", "totalPrice": 442.61, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 71.2, "hostawayCommissionAmount": null, "cleaningFee": 55, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\n\nBOOKING NOTE : Payment charge is EUR 5.8632", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "There is no meal option with this room.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 84106861, "accountId": 181258, "listingMapId": 480140, "reservationId": 59274706, "name": "Cleaning fee", "feeType": "guest", "externalReservationUnitId": null, "amount": 55, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-05-14 18:38:16", "updatedOn": "2026-05-14 18:38:16"}, {"id": 84106862, "accountId": 181258, "listingMapId": 480140, "reservationId": 59274706, "name": "VAT", "feeType": "guest", "externalReservationUnitId": null, "amount": 33.07, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-05-14 18:38:16", "updatedOn": "2026-05-14 18:38:16"}, {"id": 84106863, "accountId": 181258, "listingMapId": 480140, "reservationId": 59274706, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 23.81, "currency": "EUR", "percentage": 7.2, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-05-14 18:38:16", "updatedOn": "2026-05-14 18:38:16"}, {"id": 84106864, "accountId": 18125</t>
+          <t>{"id": 63072098, "listingMapId": 480139, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6986345614", "hostawayReservationId": "63072098", "channelReservationId": "6986345614", "externalPropertyId": "15499360", "externalUnitId": "1549936001", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "0xIa98m3", "guestPortalUrl": "https://guest-portal.hostaway.com/63072098/0xIa98m3", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-07-17 10:15:35", "pendingExpireDate": null, "guestName": "Ana Salvador", "guestFirstName": "Ana", "guestLastName": "Salvador", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": "", "guestCountry": "ES", "guestEmail": "asalva.845566@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 6, "adults": 3, "children": 3, "infants": null, "pets": null, "arrivalDate": "2026-08-24", "departureDate": "2026-08-27", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 3, "phone": null, "totalPrice": 299.91, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 49.67, "hostawayCommissionAmount": null, "cleaningFee": 55, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nApproximate time of arrival: between 16:00 and 17:00\nBOOKING NOTE : Payment charge is EUR 4.0901", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "There is no meal option with this room.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": "60", "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": {"name": null, "channelId": 2005, "channelSpecificCode": "60", "longTerm": false, "cancellationPolicyItem": [{"refundAmount": 100, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": -439200, "event": "arrival"}, {"refundAmount": 67, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": 0, "event": "arrival"}]}, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 89934997, "accountId": 181258, "listingMapId": 480139, "reservationId": 63072098, "name": "Cleaning fee", "feeType": "guest", "externalReservationUnitId": null, "amount": 55, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-07-17 10:18:24", "updatedOn": "2026-07-17 10:18:24"}, {"id": 89934998, "accountId": 181258, "listingMapId": 480139, "reservationId": 63072098, "name": "VAT", "feeType": "guest", "externalReservationUnitId": null, "amount": 21.56, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPe</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-06-08T11:43:31+00:00</t>
+          <t>2026-08-17T05:25:17+00:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>8ae9fa0df77697b2</t>
+          <t>c9878fec1ebdc42a</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>58552963</v>
+        <v>57066128</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{"id": 58552963, "listingMapId": 480137, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5319386045", "hostawayReservationId": "58552963", "channelReservationId": "5319386045", "externalPropertyId": "15950709", "externalUnitId": "1595070901", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "yPeJdRTj", "guestPortalUrl": "https://guest-portal.hostaway.com/58552963/yPeJdRTj", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-04-30 15:27:49", "pendingExpireDate": null, "guestName": "Astrid Demilly", "guestFirstName": "Astrid", "guestLastName": "Demilly", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "FR", "guestEmail": "ademil.297249@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 3, "adults": 2, "children": 1, "infants": null, "pets": null, "arrivalDate": "2026-05-12", "departureDate": "2026-05-14", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 2, "phone": "+33612812077", "totalPrice": 193.8, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 32.05, "hostawayCommissionAmount": null, "cleaningFee": 67, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nReservation has a cancellation grace period. Do not charge if cancelled before 2026-05-01 17:27:49\nBOOKING NOTE : Payment charge is EUR 2.7132", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 82888389, "accountId": 181258, "listingMapId": 480137, "reservationId": 58552963, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 67, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-30 15:29:13", "updatedOn": "2026-04-30 15:29:13"}, {"id": 82888390, "accountId": 181258, "listingMapId": 480137, "reservationId": 58552963, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 11.05, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-30 15:29:13", "updatedOn": "2026-04-30 15:29:13"}, {"id": 82888391, "accountId": 181258, "listingMapId": 480137, "reservationId": 58552963, "name": "taxe de séjour", "feeType": "guest", "externalReservationUnitId": null, "amount": 5.3, "currency": "EUR", "percentage": 7.2, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "i</t>
+          <t>{"id": 57066128, "listingMapId": 480140, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5022726075", "hostawayReservationId": "57066128", "channelReservationId": "5022726075", "externalPropertyId": "15500360", "externalUnitId": "1550036001", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "tjurDQuN", "guestPortalUrl": "https://guest-portal.hostaway.com/57066128/tjurDQuN", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-03-31 03:40:57", "pendingExpireDate": null, "guestName": "Suzy LAROCHELLE", "guestFirstName": "Suzy", "guestLastName": "LAROCHELLE", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": "", "guestCountry": "GP", "guestEmail": "slaroc.136698@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 4, "adults": 4, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-07-08", "departureDate": "2026-07-11", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 3, "phone": "+594694904580", "totalPrice": 365.63, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 58.91, "hostawayCommissionAmount": null, "cleaningFee": 55, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\n\nBOOKING NOTE : Payment charge is EUR 5.1188662", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "There is no meal option with this room.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": "16", "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": {"name": "Moderate", "channelId": 2005, "channelSpecificCode": "16", "longTerm": false, "cancellationPolicyItem": [{"refundAmount": 100, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": -432000, "event": "arrival"}]}, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 79204868, "accountId": 181258, "listingMapId": 480140, "reservationId": 57066128, "name": "Cleaning fee", "feeType": "guest", "externalReservationUnitId": null, "amount": 55, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-31 03:42:24", "updatedOn": "2026-03-31 03:42:24"}, {"id": 79204869, "accountId": 181258, "listingMapId": 480140, "reservationId": 57066128, "name": "VAT", "feeType": "guest", "externalReservationUnitId": null, "amount": 26.5, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-31 03:42:24", "updatedOn": "2026-03-31 03:42:24"}, {"id": 79204870, "accountId": 18125</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-06-08T11:43:32+00:00</t>
+          <t>2026-08-17T05:25:18+00:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>316fce907ed1f461</t>
+          <t>6da2176203049d7b</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>59168803</v>
+        <v>62830785</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{"id": 59168803, "listingMapId": 480137, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5638882353", "hostawayReservationId": "59168803", "channelReservationId": "5638882353", "externalPropertyId": "15950709", "externalUnitId": "1595070901", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "aq7UwuF7", "guestPortalUrl": "https://guest-portal.hostaway.com/59168803/aq7UwuF7", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-05-12 18:24:17", "pendingExpireDate": null, "guestName": "Klara Kuntova", "guestFirstName": "Klara", "guestLastName": "Kuntova", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": "", "guestCountry": "CZ", "guestEmail": "kkunto.706890@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 3, "adults": 2, "children": 1, "infants": null, "pets": null, "arrivalDate": "2026-07-01", "departureDate": "2026-07-04", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 3, "phone": "+420739217002", "totalPrice": 336.57, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 55.3, "hostawayCommissionAmount": null, "cleaningFee": 67, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nBOOKING NOTE : Payment charge is EUR 4.71198\nApproximate time of arrival: between 13:00 and 14:00", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 83910222, "accountId": 181258, "listingMapId": 480137, "reservationId": 59168803, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 67, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-05-12 18:25:44", "updatedOn": "2026-05-12 18:25:44"}, {"id": 83910223, "accountId": 181258, "listingMapId": 480137, "reservationId": 59168803, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 23.48, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-05-12 18:25:44", "updatedOn": "2026-05-12 18:25:44"}, {"id": 83910224, "accountId": 181258, "listingMapId": 480137, "reservationId": 59168803, "name": "taxe de séjour", "feeType": "guest", "externalReservationUnitId": null, "amount": 11.27, "currency": "EUR", "percentage": 7.2, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-05-12 18:25:44", "updatedOn</t>
+          <t xml:space="preserve">{"id": 62830785, "listingMapId": 480137, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6390513837", "hostawayReservationId": "62830785", "channelReservationId": "6390513837", "externalPropertyId": "15950709", "externalUnitId": "1595070901", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "z4DGvtNO", "guestPortalUrl": "https://guest-portal.hostaway.com/62830785/z4DGvtNO", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-07-12 17:00:00", "pendingExpireDate": null, "guestName": "Xavier Chaumette", "guestFirstName": "Xavier", "guestLastName": "Chaumette", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "FR", "guestEmail": "xchaum.902034@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 2, "adults": 2, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-07-13", "departureDate": "2026-07-16", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 3, "phone": "+33631914266", "totalPrice": 265.49, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 43.06, "hostawayCommissionAmount": null, "cleaningFee": 67, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nBOOKING NOTE : Payment charge is EUR 3.71686", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": "1", "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": {"name": null, "channelId": 2005, "channelSpecificCode": "1", "longTerm": false, "cancellationPolicyItem": [{"refundAmount": 0, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": 0, "event": "arrival"}]}, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 89421235, "accountId": 181258, "listingMapId": 480137, "reservationId": 62830785, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 67, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-07-12 17:02:49", "updatedOn": "2026-07-12 17:02:49"}, {"id": 89421236, "accountId": 181258, "listingMapId": 480137, "reservationId": 62830785, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 16.94, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-07-12 17:02:50", "updatedOn": "2026-07-12 17:02:50"}, {"id": 89421237, "accountId": </t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-06-08T11:43:33+00:00</t>
+          <t>2026-08-17T05:25:19+00:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>339f072abf010129</t>
+          <t>0c5fa4ae65f2a76f</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>58442275</v>
+        <v>62879852</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{"id": 58442275, "listingMapId": 480137, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6103870189", "hostawayReservationId": "58442275", "channelReservationId": "6103870189", "externalPropertyId": "15950709", "externalUnitId": "1595070901", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "1cG-SOdQ", "guestPortalUrl": "https://guest-portal.hostaway.com/58442275/1cG-SOdQ", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-04-28 12:08:33", "pendingExpireDate": null, "guestName": "Ihsan Alami Messaoudi", "guestFirstName": "Ihsan", "guestLastName": "Alami Messaoudi", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "MA", "guestEmail": "imessa.543436@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 3, "adults": 1, "children": 2, "infants": null, "pets": null, "arrivalDate": "2026-05-08", "departureDate": "2026-05-12", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 4, "phone": "+212659299684", "totalPrice": 360.36, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 60.2, "hostawayCommissionAmount": null, "cleaningFee": 67, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nReservation has a cancellation grace period. Do not charge if cancelled before 2026-04-29 14:08:33\nBOOKING NOTE : Payment charge is EUR 5.22046", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 82687825, "accountId": 181258, "listingMapId": 480137, "reservationId": 58442275, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 67, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-28 12:09:57", "updatedOn": "2026-04-28 12:09:57"}, {"id": 82687826, "accountId": 181258, "listingMapId": 480137, "reservationId": 58442275, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 26.1, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-28 12:09:57", "updatedOn": "2026-04-28 12:09:57"}, {"id": 82687827, "accountId": 181258, "listingMapId": 480137, "reservationId": 58442275, "name": "taxe de séjour", "feeType": "guest", "externalReservationUnitId": null, "amount": 6.26, "currency": "EUR", "percentage": 7.2, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "is</t>
+          <t>{"id": 62879852, "listingMapId": 480137, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5126230224", "hostawayReservationId": "62879852", "channelReservationId": "5126230224", "externalPropertyId": "15950709", "externalUnitId": "1595070901", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "B17g1JY1", "guestPortalUrl": "https://guest-portal.hostaway.com/62879852/B17g1JY1", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-07-13 17:45:52", "pendingExpireDate": null, "guestName": "Jakub Kawaler", "guestFirstName": "Jakub", "guestLastName": "Kawaler", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": "", "guestCountry": "PL", "guestEmail": "gkawal.610375@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 6, "adults": 6, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-09-14", "departureDate": "2026-09-17", "isDatesUnspecified": 0, "previousArrivalDate": "2026-09-14", "previousDepartureDate": "2026-09-18", "checkInTime": 16, "checkOutTime": 11, "nights": 3, "phone": "+48606460138", "totalPrice": 347, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 56.07, "hostawayCommissionAmount": null, "cleaningFee": 67, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "modified", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nBOOKING NOTE : Payment charge is EUR 6.17358\nApproximate time of arrival: between 23:00 and 00:00", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": "38", "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": {"name": null, "channelId": 2005, "channelSpecificCode": "38", "longTerm": false, "cancellationPolicyItem": [{"refundAmount": 100, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": -93600, "event": "arrival"}, {"refundAmount": 0, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": 0, "event": "arrival"}]}, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 89776257, "accountId": 181258, "listingMapId": 480137, "reservationId": 62879852, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 67, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-07-15 18:26:26", "updatedOn": "2026-07-15 18:26:26"}, {"id": 89776258, "accountId": 181258, "listingMapId": 480137, "reservationId": 62879852, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 23.89, "currency": "EUR", "pe</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-06-08T11:43:34+00:00</t>
+          <t>2026-08-17T05:25:19+00:00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>c4ddfc9e517834ee</t>
+          <t>8ee17003e873e573</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>55943028</v>
+        <v>58286525</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{"id": 55943028, "listingMapId": 480139, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5851160347", "hostawayReservationId": "55943028", "channelReservationId": "5851160347", "externalPropertyId": "15499360", "externalUnitId": "1549936001", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "nYmZ4gpP", "guestPortalUrl": "https://guest-portal.hostaway.com/55943028/nYmZ4gpP", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-03-12 13:21:47", "pendingExpireDate": null, "guestName": "mariam Sikharulidze", "guestFirstName": "mariam", "guestLastName": "Sikharulidze", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "FR", "guestEmail": "msikha.130294@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 6, "adults": 4, "children": 2, "infants": null, "pets": null, "arrivalDate": "2026-08-06", "departureDate": "2026-08-11", "isDatesUnspecified": 0, "previousArrivalDate": "2026-08-06", "previousDepartureDate": "2026-08-12", "checkInTime": 16, "checkOutTime": 11, "nights": 5, "phone": "+33780178390", "totalPrice": 519.84, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 85.07, "hostawayCommissionAmount": null, "cleaningFee": 55, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "modified", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nBOOKING NOTE : Payment charge is EUR 9.848489", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "There is no meal option with this room.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 83679153, "accountId": 181258, "listingMapId": 480139, "reservationId": 55943028, "name": "Cleaning fee", "feeType": "guest", "externalReservationUnitId": null, "amount": 55, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-05-10 09:11:07", "updatedOn": "2026-05-10 09:11:07"}, {"id": 83679154, "accountId": 181258, "listingMapId": 480139, "reservationId": 55943028, "name": "VAT", "feeType": "guest", "externalReservationUnitId": null, "amount": 40.49, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-05-10 09:11:07", "updatedOn": "2026-05-10 09:11:07"}, {"id": 83679155, "accountId": 181258, "listingMapId": 480139, "reservationId": 55943028, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 19.44, "currency": "EUR", "percentage": 7.2, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-05-10 09:11:07", "updatedOn": "2026-05-10 09:11:07"}, {"id"</t>
+          <t>{"id": 58286525, "listingMapId": 480140, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5880212214", "hostawayReservationId": "58286525", "channelReservationId": "5880212214", "externalPropertyId": "15500360", "externalUnitId": "1550036001", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "ldZsk5KR", "guestPortalUrl": "https://guest-portal.hostaway.com/58286525/ldZsk5KR", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-04-24 19:17:58", "pendingExpireDate": null, "guestName": "Nathalie Course", "guestFirstName": "Nathalie", "guestLastName": "Course", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "FR", "guestEmail": "ncours.288445@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 6, "adults": 3, "children": 3, "infants": null, "pets": null, "arrivalDate": "2026-07-11", "departureDate": "2026-07-14", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 3, "phone": null, "totalPrice": 331.51, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 54.87, "hostawayCommissionAmount": null, "cleaningFee": 55, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nBOOKING NOTE : Payment charge is EUR 4.5185", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "There is no meal option with this room.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": "16", "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": {"name": "Moderate", "channelId": 2005, "channelSpecificCode": "16", "longTerm": false, "cancellationPolicyItem": [{"refundAmount": 100, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": -432000, "event": "arrival"}]}, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 82386383, "accountId": 181258, "listingMapId": 480140, "reservationId": 58286525, "name": "Cleaning fee", "feeType": "guest", "externalReservationUnitId": null, "amount": 55, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-24 19:19:18", "updatedOn": "2026-04-24 19:19:18"}, {"id": 82386384, "accountId": 181258, "listingMapId": 480140, "reservationId": 58286525, "name": "VAT", "feeType": "guest", "externalReservationUnitId": null, "amount": 24.34, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-24 19:19:18", "updatedOn": "2026-04-24 19:19:18"}, {"id": 82386385, "accountId": 181258, "listingMapId"</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-06-08T11:43:35+00:00</t>
+          <t>2026-08-17T05:25:20+00:00</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>683b4e6ef641d0f3</t>
+          <t>07f6ed751996a056</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>58969166</v>
+        <v>62788902</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{"id": 58969166, "listingMapId": 493047, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6259089014", "hostawayReservationId": "58969166", "channelReservationId": "6259089014", "externalPropertyId": "15480052", "externalUnitId": "1548005201", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "rwQAiUZR", "guestPortalUrl": "https://guest-portal.hostaway.com/58969166/rwQAiUZR", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-05-08 08:03:53", "pendingExpireDate": null, "guestName": "Wissal Ejjbari", "guestFirstName": "Wissal", "guestLastName": "Ejjbari", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "FR", "guestEmail": "wejjba.386487@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 1, "adults": 1, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-05-08", "departureDate": "2026-05-10", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 2, "phone": "+33650171208", "totalPrice": 110.64, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 18.07, "hostawayCommissionAmount": null, "cleaningFee": 40, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\n\nBOOKING NOTE : Payment charge is EUR 1.4882", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 83525986, "accountId": 181258, "listingMapId": 493047, "reservationId": 58969166, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 40, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-05-08 08:05:17", "updatedOn": "2026-05-08 08:05:17"}, {"id": 83525987, "accountId": 181258, "listingMapId": 493047, "reservationId": 58969166, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 6.03, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-05-08 08:05:17", "updatedOn": "2026-05-08 08:05:17"}, {"id": 83525988, "accountId": 181258, "listingMapId": 493047, "reservationId": 58969166, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 4.34, "currency": "EUR", "percentage": 7.2, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-05-08 08:05:17", "updatedOn": "2026-05-08 08:05:17"}, {"id": 835259</t>
+          <t>{"id": 62788902, "listingMapId": 493047, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5974058446", "hostawayReservationId": "62788902", "channelReservationId": "5974058446", "externalPropertyId": "15480052", "externalUnitId": "1548005201", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "OlUWyff7", "guestPortalUrl": "https://guest-portal.hostaway.com/62788902/OlUWyff7", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-07-11 16:19:34", "pendingExpireDate": null, "guestName": "lucie ep", "guestFirstName": "lucie", "guestLastName": "ep", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "BE", "guestEmail": "lep.263387@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 2, "adults": 2, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-07-11", "departureDate": "2026-07-13", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 2, "phone": "+33689697439", "totalPrice": 110.64, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 18.07, "hostawayCommissionAmount": null, "cleaningFee": 40, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nBOOKING NOTE : Payment charge is EUR 1.4882", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": "38", "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": {"name": null, "channelId": 2005, "channelSpecificCode": "38", "longTerm": false, "cancellationPolicyItem": [{"refundAmount": 0, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": 0, "event": "arrival"}]}, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 89323980, "accountId": 181258, "listingMapId": 493047, "reservationId": 62788902, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 40, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-07-11 16:22:58", "updatedOn": "2026-07-11 16:22:58"}, {"id": 89323981, "accountId": 181258, "listingMapId": 493047, "reservationId": 62788902, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 6.03, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-07-11 16:22:58", "updatedOn": "2026-07-11 16:22:58"}, {"id": 89323982, "accountId": 181258, "listingMap</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-06-08T11:43:36+00:00</t>
+          <t>2026-08-17T05:25:21+00:00</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>96af8bf61bc1ed96</t>
+          <t>603a6b28f68cbb05</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>58613637</v>
+        <v>61266193</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{"id": 58613637, "listingMapId": 480137, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6575979377", "hostawayReservationId": "58613637", "channelReservationId": "6575979377", "externalPropertyId": "15950709", "externalUnitId": "1595070901", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "RfZCVNy9", "guestPortalUrl": "https://guest-portal.hostaway.com/58613637/RfZCVNy9", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-05-01 17:29:18", "pendingExpireDate": null, "guestName": "Xavier Chaumette", "guestFirstName": "Xavier", "guestLastName": "Chaumette", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "FR", "guestEmail": "xchaum.310083@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 5, "adults": 5, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-05-04", "departureDate": "2026-05-07", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 3, "phone": "+33631914266", "totalPrice": 254.95, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 41.38, "hostawayCommissionAmount": null, "cleaningFee": 67, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nBOOKING NOTE : Payment charge is EUR 3.5693", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 82973714, "accountId": 181258, "listingMapId": 480137, "reservationId": 58613637, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 67, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-05-01 17:32:38", "updatedOn": "2026-05-01 17:32:38"}, {"id": 82973715, "accountId": 181258, "listingMapId": 480137, "reservationId": 58613637, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 16.04, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-05-01 17:32:38", "updatedOn": "2026-05-01 17:32:38"}, {"id": 82973716, "accountId": 181258, "listingMapId": 480137, "reservationId": 58613637, "name": "taxe de séjour", "feeType": "guest", "externalReservationUnitId": null, "amount": 11.55, "currency": "EUR", "percentage": 7.2, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-05-01 17:32:38", "updatedOn": "2026-05-01 17:32:38"}, {"id": 82973717, "</t>
+          <t>{"id": 61266193, "listingMapId": 480137, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5750137119", "hostawayReservationId": "61266193", "channelReservationId": "5750137119", "externalPropertyId": "15950709", "externalUnitId": "1595070901", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "2Eoej7vu", "guestPortalUrl": "https://guest-portal.hostaway.com/61266193/2Eoej7vu", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-06-21 16:21:55", "pendingExpireDate": null, "guestName": "Beaufort Mathys", "guestFirstName": "Beaufort", "guestLastName": "Mathys", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "FR", "guestEmail": "bmathy.851448@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 5, "adults": 5, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-07-10", "departureDate": "2026-07-13", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 3, "phone": "+33783790731", "totalPrice": 304.81, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 49.33, "hostawayCommissionAmount": null, "cleaningFee": 67, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nReservation has a cancellation grace period. Do not charge if cancelled before 2026-06-22 18:21:55\n\nBOOKING NOTE : Payment charge is EUR 4.26734", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": "16", "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": {"name": "Moderate", "channelId": 2005, "channelSpecificCode": "16", "longTerm": false, "cancellationPolicyItem": [{"refundAmount": 100, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": -432000, "event": "arrival"}]}, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 87463389, "accountId": 181258, "listingMapId": 480137, "reservationId": 61266193, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 67, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-06-21 16:27:14", "updatedOn": "2026-06-21 16:27:14"}, {"id": 87463390, "accountId": 181258, "listingMapId": 480137, "reservationId": 61266193, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 20.29, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isIm</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-06-08T11:43:37+00:00</t>
+          <t>2026-08-17T05:25:22+00:00</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>bb9643bc60da189f</t>
+          <t>0ce25db8cce7a7aa</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>58515565</v>
+        <v>62746722</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{"id": 58515565, "listingMapId": 493047, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5112492307", "hostawayReservationId": "58515565", "channelReservationId": "5112492307", "externalPropertyId": "15480052", "externalUnitId": "1548005201", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "9oChM-lF", "guestPortalUrl": "https://guest-portal.hostaway.com/58515565/9oChM-lF", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-04-29 21:31:39", "pendingExpireDate": null, "guestName": "Paul Ulvoas", "guestFirstName": "Paul", "guestLastName": "Ulvoas", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "FR", "guestEmail": "pulvoa.469155@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 1, "adults": 1, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-04-30", "departureDate": "2026-05-03", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 3, "phone": "+33750034873", "totalPrice": 137.81, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 22.41, "hostawayCommissionAmount": null, "cleaningFee": 40, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "modified", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\n\nBOOKING NOTE : Payment charge is EUR 1.8452", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 83120434, "accountId": 181258, "listingMapId": 493047, "reservationId": 58515565, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 40, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-05-03 17:08:49", "updatedOn": "2026-05-03 17:08:49"}, {"id": 83120435, "accountId": 181258, "listingMapId": 493047, "reservationId": 58515565, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 8.35, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-05-03 17:08:49", "updatedOn": "2026-05-03 17:08:49"}, {"id": 83120436, "accountId": 181258, "listingMapId": 493047, "reservationId": 58515565, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 6.01, "currency": "EUR", "percentage": 7.2, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-05-03 17:08:49", "updatedOn": "2026-05-03 17:08:49"}, {"id": 8312043</t>
+          <t>{"id": 62746722, "listingMapId": 480139, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6612557472", "hostawayReservationId": "62746722", "channelReservationId": "6612557472", "externalPropertyId": "15499360", "externalUnitId": "1549936001", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "eboOf6B8", "guestPortalUrl": "https://guest-portal.hostaway.com/62746722/eboOf6B8", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-07-10 17:20:35", "pendingExpireDate": null, "guestName": "Luiz Carlos Barbosa", "guestFirstName": "Luiz", "guestLastName": "Carlos Barbosa", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "PT", "guestEmail": "lbarbo.565917@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 6, "adults": 2, "children": 4, "infants": null, "pets": null, "arrivalDate": "2026-12-16", "departureDate": "2026-12-18", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 2, "phone": null, "totalPrice": 203.98, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 34.14, "hostawayCommissionAmount": null, "cleaningFee": 55, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nBOOKING NOTE : Payment charge is EUR 2.8112", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "There is no meal option with this room.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": "60", "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": {"name": null, "channelId": 2005, "channelSpecificCode": "60", "longTerm": false, "cancellationPolicyItem": [{"refundAmount": 100, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": -435600, "event": "arrival"}, {"refundAmount": 50, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": 0, "event": "arrival"}]}, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 89243158, "accountId": 181258, "listingMapId": 480139, "reservationId": 62746722, "name": "Cleaning fee", "feeType": "guest", "externalReservationUnitId": null, "amount": 55, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-07-10 17:21:59", "updatedOn": "2026-07-10 17:21:59"}, {"id": 89243159, "accountId": 181258, "listingMapId": 480139, "reservationId": 62746722, "name": "VAT", "feeType": "guest", "externalReservationUnitId": null, "amount": 13.25, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "inserted</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-06-08T11:43:38+00:00</t>
+          <t>2026-08-17T05:25:22+00:00</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>9c869629de3096f1</t>
+          <t>0f872ca4bed82d1a</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>53502338</v>
+        <v>57357569</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{"id": 53502338, "listingMapId": 480139, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5383925091", "hostawayReservationId": "53502338", "channelReservationId": "5383925091", "externalPropertyId": "15499360", "externalUnitId": "1549936001", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "nMR3Iuvx", "guestPortalUrl": "https://guest-portal.hostaway.com/53502338/nMR3Iuvx", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 1, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2025-12-28 00:00:00", "pendingExpireDate": null, "guestName": "Núria Aquilué Junyent", "guestFirstName": "Núria", "guestLastName": "Aquilué Junyent", "guestExternalAccountId": null, "guestZipCode": null, "guestAddress": null, "guestCity": null, "guestCountry": null, "guestEmail": null, "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 5, "adults": 3, "children": 2, "infants": null, "pets": null, "arrivalDate": "2026-04-30", "departureDate": "2026-05-03", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 3, "phone": null, "totalPrice": 300, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": null, "hostawayCommissionAmount": null, "cleaningFee": null, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "modified", "paymentStatus": "Unknown", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": null, "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "There is no meal option with this room.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [], "reservationUnit": [], "insertedOn": "2026-01-31 13:04:29", "updatedOn": "2026-05-03 08:54:04", "latestActivityOn": "2026-05-03 08:54:03", "customerUserId": null, "guestLocale": null, "localeForMessaging": null, "localeForMessagingSource": null, "listingCustomFields": null, "rentalAgreementFileUrl": null, "reservationAgreement": "not_required", "financeField": [{"id": 218021622, "units": 1, "listingFeeSettingId": null, "type": "accommodation", "name": "baseRate", "title": "Base rate", "alias": null, "quantity": null, "value": 300, "isIncludedInTotalPrice": 1, "isOverriddenByUser": 0, "isMandatory": 1, "isQuantitySelectable": 0, "isDeleted": 0, "total": 300}, {"id": 218021623, "units": 1, "listingFeeSettingId": null, "type": "totals", "name": "totalPriceFromChannel", "title": "Total price from channel", "alias": null, "quantity": null, "value": 300, "isIncludedInTotalPrice": 0, "isOverriddenByUser": 0, "isMandatory": 0, "isQuantitySelectable": 0, "isDeleted": 0, "total": 300}], "guestPaymentCardIsVirtual": null, "insuranceStatus": "not_eligible", "claimStatus": null, "insurancePolicyId": null, "insuranceCoverageStart": null, "insuranceCoverageEnd": null, "cancellationPolicyId": 79381, "cancellationPolicy": "mod</t>
+          <t xml:space="preserve">{"id": 57357569, "listingMapId": 480137, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6642358875", "hostawayReservationId": "57357569", "channelReservationId": "6642358875", "externalPropertyId": "15950709", "externalUnitId": "1595070901", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "QGSNoQta", "guestPortalUrl": "https://guest-portal.hostaway.com/57357569/QGSNoQta", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-04-06 19:05:41", "pendingExpireDate": null, "guestName": "Javier Arroyo", "guestFirstName": "Javier", "guestLastName": "Arroyo", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "ES", "guestEmail": "jarroy.947317@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 4, "adults": 2, "children": 2, "infants": null, "pets": null, "arrivalDate": "2026-07-04", "departureDate": "2026-07-10", "isDatesUnspecified": 0, "previousArrivalDate": "2026-07-05", "previousDepartureDate": "2026-07-10", "checkInTime": 16, "checkOutTime": 11, "nights": 6, "phone": "+34667935734", "totalPrice": 597.72, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 98.75, "hostawayCommissionAmount": null, "cleaningFee": 67, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "modified", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nBOOKING NOTE : Payment charge is EUR 7.1710142", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": "16", "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": {"name": "Moderate", "channelId": 2005, "channelSpecificCode": "16", "longTerm": false, "cancellationPolicyItem": [{"refundAmount": 100, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": -432000, "event": "arrival"}]}, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 82620879, "accountId": 181258, "listingMapId": 480137, "reservationId": 57357569, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 67, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-27 16:51:06", "updatedOn": "2026-04-27 16:51:06"}, {"id": 82620880, "accountId": 181258, "listingMapId": 480137, "reservationId": 57357569, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 46.72, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-27 16:51:06", "updatedOn": "2026-04-27 16:51:06"}, </t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-06-08T11:43:39+00:00</t>
+          <t>2026-08-17T05:25:23+00:00</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>4493011ea6242a6e</t>
+          <t>e1291d4e1f66034a</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>53743611</v>
+        <v>62447871</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{"id": 53743611, "listingMapId": 480140, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6990197423", "hostawayReservationId": "53743611", "channelReservationId": "6990197423", "externalPropertyId": "15500360", "externalUnitId": "1550036001", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "pJJXykUt", "guestPortalUrl": "https://guest-portal.hostaway.com/53743611/pJJXykUt", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 1, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-02-04 09:27:07", "pendingExpireDate": null, "guestName": "Samantha Simon", "guestFirstName": "Samantha", "guestLastName": "Simon", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": "", "guestCountry": "BE", "guestEmail": "ssimon.966720@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 6, "adults": 2, "children": 4, "infants": null, "pets": null, "arrivalDate": "2026-04-28", "departureDate": "2026-05-03", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 5, "phone": "+32470079549", "totalPrice": 598.5, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 96.02, "hostawayCommissionAmount": null, "cleaningFee": 50, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "modified", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nApproximate time of arrival: between 19:00 and 20:00\nBOOKING NOTE : Payment charge is EUR 8.378944", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "There is no meal option with this room.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 82954360, "accountId": 181258, "listingMapId": 480140, "reservationId": 53743611, "name": "Cleaning fee", "feeType": "guest", "externalReservationUnitId": null, "amount": 50, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-05-01 13:00:34", "updatedOn": "2026-05-01 13:00:34"}, {"id": 82954361, "accountId": 181258, "listingMapId": 480140, "reservationId": 53743611, "name": "VAT", "feeType": "guest", "externalReservationUnitId": null, "amount": 46.8, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-05-01 13:00:34", "updatedOn": "2026-05-01 13:00:34"}, {"id": 82954362, "accountId": 181258, "listingMapId": 480140, "reservationId": 53743611, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 33.7, "currency": "EUR", "percentage": 7.2, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-05-01 13:00:34", "updatedOn": "2026</t>
+          <t>{"id": 62447871, "listingMapId": 493047, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6239681137", "hostawayReservationId": "62447871", "channelReservationId": "6239681137", "externalPropertyId": "15480052", "externalUnitId": "1548005201", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "B-fw3Np5", "guestPortalUrl": "https://guest-portal.hostaway.com/62447871/B-fw3Np5", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-07-04 17:19:50", "pendingExpireDate": null, "guestName": "Marco Rapallo", "guestFirstName": "Marco", "guestLastName": "Rapallo", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "IT", "guestEmail": "mrapal.446141@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 1, "adults": 1, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-07-06", "departureDate": "2026-07-10", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 4, "phone": "+393518059212", "totalPrice": 181.28, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 29.34, "hostawayCommissionAmount": null, "cleaningFee": 40, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nBOOKING NOTE : Payment charge is EUR 2.4164", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": "38", "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": {"name": null, "channelId": 2005, "channelSpecificCode": "38", "longTerm": false, "cancellationPolicyItem": [{"refundAmount": 100, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": -93600, "event": "arrival"}, {"refundAmount": 0, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": 0, "event": "arrival"}]}, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 88646004, "accountId": 181258, "listingMapId": 493047, "reservationId": 62447871, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 40, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-07-04 17:21:22", "updatedOn": "2026-07-04 17:21:22"}, {"id": 88646005, "accountId": 181258, "listingMapId": 493047, "reservationId": 62447871, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 12.05, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isI</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-06-08T11:43:40+00:00</t>
+          <t>2026-08-17T05:25:24+00:00</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>28c80d99278146f3</t>
+          <t>363a10ad073e5f11</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>57636469</v>
+        <v>62366750</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{"id": 57636469, "listingMapId": 480140, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6089684943", "hostawayReservationId": "57636469", "channelReservationId": "6089684943", "externalPropertyId": "15500360", "externalUnitId": "1550036001", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "SEb6gkAK", "guestPortalUrl": "https://guest-portal.hostaway.com/57636469/SEb6gkAK", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-04-12 21:01:18", "pendingExpireDate": null, "guestName": "Jose Manuel Herrera", "guestFirstName": "Jose", "guestLastName": "Manuel Herrera", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "ES", "guestEmail": "jherre.706373@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 4, "adults": 3, "children": 1, "infants": null, "pets": null, "arrivalDate": "2026-08-20", "departureDate": "2026-08-26", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 6, "phone": null, "totalPrice": 614.11, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 99.95, "hostawayCommissionAmount": null, "cleaningFee": 55, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nBOOKING NOTE : Payment charge is EUR 8.597582", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "There is no meal option with this room.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 80885084, "accountId": 181258, "listingMapId": 480140, "reservationId": 57636469, "name": "Cleaning fee", "feeType": "guest", "externalReservationUnitId": null, "amount": 55, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-12 21:02:55", "updatedOn": "2026-04-12 21:02:55"}, {"id": 80885085, "accountId": 181258, "listingMapId": 480140, "reservationId": 57636469, "name": "VAT", "feeType": "guest", "externalReservationUnitId": null, "amount": 48.45, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-12 21:02:55", "updatedOn": "2026-04-12 21:02:55"}, {"id": 80885086, "accountId": 181258, "listingMapId": 480140, "reservationId": 57636469, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 26.16, "currency": "EUR", "percentage": 7.2, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-12 21:02:55", "updatedOn": "2026-04-12 21:02:55"}, {"id": 80885087, "accountId": 181258</t>
+          <t>{"id": 62366750, "listingMapId": 480139, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5738519473", "hostawayReservationId": "62366750", "channelReservationId": "5738519473", "externalPropertyId": "15499360", "externalUnitId": "1549936001", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "MZSyU8C7", "guestPortalUrl": "https://guest-portal.hostaway.com/62366750/MZSyU8C7", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-07-02 19:15:07", "pendingExpireDate": null, "guestName": "Chahboun Noureddine", "guestFirstName": "Chahboun", "guestLastName": "Noureddine", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "FR", "guestEmail": "cnoure.237582@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 2, "adults": 2, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-07-06", "departureDate": "2026-07-10", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 4, "phone": "+33683692219", "totalPrice": 232.21, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 37.62, "hostawayCommissionAmount": null, "cleaningFee": 55, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nReservation has a cancellation grace period. Do not charge if cancelled before 2026-07-03 21:15:07\n\nBOOKING NOTE : Payment charge is EUR 3.09848", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "There is no meal option with this room.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": "1", "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": {"name": null, "channelId": 2005, "channelSpecificCode": "1", "longTerm": false, "cancellationPolicyItem": [{"refundAmount": 100, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": -189893, "event": "arrival"}, {"refundAmount": 0, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": 0, "event": "arrival"}]}, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 88476503, "accountId": 181258, "listingMapId": 480139, "reservationId": 62366750, "name": "Cleaning fee", "feeType": "guest", "externalReservationUnitId": null, "amount": 55, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-07-02 19:19:32", "updatedOn": "2026-07-02 19:19:32"}, {"id": 88476504, "accountId": 181258, "listingMapId": 480139, "reservationId": 62366750, "name": "VAT", "feeType": "guest", "externalReservationUnitId": null, "amount": 15.12, "c</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-06-08T11:43:41+00:00</t>
+          <t>2026-08-17T05:25:26+00:00</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1f665f168ddcfd12</t>
+          <t>42b338c2b263ca67</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>58438124</v>
+        <v>62639290</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{"id": 58438124, "listingMapId": 480139, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6669176297", "hostawayReservationId": "58438124", "channelReservationId": "6669176297", "externalPropertyId": "15499360", "externalUnitId": "1549936001", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "A1kNVcIQ", "guestPortalUrl": "https://guest-portal.hostaway.com/58438124/A1kNVcIQ", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-04-28 09:53:40", "pendingExpireDate": null, "guestName": "Olfa Ben Hassine", "guestFirstName": "Olfa", "guestLastName": "Ben Hassine", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "FR", "guestEmail": "ohassi.659128@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 6, "adults": 2, "children": 4, "infants": null, "pets": null, "arrivalDate": "2026-08-13", "departureDate": "2026-08-19", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 6, "phone": null, "totalPrice": 590.02, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 98.36, "hostawayCommissionAmount": null, "cleaningFee": 55, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nBOOKING NOTE : Payment charge is EUR 8.4203", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "There is no meal option with this room.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 82677563, "accountId": 181258, "listingMapId": 480139, "reservationId": 58438124, "name": "Cleaning fee", "feeType": "guest", "externalReservationUnitId": null, "amount": 55, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-28 09:54:59", "updatedOn": "2026-04-28 09:54:59"}, {"id": 82677564, "accountId": 181258, "listingMapId": 480139, "reservationId": 58438124, "name": "VAT", "feeType": "guest", "externalReservationUnitId": null, "amount": 47.6, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-28 09:54:59", "updatedOn": "2026-04-28 09:54:59"}, {"id": 82677565, "accountId": 181258, "listingMapId": 480139, "reservationId": 58438124, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 11.42, "currency": "EUR", "percentage": 7.2, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-28 09:54:59", "updatedOn": "2026-04-28 09:54:59"}, {"id": 82677566, "accountId": 181258, "listin</t>
+          <t>{"id": 62639290, "listingMapId": 480139, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6710486761", "hostawayReservationId": "62639290", "channelReservationId": "6710486761", "externalPropertyId": "15499360", "externalUnitId": "1549936001", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "_FkkcGzF", "guestPortalUrl": "https://guest-portal.hostaway.com/62639290/_FkkcGzF", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-07-08 12:56:34", "pendingExpireDate": null, "guestName": "Leticia Garcia Ruano", "guestFirstName": "Leticia", "guestLastName": "Garcia Ruano", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "ES", "guestEmail": "lruano.172026@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 4, "adults": 2, "children": 2, "infants": null, "pets": null, "arrivalDate": "2026-12-24", "departureDate": "2026-12-27", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 3, "phone": null, "totalPrice": 280.86, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 46.53, "hostawayCommissionAmount": null, "cleaningFee": 55, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nBOOKING NOTE : Payment charge is EUR 3.932005", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "There is no meal option with this room.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": "60", "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": {"name": null, "channelId": 2005, "channelSpecificCode": "60", "longTerm": false, "cancellationPolicyItem": [{"refundAmount": 100, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": -435600, "event": "arrival"}, {"refundAmount": 67, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": 0, "event": "arrival"}]}, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 89027989, "accountId": 181258, "listingMapId": 480139, "reservationId": 62639290, "name": "Cleaning fee", "feeType": "guest", "externalReservationUnitId": null, "amount": 55, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-07-08 12:57:59", "updatedOn": "2026-07-08 12:57:59"}, {"id": 89027990, "accountId": 181258, "listingMapId": 480139, "reservationId": 62639290, "name": "VAT", "feeType": "guest", "externalReservationUnitId": null, "amount": 19.88, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "inse</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-06-08T11:43:41+00:00</t>
+          <t>2026-08-17T05:25:27+00:00</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>92cb9c71e9a5ae23</t>
+          <t>24353d950ce5b3a8</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>57674814</v>
+        <v>60290392</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{"id": 57674814, "listingMapId": 480140, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6125105485", "hostawayReservationId": "57674814", "channelReservationId": "6125105485", "externalPropertyId": "15500360", "externalUnitId": "1550036001", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "FZ5YQEIF", "guestPortalUrl": "https://guest-portal.hostaway.com/57674814/FZ5YQEIF", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-04-13 18:24:36", "pendingExpireDate": null, "guestName": "Paloma Paniagua Martin", "guestFirstName": "Paloma", "guestLastName": "Paniagua Martin", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": "", "guestCountry": "ES", "guestEmail": "nqlnnj.822584@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 4, "adults": 4, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-07-14", "departureDate": "2026-07-17", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 3, "phone": null, "totalPrice": 360.2, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 58.05, "hostawayCommissionAmount": null, "cleaningFee": 55, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nBOOKING NOTE : Payment charge is EUR 5.042793\nApproximate time of arrival: between 16:00 and 17:00", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "There is no meal option with this room.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 81081409, "accountId": 181258, "listingMapId": 480140, "reservationId": 57674814, "name": "Cleaning fee", "feeType": "guest", "externalReservationUnitId": null, "amount": 55, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-13 18:26:01", "updatedOn": "2026-04-13 18:26:01"}, {"id": 81081410, "accountId": 181258, "listingMapId": 480140, "reservationId": 57674814, "name": "VAT", "feeType": "guest", "externalReservationUnitId": null, "amount": 26.04, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-13 18:26:01", "updatedOn": "2026-04-13 18:26:01"}, {"id": 81081411, "accountId": 181258, "listingMapId": 480140, "reservationId": 57674814, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 18.75, "currency": "EUR", "percentage": 7.2, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-13 18:26:01", "updatedOn":</t>
+          <t>{"id": 60290392, "listingMapId": 480140, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6637658696", "hostawayReservationId": "60290392", "channelReservationId": "6637658696", "externalPropertyId": "15500360", "externalUnitId": "1550036001", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "vRzwemTt", "guestPortalUrl": "https://guest-portal.hostaway.com/60290392/vRzwemTt", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-06-01 18:31:20", "pendingExpireDate": null, "guestName": "Uwe Stolzenburg", "guestFirstName": "Uwe", "guestLastName": "Stolzenburg", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": "", "guestCountry": "DE", "guestEmail": "ustolz.279753@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 2, "adults": 2, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-07-05", "departureDate": "2026-07-07", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 2, "phone": null, "totalPrice": 240.66, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 38.97, "hostawayCommissionAmount": null, "cleaningFee": 55, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nApproximate time of arrival: between 14:00 and 15:00\nBOOKING NOTE : Payment charge is EUR 3.2095", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "There is no meal option with this room.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": "16", "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": {"name": "Moderate", "channelId": 2005, "channelSpecificCode": "16", "longTerm": false, "cancellationPolicyItem": [{"refundAmount": 100, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": -432000, "event": "arrival"}]}, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 85682976, "accountId": 181258, "listingMapId": 480140, "reservationId": 60290392, "name": "Cleaning fee", "feeType": "guest", "externalReservationUnitId": null, "amount": 55, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-06-01 18:33:31", "updatedOn": "2026-06-01 18:33:31"}, {"id": 85682977, "accountId": 181258, "listingMapId": 480140, "reservationId": 60290392, "name": "VAT", "feeType": "guest", "externalReservationUnitId": null, "amount": 15.84, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-06-01 18:33:32", "updatedOn": "2026-06-01 18:33:32</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-06-08T11:43:42+00:00</t>
+          <t>2026-08-17T05:25:28+00:00</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>52b9ff22bb6bb6a3</t>
+          <t>530c1934e0b138af</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>56885582</v>
+        <v>62475088</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{"id": 56885582, "listingMapId": 485104, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5176698850", "hostawayReservationId": "56885582", "channelReservationId": "5176698850", "externalPropertyId": "16046812", "externalUnitId": "1604681201", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "QKQe3kgN", "guestPortalUrl": "https://guest-portal.hostaway.com/56885582/QKQe3kgN", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-03-28 20:35:48", "pendingExpireDate": null, "guestName": "Valerie Blier", "guestFirstName": "Valerie", "guestLastName": "Blier", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "FR", "guestEmail": "vblier.632926@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 4, "adults": 3, "children": 1, "infants": null, "pets": null, "arrivalDate": "2026-04-20", "departureDate": "2026-04-24", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 4, "phone": "+33616916975", "totalPrice": 244.54, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 39.63, "hostawayCommissionAmount": null, "cleaningFee": null, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nBOOKING NOTE : Payment charge is EUR 3.4236034", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 78997386, "accountId": 181258, "listingMapId": 485104, "reservationId": 56885582, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 21.19, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-28 20:37:10", "updatedOn": "2026-03-28 20:37:10"}, {"id": 78997387, "accountId": 181258, "listingMapId": 485104, "reservationId": 56885582, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 11.44, "currency": "EUR", "percentage": 7.2, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-28 20:37:10", "updatedOn": "2026-03-28 20:37:10"}, {"id": 78997388, "accountId": 181258, "listingMapId": 485104, "reservationId": 56885582, "name": "TVA", "feeType": "hotel", "externalReservationUnitId": null, "amount": 21.19, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-28 20:37:10", "updatedOn": "2026-03-28 20:37:10"}, {"id": 78997389, "accoun</t>
+          <t>{"id": 62475088, "listingMapId": 480141, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6896025236", "hostawayReservationId": "62475088", "channelReservationId": "6896025236", "externalPropertyId": "15971299", "externalUnitId": "1597129901", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "ZbdagArV", "guestPortalUrl": "https://guest-portal.hostaway.com/62475088/ZbdagArV", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-07-05 12:10:59", "pendingExpireDate": null, "guestName": "FRANCK SANDRIER", "guestFirstName": "FRANCK", "guestLastName": "SANDRIER", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "FR", "guestEmail": "fsandr.245357@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 11, "adults": 11, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-10-30", "departureDate": "2026-11-01", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 2, "phone": null, "totalPrice": 445.09, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 72.17, "hostawayCommissionAmount": null, "cleaningFee": 110, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nBOOKING NOTE : Payment charge is EUR 5.943", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "There is no meal option with this room.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": "30", "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": {"name": null, "channelId": 2005, "channelSpecificCode": "30", "longTerm": false, "cancellationPolicyItem": [{"refundAmount": 100, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": -1216800, "event": "arrival"}, {"refundAmount": 50, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": 0, "event": "arrival"}]}, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 88711015, "accountId": 181258, "listingMapId": 480141, "reservationId": 62475088, "name": "Cleaning fee", "feeType": "guest", "externalReservationUnitId": null, "amount": 110, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-07-05 12:15:17", "updatedOn": "2026-07-05 12:15:17"}, {"id": 88711016, "accountId": 181258, "listingMapId": 480141, "reservationId": 62475088, "name": "VAT", "feeType": "guest", "externalReservationUnitId": null, "amount": 28.59, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedO</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-06-08T11:43:43+00:00</t>
+          <t>2026-08-17T05:25:29+00:00</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>ee326159b2c59afe</t>
+          <t>6ef259b57caa164b</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>56765333</v>
+        <v>59168803</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"id": 56765333, "listingMapId": 485104, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6174292312", "hostawayReservationId": "56765333", "channelReservationId": "6174292312", "externalPropertyId": "16046812", "externalUnitId": "1604681201", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "ym9d9YSi", "guestPortalUrl": "https://guest-portal.hostaway.com/56765333/ym9d9YSi", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-03-26 19:05:27", "pendingExpireDate": null, "guestName": "Amjhadi Youssef", "guestFirstName": "Amjhadi", "guestLastName": "Youssef", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": "", "guestCountry": "FR", "guestEmail": "ayouss.162491@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 2, "adults": 2, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-03-27", "departureDate": "2026-03-29", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 2, "phone": "+33651159183", "totalPrice": 62.9, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 10.04, "hostawayCommissionAmount": null, "cleaningFee": null, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "modified", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nApproximate time of arrival: between 16:00 and 17:00\nBOOKING NOTE : Payment charge is EUR 0.8806616", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 79325736, "accountId": 181258, "listingMapId": 485104, "reservationId": 56765333, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 5.37, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-01 12:32:26", "updatedOn": "2026-04-01 12:32:26"}, {"id": 79325737, "accountId": 181258, "listingMapId": 485104, "reservationId": 56765333, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 3.86, "currency": "EUR", "percentage": 7.19, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-01 12:32:26", "updatedOn": "2026-04-01 12:32:26"}, {"id": 79325738, "accountId": 181258, "listingMapId": 485104, "reservationId": 56765333, "name": "TVA", "feeType": "hotel", "externalReservationUnitId": null, "amount": 5.37, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-01 12:32:26", </t>
+          <t>{"id": 59168803, "listingMapId": 480137, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5638882353", "hostawayReservationId": "59168803", "channelReservationId": "5638882353", "externalPropertyId": "15950709", "externalUnitId": "1595070901", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "aq7UwuF7", "guestPortalUrl": "https://guest-portal.hostaway.com/59168803/aq7UwuF7", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-05-12 18:24:17", "pendingExpireDate": null, "guestName": "Klara Kuntova", "guestFirstName": "Klara", "guestLastName": "Kuntova", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": "", "guestCountry": "CZ", "guestEmail": "kkunto.706890@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 3, "adults": 2, "children": 1, "infants": null, "pets": null, "arrivalDate": "2026-07-01", "departureDate": "2026-07-04", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 3, "phone": "+420739217002", "totalPrice": 336.57, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 55.3, "hostawayCommissionAmount": null, "cleaningFee": 67, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nBOOKING NOTE : Payment charge is EUR 4.71198\nApproximate time of arrival: between 13:00 and 14:00", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": "16", "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": {"name": "Moderate", "channelId": 2005, "channelSpecificCode": "16", "longTerm": false, "cancellationPolicyItem": [{"refundAmount": 100, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": -432000, "event": "arrival"}]}, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 83910222, "accountId": 181258, "listingMapId": 480137, "reservationId": 59168803, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 67, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-05-12 18:25:44", "updatedOn": "2026-05-12 18:25:44"}, {"id": 83910223, "accountId": 181258, "listingMapId": 480137, "reservationId": 59168803, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 23.48, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-05-12 18:25:44", "update</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-06-08T11:43:44+00:00</t>
+          <t>2026-08-17T05:25:29+00:00</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>4ea38c4a23310e3f</t>
+          <t>339f072abf010129</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>57242598</v>
+        <v>62439384</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{"id": 57242598, "listingMapId": 480139, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6614587583", "hostawayReservationId": "57242598", "channelReservationId": "6614587583", "externalPropertyId": "15499360", "externalUnitId": "1549936001", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "kTQGEiLf", "guestPortalUrl": "https://guest-portal.hostaway.com/57242598/kTQGEiLf", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-04-03 19:11:37", "pendingExpireDate": null, "guestName": "INES MARIA NOGALES FLORES", "guestFirstName": "INES", "guestLastName": "MARIA NOGALES FLORES", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": "", "guestCountry": "ES", "guestEmail": "iflore.270703@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 4, "adults": 2, "children": 2, "infants": null, "pets": null, "arrivalDate": "2026-04-23", "departureDate": "2026-04-28", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 5, "phone": "+34652486712", "totalPrice": 477.82, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 79.02, "hostawayCommissionAmount": null, "cleaningFee": 67, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nBOOKING NOTE : Payment charge is EUR 6.6894646", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "There is no meal option with this room.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 79560356, "accountId": 181258, "listingMapId": 480139, "reservationId": 57242598, "name": "Cleaning fee", "feeType": "guest", "externalReservationUnitId": null, "amount": 67, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-03 19:12:58", "updatedOn": "2026-04-03 19:12:58"}, {"id": 79560357, "accountId": 181258, "listingMapId": 480139, "reservationId": 57242598, "name": "VAT", "feeType": "guest", "externalReservationUnitId": null, "amount": 36.16, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-03 19:12:58", "updatedOn": "2026-04-03 19:12:58"}, {"id": 79560358, "accountId": 181258, "listingMapId": 480139, "reservationId": 57242598, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 13.02, "currency": "EUR", "percentage": 7.2, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-03 19:12:58", "updatedOn": "2026-04-03 19:12:58"}, {"id": 7956035</t>
+          <t>{"id": 62439384, "listingMapId": 480141, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6955046662", "hostawayReservationId": "62439384", "channelReservationId": "6955046662", "externalPropertyId": "15971299", "externalUnitId": "1597129901", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "NFM4zrW1", "guestPortalUrl": "https://guest-portal.hostaway.com/62439384/NFM4zrW1", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-07-04 13:20:56", "pendingExpireDate": null, "guestName": "Nelia Freitas", "guestFirstName": "Nelia", "guestLastName": "Freitas", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "PT", "guestEmail": "nfreit.186494@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 9, "adults": 7, "children": 2, "infants": null, "pets": null, "arrivalDate": "2026-09-01", "departureDate": "2026-09-03", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 2, "phone": null, "totalPrice": 440.51, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 72.17, "hostawayCommissionAmount": null, "cleaningFee": 110, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nBOOKING NOTE : Payment charge is EUR 5.943", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "There is no meal option with this room.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": "30", "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": {"name": null, "channelId": 2005, "channelSpecificCode": "30", "longTerm": false, "cancellationPolicyItem": [{"refundAmount": 100, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": -1216800, "event": "arrival"}, {"refundAmount": 50, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": 0, "event": "arrival"}]}, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 88625676, "accountId": 181258, "listingMapId": 480141, "reservationId": 62439384, "name": "Cleaning fee", "feeType": "guest", "externalReservationUnitId": null, "amount": 110, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-07-04 13:22:30", "updatedOn": "2026-07-04 13:22:30"}, {"id": 88625677, "accountId": 181258, "listingMapId": 480141, "reservationId": 62439384, "name": "VAT", "feeType": "guest", "externalReservationUnitId": null, "amount": 28.59, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-06-08T11:43:48+00:00</t>
+          <t>2026-08-17T05:25:30+00:00</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>6db223f213995422</t>
+          <t>1ada33ae1979ac60</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>57357569</v>
+        <v>61397934</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{"id": 57357569, "listingMapId": 480137, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6642358875", "hostawayReservationId": "57357569", "channelReservationId": "6642358875", "externalPropertyId": "15950709", "externalUnitId": "1595070901", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "QGSNoQta", "guestPortalUrl": "https://guest-portal.hostaway.com/57357569/QGSNoQta", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-04-06 19:05:41", "pendingExpireDate": null, "guestName": "Javier Arroyo", "guestFirstName": "Javier", "guestLastName": "Arroyo", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "ES", "guestEmail": "jarroy.947317@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 4, "adults": 2, "children": 2, "infants": null, "pets": null, "arrivalDate": "2026-07-04", "departureDate": "2026-07-10", "isDatesUnspecified": 0, "previousArrivalDate": "2026-07-05", "previousDepartureDate": "2026-07-10", "checkInTime": 16, "checkOutTime": 11, "nights": 6, "phone": "+34667935734", "totalPrice": 597.72, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 98.75, "hostawayCommissionAmount": null, "cleaningFee": 67, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "modified", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nBOOKING NOTE : Payment charge is EUR 7.1710142", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 82620879, "accountId": 181258, "listingMapId": 480137, "reservationId": 57357569, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 67, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-27 16:51:06", "updatedOn": "2026-04-27 16:51:06"}, {"id": 82620880, "accountId": 181258, "listingMapId": 480137, "reservationId": 57357569, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 46.72, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-27 16:51:06", "updatedOn": "2026-04-27 16:51:06"}, {"id": 82620881, "accountId": 181258, "listingMapId": 480137, "reservationId": 57357569, "name": "taxe de séjour", "feeType": "guest", "externalReservationUnitId": null, "amount": 16.82, "currency": "EUR", "percentage": 7.2, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-27 16:51:06", "updatedOn": "2026-04-27 16:51:06"}, {"i</t>
+          <t>{"id": 61397934, "listingMapId": 493047, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5383835722", "hostawayReservationId": "61397934", "channelReservationId": "5383835722", "externalPropertyId": "15480052", "externalUnitId": "1548005201", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "l-S7y68C", "guestPortalUrl": "https://guest-portal.hostaway.com/61397934/l-S7y68C", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-06-23 21:31:08", "pendingExpireDate": null, "guestName": "Esposito Giuseppe", "guestFirstName": "Esposito", "guestLastName": "Giuseppe", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "IT", "guestEmail": "egiuse.780987@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 1, "adults": 1, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-07-01", "departureDate": "2026-07-04", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 3, "phone": "+393278346926", "totalPrice": 145.96, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 23.71, "hostawayCommissionAmount": null, "cleaningFee": 40, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nBOOKING NOTE : Payment charge is EUR 1.9523", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": null, "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 87666268, "accountId": 181258, "listingMapId": 493047, "reservationId": 61397934, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 40, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-06-23 21:32:51", "updatedOn": "2026-06-23 21:32:51"}, {"id": 87666269, "accountId": 181258, "listingMapId": 493047, "reservationId": 61397934, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 9.04, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-06-23 21:32:51", "updatedOn": "2026-06-23 21:32:51"}, {"id": 87666270, "accountId": 181258, "listingMapId": 493047, "reservationId": 61397934, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 6.51, "currency": "EUR", "percentage": 7.2, "isIncluded":</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-06-08T11:43:49+00:00</t>
+          <t>2026-08-17T05:25:31+00:00</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>e1291d4e1f66034a</t>
+          <t>688b9d8a25f444ef</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>58269316</v>
+        <v>57852998</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{"id": 58269316, "listingMapId": 493047, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6942565816", "hostawayReservationId": "58269316", "channelReservationId": "6942565816", "externalPropertyId": "15480052", "externalUnitId": "1548005201", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "6DpKf0Bj", "guestPortalUrl": "https://guest-portal.hostaway.com/58269316/6DpKf0Bj", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-04-24 12:15:48", "pendingExpireDate": null, "guestName": "Antoine Kaikilekofe", "guestFirstName": "Antoine", "guestLastName": "Kaikilekofe", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "FR", "guestEmail": "akaiki.295425@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 2, "adults": 2, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-04-24", "departureDate": "2026-04-26", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 2, "phone": "+33662201326", "totalPrice": 110.64, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 18.07, "hostawayCommissionAmount": null, "cleaningFee": 40, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nBOOKING NOTE : Payment charge is EUR 1.4882", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 82355613, "accountId": 181258, "listingMapId": 493047, "reservationId": 58269316, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 40, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-24 12:17:12", "updatedOn": "2026-04-24 12:17:12"}, {"id": 82355614, "accountId": 181258, "listingMapId": 493047, "reservationId": 58269316, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 6.03, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-24 12:17:12", "updatedOn": "2026-04-24 12:17:12"}, {"id": 82355615, "accountId": 181258, "listingMapId": 493047, "reservationId": 58269316, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 4.34, "currency": "EUR", "percentage": 7.2, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-24 12:17:12", "updatedOn": "2026-04-24 12:17:12"}, {"id"</t>
+          <t>{"id": 57852998, "listingMapId": 480140, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6427282920", "hostawayReservationId": "57852998", "channelReservationId": "6427282920", "externalPropertyId": "15500360", "externalUnitId": "1550036001", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "SHF2KKIc", "guestPortalUrl": "https://guest-portal.hostaway.com/57852998/SHF2KKIc", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-04-17 14:40:27", "pendingExpireDate": null, "guestName": "blandine vaucher", "guestFirstName": "blandine", "guestLastName": "vaucher", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "FR", "guestEmail": "bvauch.215055@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 2, "adults": 2, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-06-28", "departureDate": "2026-07-03", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 5, "phone": null, "totalPrice": 514.16, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 82.61, "hostawayCommissionAmount": null, "cleaningFee": 55, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nBOOKING NOTE : Payment charge is EUR 6.8033", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "There is no meal option with this room.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": "16", "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": {"name": "Moderate", "channelId": 2005, "channelSpecificCode": "16", "longTerm": false, "cancellationPolicyItem": [{"refundAmount": 100, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": -432000, "event": "arrival"}]}, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 81773068, "accountId": 181258, "listingMapId": 480140, "reservationId": 57852998, "name": "Cleaning fee", "feeType": "guest", "externalReservationUnitId": null, "amount": 55, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-17 14:41:57", "updatedOn": "2026-04-17 14:41:57"}, {"id": 81773069, "accountId": 181258, "listingMapId": 480140, "reservationId": 57852998, "name": "VAT", "feeType": "guest", "externalReservationUnitId": null, "amount": 39.18, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-17 14:41:57", "updatedOn": "2026-04-17 14:41:57"}, {"id": 81773070, "accountId": 181258, "listingM</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-06-08T11:43:49+00:00</t>
+          <t>2026-08-17T05:25:32+00:00</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>84f431e0575b9c67</t>
+          <t>a5d6227d0ae25d26</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>58286525</v>
+        <v>57594520</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{"id": 58286525, "listingMapId": 480140, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5880212214", "hostawayReservationId": "58286525", "channelReservationId": "5880212214", "externalPropertyId": "15500360", "externalUnitId": "1550036001", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "ldZsk5KR", "guestPortalUrl": "https://guest-portal.hostaway.com/58286525/ldZsk5KR", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-04-24 19:17:58", "pendingExpireDate": null, "guestName": "Nathalie Course", "guestFirstName": "Nathalie", "guestLastName": "Course", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "FR", "guestEmail": "ncours.288445@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 6, "adults": 3, "children": 3, "infants": null, "pets": null, "arrivalDate": "2026-07-11", "departureDate": "2026-07-14", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 3, "phone": null, "totalPrice": 331.51, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 54.87, "hostawayCommissionAmount": null, "cleaningFee": 55, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nBOOKING NOTE : Payment charge is EUR 4.5185", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "There is no meal option with this room.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 82386383, "accountId": 181258, "listingMapId": 480140, "reservationId": 58286525, "name": "Cleaning fee", "feeType": "guest", "externalReservationUnitId": null, "amount": 55, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-24 19:19:18", "updatedOn": "2026-04-24 19:19:18"}, {"id": 82386384, "accountId": 181258, "listingMapId": 480140, "reservationId": 58286525, "name": "VAT", "feeType": "guest", "externalReservationUnitId": null, "amount": 24.34, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-24 19:19:18", "updatedOn": "2026-04-24 19:19:18"}, {"id": 82386385, "accountId": 181258, "listingMapId": 480140, "reservationId": 58286525, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 8.76, "currency": "EUR", "percentage": 7.2, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-24 19:19:18", "updatedOn": "2026-04-24 19:19:18"}, {"id": 82386386, "accountId": 181258, "listingM</t>
+          <t>{"id": 57594520, "listingMapId": 480139, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5471436537", "hostawayReservationId": "57594520", "channelReservationId": "5471436537", "externalPropertyId": "15499360", "externalUnitId": "1549936001", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "B7pcbRoX", "guestPortalUrl": "https://guest-portal.hostaway.com/57594520/B7pcbRoX", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-04-11 18:40:57", "pendingExpireDate": null, "guestName": "Maria Molloy", "guestFirstName": "Maria", "guestLastName": "Molloy", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "IE", "guestEmail": "mmollo.123335@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 4, "adults": 3, "children": 1, "infants": null, "pets": null, "arrivalDate": "2026-06-26", "departureDate": "2026-06-29", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 3, "phone": null, "totalPrice": 357.3, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 58.34, "hostawayCommissionAmount": null, "cleaningFee": 55, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nBOOKING NOTE : Payment charge is EUR 5.0021384", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "There is no meal option with this room.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": "16", "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": {"name": "Moderate", "channelId": 2005, "channelSpecificCode": "16", "longTerm": false, "cancellationPolicyItem": [{"refundAmount": 100, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": -432000, "event": "arrival"}]}, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 80671540, "accountId": 181258, "listingMapId": 480139, "reservationId": 57594520, "name": "Cleaning fee", "feeType": "guest", "externalReservationUnitId": null, "amount": 55, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-11 18:42:24", "updatedOn": "2026-04-11 18:42:24"}, {"id": 80671541, "accountId": 181258, "listingMapId": 480139, "reservationId": 57594520, "name": "VAT", "feeType": "guest", "externalReservationUnitId": null, "amount": 26.2, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-11 18:42:24", "updatedOn": "2026-04-11 18:42:24"}, {"id": 80671542, "accountId": 181258, "listingMapId": 480</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-06-08T11:43:50+00:00</t>
+          <t>2026-08-17T05:25:33+00:00</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>07f6ed751996a056</t>
+          <t>3063cc4376302364</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>58274276</v>
+        <v>60879784</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{"id": 58274276, "listingMapId": 480139, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5508646639", "hostawayReservationId": "58274276", "channelReservationId": "5508646639", "externalPropertyId": "15499360", "externalUnitId": "1549936001", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "7p5IE8JG", "guestPortalUrl": "https://guest-portal.hostaway.com/58274276/7p5IE8JG", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-04-24 14:05:28", "pendingExpireDate": null, "guestName": "Clarence Malbrouck", "guestFirstName": "Clarence", "guestLastName": "Malbrouck", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "FR", "guestEmail": "cmalbr.339983@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 5, "adults": 5, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-07-28", "departureDate": "2026-08-05", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 8, "phone": null, "totalPrice": 767.74, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 123.07, "hostawayCommissionAmount": null, "cleaningFee": 55, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\n\nBOOKING NOTE : Payment charge is EUR 10.1353", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "There is no meal option with this room.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 82363264, "accountId": 181258, "listingMapId": 480139, "reservationId": 58274276, "name": "Cleaning fee", "feeType": "guest", "externalReservationUnitId": null, "amount": 55, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-24 14:06:52", "updatedOn": "2026-04-24 14:06:52"}, {"id": 82363265, "accountId": 181258, "listingMapId": 480139, "reservationId": 58274276, "name": "VAT", "feeType": "guest", "externalReservationUnitId": null, "amount": 60.81, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-24 14:06:52", "updatedOn": "2026-04-24 14:06:52"}, {"id": 82363266, "accountId": 181258, "listingMapId": 480139, "reservationId": 58274276, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 43.79, "currency": "EUR", "percentage": 7.2, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-24 14:06:52", "updatedOn": "2026-04-24 14:06:52"}, {"id": 82363267, "accountId": 181</t>
+          <t>{"id": 60879784, "listingMapId": 480139, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5594666915", "hostawayReservationId": "60879784", "channelReservationId": "5594666915", "externalPropertyId": "15499360", "externalUnitId": "1549936001", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "yIr0YWZB", "guestPortalUrl": "https://guest-portal.hostaway.com/60879784/yIr0YWZB", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-06-13 00:09:52", "pendingExpireDate": null, "guestName": "Abdel-Farid SALAMI", "guestFirstName": "Abdel-Farid", "guestLastName": "SALAMI", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "BJ", "guestEmail": "asalam.982636@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 2, "adults": 2, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-06-16", "departureDate": "2026-06-26", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 10, "phone": "+229199196666", "totalPrice": 707.06, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 113.39, "hostawayCommissionAmount": null, "cleaningFee": 55, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nBOOKING NOTE : Payment charge is EUR 9.338", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "There is no meal option with this room.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": "16", "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": {"name": "Moderate", "channelId": 2005, "channelSpecificCode": "16", "longTerm": false, "cancellationPolicyItem": [{"refundAmount": 100, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": -432000, "event": "arrival"}]}, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 86681446, "accountId": 181258, "listingMapId": 480139, "reservationId": 60879784, "name": "Cleaning fee", "feeType": "guest", "externalReservationUnitId": null, "amount": 55, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-06-13 00:11:10", "updatedOn": "2026-06-13 00:11:10"}, {"id": 86681447, "accountId": 181258, "listingMapId": 480139, "reservationId": 60879784, "name": "VAT", "feeType": "guest", "externalReservationUnitId": null, "amount": 55.64, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-06-13 00:11:10", "updatedOn": "2026-06-13 00:11:10"}, {"id": 86681448, "accountId": 1</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-06-08T11:43:51+00:00</t>
+          <t>2026-08-17T05:25:33+00:00</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>da1a89c4c81f4d0a</t>
+          <t>4a021dd23a993a06</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>57301034</v>
+        <v>60299082</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{"id": 57301034, "listingMapId": 493047, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6460756517", "hostawayReservationId": "57301034", "channelReservationId": "6460756517", "externalPropertyId": "15480052", "externalUnitId": "1548005201", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "ditoz8G4", "guestPortalUrl": "https://guest-portal.hostaway.com/57301034/ditoz8G4", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-04-05 11:51:14", "pendingExpireDate": null, "guestName": "Lamnaddaf Rania", "guestFirstName": "Lamnaddaf", "guestLastName": "Rania", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": "", "guestCountry": "FR", "guestEmail": "lrania.690109@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 2, "adults": 1, "children": 1, "infants": null, "pets": null, "arrivalDate": "2026-04-19", "departureDate": "2026-04-24", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 5, "phone": "+33754879782", "totalPrice": 212.05, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 35.12, "hostawayCommissionAmount": null, "cleaningFee": 40, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nBOOKING NOTE : Payment charge is EUR 2.9687336\nApproximate time of arrival: between 16:00 and 17:00", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 79744013, "accountId": 181258, "listingMapId": 493047, "reservationId": 57301034, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 40, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-05 11:52:38", "updatedOn": "2026-04-05 11:52:38"}, {"id": 79744014, "accountId": 181258, "listingMapId": 493047, "reservationId": 57301034, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 15.15, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-05 11:52:38", "updatedOn": "2026-04-05 11:52:38"}, {"id": 79744015, "accountId": 181258, "listingMapId": 493047, "reservationId": 57301034, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 5.45, "currency": "EUR", "percentage": 7.2, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-05 11:52:3</t>
+          <t>{"id": 60299082, "listingMapId": 480137, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5843937748", "hostawayReservationId": "60299082", "channelReservationId": "5843937748", "externalPropertyId": "15950709", "externalUnitId": "1595070901", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "HqQHlU8d", "guestPortalUrl": "https://guest-portal.hostaway.com/60299082/HqQHlU8d", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-06-01 21:16:46", "pendingExpireDate": null, "guestName": "Sonia Naomi Vazquez Valdes", "guestFirstName": "Sonia", "guestLastName": "Naomi Vazquez Valdes", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": "", "guestCountry": "ES", "guestEmail": "svalde.190088@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 3, "adults": 3, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-06-23", "departureDate": "2026-06-25", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 2, "phone": "+341819580", "totalPrice": 230.97, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 37.55, "hostawayCommissionAmount": null, "cleaningFee": 67, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nBOOKING NOTE : Payment charge is EUR 3.23358", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": "16", "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": {"name": "Moderate", "channelId": 2005, "channelSpecificCode": "16", "longTerm": false, "cancellationPolicyItem": [{"refundAmount": 100, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": -432000, "event": "arrival"}]}, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 85699110, "accountId": 181258, "listingMapId": 480137, "reservationId": 60299082, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 67, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-06-01 21:18:26", "updatedOn": "2026-06-01 21:18:26"}, {"id": 85699111, "accountId": 181258, "listingMapId": 480137, "reservationId": 60299082, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 13.99, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-06-01 21:18:26", "updatedOn": "2026-06-01 21:18:26"</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-06-08T11:43:52+00:00</t>
+          <t>2026-08-17T05:25:34+00:00</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>20b589c45bd0aa08</t>
+          <t>8c578665dc59b421</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>58033344</v>
+        <v>59334748</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{"id": 58033344, "listingMapId": 480139, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6122094341", "hostawayReservationId": "58033344", "channelReservationId": "6122094341", "externalPropertyId": "15499360", "externalUnitId": "1549936001", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "_OAfCrm1", "guestPortalUrl": "https://guest-portal.hostaway.com/58033344/_OAfCrm1", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-04-19 16:52:50", "pendingExpireDate": null, "guestName": "Marije Moreau", "guestFirstName": "Marije", "guestLastName": "Moreau", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": "", "guestCountry": "FR", "guestEmail": "mmorea.188123@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 5, "adults": 3, "children": 2, "infants": null, "pets": null, "arrivalDate": "2026-06-10", "departureDate": "2026-06-14", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 4, "phone": null, "totalPrice": 458.71, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 75.39, "hostawayCommissionAmount": null, "cleaningFee": 55, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\n\nBOOKING NOTE : Payment charge is EUR 6.2083", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "There is no meal option with this room.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 81935560, "accountId": 181258, "listingMapId": 480139, "reservationId": 58033344, "name": "Cleaning fee", "feeType": "guest", "externalReservationUnitId": null, "amount": 55, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-19 16:54:29", "updatedOn": "2026-04-19 16:54:29"}, {"id": 81935561, "accountId": 181258, "listingMapId": 480139, "reservationId": 58033344, "name": "VAT", "feeType": "guest", "externalReservationUnitId": null, "amount": 35.31, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-19 16:54:29", "updatedOn": "2026-04-19 16:54:29"}, {"id": 81935562, "accountId": 181258, "listingMapId": 480139, "reservationId": 58033344, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 15.26, "currency": "EUR", "percentage": 7.2, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-19 16:54:29", "updatedOn": "2026-04-19 16:54:29"}, {"id": 81935563, "accountId": 181258, "listingMap</t>
+          <t>{"id": 59334748, "listingMapId": 480137, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5206720926", "hostawayReservationId": "59334748", "channelReservationId": "5206720926", "externalPropertyId": "15950709", "externalUnitId": "1595070901", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "43pRRoGg", "guestPortalUrl": "https://guest-portal.hostaway.com/59334748/43pRRoGg", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-05-15 14:16:05", "pendingExpireDate": null, "guestName": "Julien Catala", "guestFirstName": "Julien", "guestLastName": "Catala", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": "", "guestCountry": "FR", "guestEmail": "jcatal.461010@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 3, "adults": 3, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-06-19", "departureDate": "2026-06-21", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 2, "phone": "+33666203757", "totalPrice": 254.95, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 41.38, "hostawayCommissionAmount": null, "cleaningFee": 67, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nBOOKING NOTE : Payment charge is EUR 3.5693\nApproximate time of arrival: between 16:00 and 17:00", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": "16", "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": {"name": "Moderate", "channelId": 2005, "channelSpecificCode": "16", "longTerm": false, "cancellationPolicyItem": [{"refundAmount": 100, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": -432000, "event": "arrival"}]}, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 84175606, "accountId": 181258, "listingMapId": 480137, "reservationId": 59334748, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 67, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-05-15 14:17:36", "updatedOn": "2026-05-15 14:17:36"}, {"id": 84175607, "accountId": 181258, "listingMapId": 480137, "reservationId": 59334748, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 16.04, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-05-15 14:17:36", "upda</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-06-08T11:43:55+00:00</t>
+          <t>2026-08-17T05:25:35+00:00</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>9edad70f4de6985e</t>
+          <t>3ce64a5cebfbdf38</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>56163020</v>
+        <v>60799881</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{"id": 56163020, "listingMapId": 493047, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5177336485", "hostawayReservationId": "56163020", "channelReservationId": "5177336485", "externalPropertyId": "15480052", "externalUnitId": "1548005201", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "g19FJnTa", "guestPortalUrl": "https://guest-portal.hostaway.com/56163020/g19FJnTa", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-03-16 12:23:41", "pendingExpireDate": null, "guestName": "Nelly Tuffreau", "guestFirstName": "Nelly", "guestLastName": "Tuffreau", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "FR", "guestEmail": "ntuffr.226196@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 2, "adults": 2, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-04-16", "departureDate": "2026-04-19", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 3, "phone": "+33698479128", "totalPrice": 145.05, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 23.56, "hostawayCommissionAmount": null, "cleaningFee": 40, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\n\nBOOKING NOTE : Payment charge is EUR 2.0307532", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 77888422, "accountId": 181258, "listingMapId": 493047, "reservationId": 56163020, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 40, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-16 12:25:03", "updatedOn": "2026-03-16 12:25:03"}, {"id": 77888423, "accountId": 181258, "listingMapId": 493047, "reservationId": 56163020, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 8.96, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-16 12:25:03", "updatedOn": "2026-03-16 12:25:03"}, {"id": 77888424, "accountId": 181258, "listingMapId": 493047, "reservationId": 56163020, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 6.45, "currency": "EUR", "percentage": 7.2, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-16 12:25:03", "updatedOn": "2026-03-16 12:25:03"}, {"id": 778</t>
+          <t>{"id": 60799881, "listingMapId": 493047, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6503765721", "hostawayReservationId": "60799881", "channelReservationId": "6503765721", "externalPropertyId": "15480052", "externalUnitId": "1548005201", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "VlpJ7nmH", "guestPortalUrl": "https://guest-portal.hostaway.com/60799881/VlpJ7nmH", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-06-11 12:29:50", "pendingExpireDate": null, "guestName": "Niklas Gunther", "guestFirstName": "Niklas", "guestLastName": "Gunther", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "DE", "guestEmail": "ngunth.593795@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 2, "adults": 2, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-06-16", "departureDate": "2026-06-21", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 5, "phone": "+4915567461010", "totalPrice": 217.5, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 35.12, "hostawayCommissionAmount": null, "cleaningFee": 40, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nBOOKING NOTE : Payment charge is EUR 2.8924", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": null, "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 86546958, "accountId": 181258, "listingMapId": 493047, "reservationId": 60799881, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 40, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-06-11 12:31:11", "updatedOn": "2026-06-11 12:31:11"}, {"id": 86546959, "accountId": 181258, "listingMapId": 493047, "reservationId": 60799881, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 15.15, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-06-11 12:31:11", "updatedOn": "2026-06-11 12:31:11"}, {"id": 86546960, "accountId": 181258, "listingMapId": 493047, "reservationId": 60799881, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 10.9, "currency": "EUR", "percentage": 7.2, "isIncluded": 1, "</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-06-08T11:43:56+00:00</t>
+          <t>2026-08-17T05:25:36+00:00</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>07db7b06ecbcbd8e</t>
+          <t>232bb75472a84392</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>57852998</v>
+        <v>60296863</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{"id": 57852998, "listingMapId": 480140, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6427282920", "hostawayReservationId": "57852998", "channelReservationId": "6427282920", "externalPropertyId": "15500360", "externalUnitId": "1550036001", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "SHF2KKIc", "guestPortalUrl": "https://guest-portal.hostaway.com/57852998/SHF2KKIc", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-04-17 14:40:27", "pendingExpireDate": null, "guestName": "blandine vaucher", "guestFirstName": "blandine", "guestLastName": "vaucher", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "FR", "guestEmail": "bvauch.215055@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 2, "adults": 2, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-06-28", "departureDate": "2026-07-03", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 5, "phone": null, "totalPrice": 514.16, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 82.61, "hostawayCommissionAmount": null, "cleaningFee": 55, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nBOOKING NOTE : Payment charge is EUR 6.8033", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "There is no meal option with this room.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 81773068, "accountId": 181258, "listingMapId": 480140, "reservationId": 57852998, "name": "Cleaning fee", "feeType": "guest", "externalReservationUnitId": null, "amount": 55, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-17 14:41:57", "updatedOn": "2026-04-17 14:41:57"}, {"id": 81773069, "accountId": 181258, "listingMapId": 480140, "reservationId": 57852998, "name": "VAT", "feeType": "guest", "externalReservationUnitId": null, "amount": 39.18, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-17 14:41:57", "updatedOn": "2026-04-17 14:41:57"}, {"id": 81773070, "accountId": 181258, "listingMapId": 480140, "reservationId": 57852998, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 28.21, "currency": "EUR", "percentage": 7.2, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-17 14:41:57", "updatedOn": "2026-04-17 14:41:57"}, {"id": 81773071, "accountId": 181258, "li</t>
+          <t>{"id": 60296863, "listingMapId": 480140, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5075416435", "hostawayReservationId": "60296863", "channelReservationId": "5075416435", "externalPropertyId": "15500360", "externalUnitId": "1550036001", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "lmwP56yj", "guestPortalUrl": "https://guest-portal.hostaway.com/60296863/lmwP56yj", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-06-01 20:34:45", "pendingExpireDate": null, "guestName": "Rossen Ploskov", "guestFirstName": "Rossen", "guestLastName": "Ploskov", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "BG", "guestEmail": "rplosk.904645@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 3, "adults": 3, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-06-14", "departureDate": "2026-06-21", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 7, "phone": "+359896700987", "totalPrice": 638.23, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 102.41, "hostawayCommissionAmount": null, "cleaningFee": 55, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nBOOKING NOTE : Payment charge is EUR 8.4336", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "There is no meal option with this room.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": "16", "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": {"name": "Moderate", "channelId": 2005, "channelSpecificCode": "16", "longTerm": false, "cancellationPolicyItem": [{"refundAmount": 100, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": -432000, "event": "arrival"}]}, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 85695206, "accountId": 181258, "listingMapId": 480140, "reservationId": 60296863, "name": "Cleaning fee", "feeType": "guest", "externalReservationUnitId": null, "amount": 55, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-06-01 20:36:25", "updatedOn": "2026-06-01 20:36:25"}, {"id": 85695207, "accountId": 181258, "listingMapId": 480140, "reservationId": 60296863, "name": "VAT", "feeType": "guest", "externalReservationUnitId": null, "amount": 49.76, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-06-01 20:36:25", "updatedOn": "2026-06-01 20:36:25"}, {"id": 85695208, "accountId": 181258, "</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-06-08T11:43:57+00:00</t>
+          <t>2026-08-17T05:25:37+00:00</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>a5d6227d0ae25d26</t>
+          <t>d8cac24f80105f44</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>56052100</v>
+        <v>60330887</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{"id": 56052100, "listingMapId": 480139, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5385306861", "hostawayReservationId": "56052100", "channelReservationId": "5385306861", "externalPropertyId": "15499360", "externalUnitId": "1549936001", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "Xmn9RdqR", "guestPortalUrl": "https://guest-portal.hostaway.com/56052100/Xmn9RdqR", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-03-14 12:16:27", "pendingExpireDate": null, "guestName": "Gillian Douglass", "guestFirstName": "Gillian", "guestLastName": "Douglass", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "GB", "guestEmail": "gdougl.477450@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 2, "adults": 2, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-04-11", "departureDate": "2026-04-14", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 3, "phone": "+447878620366", "totalPrice": 361.85, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 58.31, "hostawayCommissionAmount": null, "cleaningFee": 55, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\n\nBOOKING NOTE : Payment charge is EUR 5.0659126", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "There is no meal option with this room.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 77716640, "accountId": 181258, "listingMapId": 480139, "reservationId": 56052100, "name": "Cleaning fee", "feeType": "guest", "externalReservationUnitId": null, "amount": 55, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-14 12:33:45", "updatedOn": "2026-03-14 12:33:45"}, {"id": 77716641, "accountId": 181258, "listingMapId": 480139, "reservationId": 56052100, "name": "VAT", "feeType": "guest", "externalReservationUnitId": null, "amount": 26.18, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-14 12:33:45", "updatedOn": "2026-03-14 12:33:45"}, {"id": 77716642, "accountId": 181258, "listingMapId": 480139, "reservationId": 56052100, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 18.85, "currency": "EUR", "percentage": 7.2, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-14 12:33:45", "updatedOn": "2026-03-14 12:33:45"}, {"id": 77716643, "account</t>
+          <t>{"id": 60330887, "listingMapId": 480137, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6940784720", "hostawayReservationId": "60330887", "channelReservationId": "6940784720", "externalPropertyId": "15950709", "externalUnitId": "1595070901", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "xGpwHPEM", "guestPortalUrl": "https://guest-portal.hostaway.com/60330887/xGpwHPEM", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-06-02 12:51:58", "pendingExpireDate": null, "guestName": "Thierry OLLIVIER", "guestFirstName": "Thierry", "guestLastName": "OLLIVIER", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": "", "guestCountry": "FR", "guestEmail": "tolliv.187487@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 3, "adults": 3, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-06-10", "departureDate": "2026-06-15", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 5, "phone": "+33781244870", "totalPrice": 460.15, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 74.12, "hostawayCommissionAmount": null, "cleaningFee": 67, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nReservation has a cancellation grace period. Do not charge if cancelled before 2026-06-03 14:51:58\nApproximate time of arrival: between 19:00 and 20:00\nBOOKING NOTE : Payment charge is EUR 6.4421", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": "16", "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": {"name": "Moderate", "channelId": 2005, "channelSpecificCode": "16", "longTerm": false, "cancellationPolicyItem": [{"refundAmount": 100, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": -432000, "event": "arrival"}]}, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 85749347, "accountId": 181258, "listingMapId": 480137, "reservationId": 60330887, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 67, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-06-02 12:53:46", "updatedOn": "2026-06-02 12:53:46"}, {"id": 85749348, "accountId": 181258, "listingMapId": 480137, "reservationId": 60330887, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 33.55, "currency": "EUR", "percentage": 10, "isIn</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-06-08T11:43:58+00:00</t>
+          <t>2026-08-17T05:25:39+00:00</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>8560ed14c2f934dd</t>
+          <t>f7f8fa109a23ab06</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>56916115</v>
+        <v>59599320</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>{"id": 56916115, "listingMapId": 480137, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6962385915", "hostawayReservationId": "56916115", "channelReservationId": "6962385915", "externalPropertyId": "15950709", "externalUnitId": "1595070901", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "SAYBl6Pk", "guestPortalUrl": "https://guest-portal.hostaway.com/56916115/SAYBl6Pk", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-03-29 13:37:24", "pendingExpireDate": null, "guestName": "Patrick BOURGON", "guestFirstName": "Patrick", "guestLastName": "BOURGON", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": "", "guestCountry": "FR", "guestEmail": "pbourg.657327@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 2, "adults": 2, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-04-10", "departureDate": "2026-04-13", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 3, "phone": "+33681453845", "totalPrice": 216.33, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 34.52, "hostawayCommissionAmount": null, "cleaningFee": null, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nReservation has a cancellation grace period. Do not charge if cancelled before 2026-03-30 15:37:24\nBOOKING NOTE : Payment charge is EUR 3.0286186\nApproximate time of arrival: between 16:00 and 17:00", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 79045657, "accountId": 181258, "listingMapId": 480137, "reservationId": 56916115, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 18.46, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-29 13:39:00", "updatedOn": "2026-03-29 13:39:00"}, {"id": 79045658, "accountId": 181258, "listingMapId": 480137, "reservationId": 56916115, "name": "taxe de séjour", "feeType": "guest", "externalReservationUnitId": null, "amount": 13.29, "currency": "EUR", "percentage": 7.2, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-29 13:39:00", "updatedOn": "2026-03-29 13:39:00"}, {"id": 79045659, "accountId": 181258, "listingMapId": 480137, "reservationId": 56916115, "name": "TVA", "feeType": "hotel", "externalReservationUnitId": null, "amount": 18.46, "currency": "EUR", "percentage": 10, "isIncluded": 1,</t>
+          <t>{"id": 59599320, "listingMapId": 493047, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6920404227", "hostawayReservationId": "59599320", "channelReservationId": "6920404227", "externalPropertyId": "15480052", "externalUnitId": "1548005201", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "gQ1LWbUO", "guestPortalUrl": "https://guest-portal.hostaway.com/59599320/gQ1LWbUO", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-05-18 14:26:21", "pendingExpireDate": null, "guestName": "Joan Jordan Tejedor", "guestFirstName": "Joan", "guestLastName": "Jordan Tejedor", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "ES", "guestEmail": "jtejed.761022@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 1, "adults": 1, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-06-13", "departureDate": "2026-06-15", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 2, "phone": "+34630393387", "totalPrice": 124.22, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 20.24, "hostawayCommissionAmount": null, "cleaningFee": 40, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nBOOKING NOTE : Payment charge is EUR 1.6667", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": null, "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 84444903, "accountId": 181258, "listingMapId": 493047, "reservationId": 59599320, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 40, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-05-18 14:29:13", "updatedOn": "2026-05-18 14:29:13"}, {"id": 84444904, "accountId": 181258, "listingMapId": 493047, "reservationId": 59599320, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 7.19, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-05-18 14:29:13", "updatedOn": "2026-05-18 14:29:13"}, {"id": 84444905, "accountId": 181258, "listingMapId": 493047, "reservationId": 59599320, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 5.17, "currency": "EUR", "percentage": 7.19, "isInclud</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-06-08T11:43:59+00:00</t>
+          <t>2026-08-17T05:25:40+00:00</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>95e1e6530d6c1fe9</t>
+          <t>c63a8fcad76c1d54</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>57614911</v>
+        <v>58033344</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>{"id": 57614911, "listingMapId": 480137, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6024970652", "hostawayReservationId": "57614911", "channelReservationId": "6024970652", "externalPropertyId": "15950709", "externalUnitId": "1595070901", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "kca0P8JK", "guestPortalUrl": "https://guest-portal.hostaway.com/57614911/kca0P8JK", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-04-12 09:47:05", "pendingExpireDate": null, "guestName": "elmaazouzi lamia", "guestFirstName": "elmaazouzi", "guestLastName": "lamia", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": "", "guestCountry": "MA", "guestEmail": "elamia.308766@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 6, "adults": 3, "children": 3, "infants": null, "pets": null, "arrivalDate": "2026-07-21", "departureDate": "2026-07-25", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 4, "phone": "+212698183000", "totalPrice": 420.19, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 69.53, "hostawayCommissionAmount": null, "cleaningFee": 67, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\n\nBOOKING NOTE : Payment charge is EUR 5.8826978", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 80778549, "accountId": 181258, "listingMapId": 480137, "reservationId": 57614911, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 67, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-12 09:51:32", "updatedOn": "2026-04-12 09:51:32"}, {"id": 80778551, "accountId": 181258, "listingMapId": 480137, "reservationId": 57614911, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 31.09, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-12 09:51:32", "updatedOn": "2026-04-12 09:51:32"}, {"id": 80778553, "accountId": 181258, "listingMapId": 480137, "reservationId": 57614911, "name": "taxe de séjour", "feeType": "guest", "externalReservationUnitId": null, "amount": 11.19, "currency": "EUR", "percentage": 7.2, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-12 09:51:32", "updatedOn": "2026-04-12 09:51:32"}, {"id": 80778555,</t>
+          <t>{"id": 58033344, "listingMapId": 480139, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6122094341", "hostawayReservationId": "58033344", "channelReservationId": "6122094341", "externalPropertyId": "15499360", "externalUnitId": "1549936001", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "_OAfCrm1", "guestPortalUrl": "https://guest-portal.hostaway.com/58033344/_OAfCrm1", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-04-19 16:52:50", "pendingExpireDate": null, "guestName": "Marije Moreau", "guestFirstName": "Marije", "guestLastName": "Moreau", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": "", "guestCountry": "FR", "guestEmail": "mmorea.188123@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 5, "adults": 3, "children": 2, "infants": null, "pets": null, "arrivalDate": "2026-06-10", "departureDate": "2026-06-14", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 4, "phone": null, "totalPrice": 458.71, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 75.39, "hostawayCommissionAmount": null, "cleaningFee": 55, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\n\nBOOKING NOTE : Payment charge is EUR 6.2083", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "There is no meal option with this room.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": "16", "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": {"name": "Moderate", "channelId": 2005, "channelSpecificCode": "16", "longTerm": false, "cancellationPolicyItem": [{"refundAmount": 100, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": -432000, "event": "arrival"}]}, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 81935560, "accountId": 181258, "listingMapId": 480139, "reservationId": 58033344, "name": "Cleaning fee", "feeType": "guest", "externalReservationUnitId": null, "amount": 55, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-19 16:54:29", "updatedOn": "2026-04-19 16:54:29"}, {"id": 81935561, "accountId": 181258, "listingMapId": 480139, "reservationId": 58033344, "name": "VAT", "feeType": "guest", "externalReservationUnitId": null, "amount": 35.31, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-19 16:54:29", "updatedOn": "2026-04-19 16:54:29"}, {"id": 81935562, "accountId": 181258, "listingMapId": 4</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-06-08T11:44:00+00:00</t>
+          <t>2026-08-17T05:25:41+00:00</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>55b2da18d712a44c</t>
+          <t>9edad70f4de6985e</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>57280196</v>
+        <v>60550389</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"id": 57280196, "listingMapId": 493047, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5221473980", "hostawayReservationId": "57280196", "channelReservationId": "5221473980", "externalPropertyId": "15480052", "externalUnitId": "1548005201", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "GdhXR44d", "guestPortalUrl": "https://guest-portal.hostaway.com/57280196/GdhXR44d", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-04-04 19:51:07", "pendingExpireDate": null, "guestName": "Andrea MANIVONG", "guestFirstName": "Andrea", "guestLastName": "MANIVONG", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": "", "guestCountry": "FR", "guestEmail": "amaniv.555116@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 2, "adults": 2, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-04-06", "departureDate": "2026-04-12", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 6, "phone": "+33760437425", "totalPrice": 251.92, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 40.61, "hostawayCommissionAmount": null, "cleaningFee": 40, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\n\nBOOKING NOTE : Payment charge is EUR 3.5268646", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 79666912, "accountId": 181258, "listingMapId": 493047, "reservationId": 57280196, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 40, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-04 19:52:24", "updatedOn": "2026-04-04 19:52:24"}, {"id": 79666913, "accountId": 181258, "listingMapId": 493047, "reservationId": 57280196, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 18.08, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-04 19:52:24", "updatedOn": "2026-04-04 19:52:24"}, {"id": 79666914, "accountId": 181258, "listingMapId": 493047, "reservationId": 57280196, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 13.02, "currency": "EUR", "percentage": 7.2, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-04 19:52:24", "updatedOn": "2026-04-04 19:52:24"}, {"id": </t>
+          <t xml:space="preserve">{"id": 60550389, "listingMapId": 493047, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5566472242", "hostawayReservationId": "60550389", "channelReservationId": "5566472242", "externalPropertyId": "15480052", "externalUnitId": "1548005201", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "dY8FibiL", "guestPortalUrl": "https://guest-portal.hostaway.com/60550389/dY8FibiL", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-06-06 15:12:58", "pendingExpireDate": null, "guestName": "Hugues Eric LEDOT", "guestFirstName": "Hugues", "guestLastName": "Eric LEDOT", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "FR", "guestEmail": "hledot.933397@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 2, "adults": 2, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-06-11", "departureDate": "2026-06-13", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 2, "phone": "+33651754934", "totalPrice": 110.64, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 18.07, "hostawayCommissionAmount": null, "cleaningFee": 40, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nBOOKING NOTE : Payment charge is EUR 1.4882", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": null, "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 86109993, "accountId": 181258, "listingMapId": 493047, "reservationId": 60550389, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 40, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-06-06 15:14:29", "updatedOn": "2026-06-06 15:14:29"}, {"id": 86109994, "accountId": 181258, "listingMapId": 493047, "reservationId": 60550389, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 6.03, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-06-06 15:14:29", "updatedOn": "2026-06-06 15:14:29"}, {"id": 86109995, "accountId": 181258, "listingMapId": 493047, "reservationId": 60550389, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 4.34, "currency": "EUR", "percentage": 7.2, "isIncluded": </t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-06-08T11:44:01+00:00</t>
+          <t>2026-08-17T05:25:42+00:00</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>5c0c797cc559f1fb</t>
+          <t>9662fad81c8052e4</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>57594520</v>
+        <v>60797196</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>{"id": 57594520, "listingMapId": 480139, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5471436537", "hostawayReservationId": "57594520", "channelReservationId": "5471436537", "externalPropertyId": "15499360", "externalUnitId": "1549936001", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "B7pcbRoX", "guestPortalUrl": "https://guest-portal.hostaway.com/57594520/B7pcbRoX", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-04-11 18:40:57", "pendingExpireDate": null, "guestName": "Maria Molloy", "guestFirstName": "Maria", "guestLastName": "Molloy", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "IE", "guestEmail": "mmollo.123335@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 4, "adults": 3, "children": 1, "infants": null, "pets": null, "arrivalDate": "2026-06-26", "departureDate": "2026-06-29", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 3, "phone": null, "totalPrice": 357.3, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 58.34, "hostawayCommissionAmount": null, "cleaningFee": 55, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nBOOKING NOTE : Payment charge is EUR 5.0021384", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "There is no meal option with this room.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 80671540, "accountId": 181258, "listingMapId": 480139, "reservationId": 57594520, "name": "Cleaning fee", "feeType": "guest", "externalReservationUnitId": null, "amount": 55, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-11 18:42:24", "updatedOn": "2026-04-11 18:42:24"}, {"id": 80671541, "accountId": 181258, "listingMapId": 480139, "reservationId": 57594520, "name": "VAT", "feeType": "guest", "externalReservationUnitId": null, "amount": 26.2, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-11 18:42:24", "updatedOn": "2026-04-11 18:42:24"}, {"id": 80671542, "accountId": 181258, "listingMapId": 480139, "reservationId": 57594520, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 14.15, "currency": "EUR", "percentage": 7.2, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-11 18:42:24", "updatedOn": "2026-04-11 18:42:24"}, {"id": 80671543, "accountId": 181258, "listingMapId</t>
+          <t>{"id": 60797196, "listingMapId": 480141, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5612618561", "hostawayReservationId": "60797196", "channelReservationId": "5612618561", "externalPropertyId": "15971299", "externalUnitId": "1597129901", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "rRsF1zkq", "guestPortalUrl": "https://guest-portal.hostaway.com/60797196/rRsF1zkq", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 1, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-04-17 16:29:33", "pendingExpireDate": null, "guestName": "Sylvie BOULANGER", "guestFirstName": "Sylvie", "guestLastName": "BOULANGER", "guestExternalAccountId": null, "guestZipCode": null, "guestAddress": null, "guestCity": null, "guestCountry": null, "guestEmail": null, "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 5, "adults": 5, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-09-24", "departureDate": "2026-09-26", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 2, "phone": null, "totalPrice": 440, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": null, "hostawayCommissionAmount": null, "cleaningFee": null, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Unknown", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": null, "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "There is no meal option with this room.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": "14", "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": {"name": "Firm", "channelId": 2005, "channelSpecificCode": "14", "longTerm": false, "cancellationPolicyItem": [{"refundAmount": 100, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": -1209600, "event": "arrival"}]}, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [], "reservationUnit": [], "insertedOn": "2026-06-11 11:03:42", "updatedOn": "2026-06-11 11:03:42", "latestActivityOn": "2026-06-11 11:03:42", "customerUserId": null, "guestLocale": null, "localeForMessaging": null, "localeForMessagingSource": null, "listingCustomFields": null, "rentalAgreementFileUrl": null, "reservationAgreement": "not_required", "financeField": [{"id": 258061545, "units": 1, "listingFeeSettingId": null, "type": "accommodation", "name": "baseRate", "title": "Base rate", "alias": null, "quantity": null, "value": 440, "isIncludedInTotalPrice": 1, "isOverriddenByUser": 0, "isMandatory": 1, "isQuantitySelectable": 0, "isDeleted": 0, "total": 440}, {"id": 258061546, "units": 1, "listingFeeSettingId": null, "type": "totals", "name": "totalPriceFromChannel", "title": "Total price from channel", "alias": null, "quantity": null, "value": 440, "isIncludedI</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-06-08T11:44:02+00:00</t>
+          <t>2026-08-17T05:25:43+00:00</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>3063cc4376302364</t>
+          <t>39deeea0e14754fd</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>57088437</v>
+        <v>60438998</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>{"id": 57088437, "listingMapId": 480137, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5931665862", "hostawayReservationId": "57088437", "channelReservationId": "5931665862", "externalPropertyId": "15950709", "externalUnitId": "1595070901", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "PY_HxToc", "guestPortalUrl": "https://guest-portal.hostaway.com/57088437/PY_HxToc", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-03-31 15:55:34", "pendingExpireDate": null, "guestName": "SOULIE ANTHONY GUILLAUME CHOQUEREAU", "guestFirstName": "SOULIE", "guestLastName": "ANTHONY GUILLAUME CHOQUEREAU", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "FR", "guestEmail": "santho.342426@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 2, "adults": 2, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-04-07", "departureDate": "2026-04-09", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 2, "phone": "+33612571421", "totalPrice": 140, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 22.34, "hostawayCommissionAmount": null, "cleaningFee": null, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\n\nBOOKING NOTE : Payment charge is EUR 1.9600098", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 79247757, "accountId": 181258, "listingMapId": 480137, "reservationId": 57088437, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 11.95, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-31 15:56:59", "updatedOn": "2026-03-31 15:56:59"}, {"id": 79247758, "accountId": 181258, "listingMapId": 480137, "reservationId": 57088437, "name": "taxe de séjour", "feeType": "guest", "externalReservationUnitId": null, "amount": 8.6, "currency": "EUR", "percentage": 7.2, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-31 15:56:59", "updatedOn": "2026-03-31 15:56:59"}, {"id": 79247759, "accountId": 181258, "listingMapId": 480137, "reservationId": 57088437, "name": "TVA", "feeType": "hotel", "externalReservationUnitId": null, "amount": 11.95, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-31 15:56:59", "updatedOn": "2026-03-31 1</t>
+          <t>{"id": 60438998, "listingMapId": 493047, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5024614275", "hostawayReservationId": "60438998", "channelReservationId": "5024614275", "externalPropertyId": "15480052", "externalUnitId": "1548005201", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "TJPf3N4D", "guestPortalUrl": "https://guest-portal.hostaway.com/60438998/TJPf3N4D", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-06-04 09:48:50", "pendingExpireDate": null, "guestName": "Emmanuel Benard", "guestFirstName": "Emmanuel", "guestLastName": "Benard", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "FR", "guestEmail": "ebenar.495719@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 1, "adults": 1, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-06-08", "departureDate": "2026-06-11", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 3, "phone": "+33688761250", "totalPrice": 146.87, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 23.85, "hostawayCommissionAmount": null, "cleaningFee": 40, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\n\nBOOKING NOTE : Payment charge is EUR 1.9642", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": null, "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 85918298, "accountId": 181258, "listingMapId": 493047, "reservationId": 60438998, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 40, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-06-04 09:52:40", "updatedOn": "2026-06-04 09:52:40"}, {"id": 85918299, "accountId": 181258, "listingMapId": 493047, "reservationId": 60438998, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 9.12, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-06-04 09:52:40", "updatedOn": "2026-06-04 09:52:40"}, {"id": 85918300, "accountId": 181258, "listingMapId": 493047, "reservationId": 60438998, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 6.57, "currency": "EUR", "percentage": 7.21, "isIncluded": 1</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-06-08T11:44:03+00:00</t>
+          <t>2026-08-17T05:25:43+00:00</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>18045de1450a7091</t>
+          <t>249fa21942c28ccd</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>55669313</v>
+        <v>60539937</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>{"id": 55669313, "listingMapId": 480139, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6598251257", "hostawayReservationId": "55669313", "channelReservationId": "6598251257", "externalPropertyId": "15499360", "externalUnitId": "1549936001", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "SOo-lIN9", "guestPortalUrl": "https://guest-portal.hostaway.com/55669313/SOo-lIN9", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-03-07 16:49:25", "pendingExpireDate": null, "guestName": "Andoni Iztueta Villar", "guestFirstName": "Andoni", "guestLastName": "Iztueta Villar", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "ES", "guestEmail": "avilla.130389@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 5, "adults": 2, "children": 3, "infants": null, "pets": null, "arrivalDate": "2026-04-06", "departureDate": "2026-04-08", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 2, "phone": "+34615786412", "totalPrice": 259.25, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 41.94, "hostawayCommissionAmount": null, "cleaningFee": 55, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nBOOKING NOTE : Payment charge is EUR 3.6294664", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "There is no meal option with this room.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 77029925, "accountId": 181258, "listingMapId": 480139, "reservationId": 55669313, "name": "Cleaning fee", "feeType": "guest", "externalReservationUnitId": null, "amount": 55, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-07 16:50:56", "updatedOn": "2026-03-07 16:50:56"}, {"id": 77029926, "accountId": 181258, "listingMapId": 480139, "reservationId": 55669313, "name": "VAT", "feeType": "guest", "externalReservationUnitId": null, "amount": 17.43, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-07 16:50:56", "updatedOn": "2026-03-07 16:50:56"}, {"id": 77029927, "accountId": 181258, "listingMapId": 480139, "reservationId": 55669313, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 12.55, "currency": "EUR", "percentage": 7.2, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-07 16:50:56", "updatedOn": "2026-03-07 16:50:56"}, {"id": 77029928, "acc</t>
+          <t>{"id": 60539937, "listingMapId": 493047, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6567109043", "hostawayReservationId": "60539937", "channelReservationId": "6567109043", "externalPropertyId": "15480052", "externalUnitId": "1548005201", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "FZ6CvPYV", "guestPortalUrl": "https://guest-portal.hostaway.com/60539937/FZ6CvPYV", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-06-06 08:44:27", "pendingExpireDate": null, "guestName": "Aldo SINAWE", "guestFirstName": "Aldo", "guestLastName": "SINAWE", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": "", "guestCountry": "FR", "guestEmail": "asinaw.444897@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 1, "adults": 1, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-06-06", "departureDate": "2026-06-08", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 2, "phone": "+33754720522", "totalPrice": 99.77, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 16.34, "hostawayCommissionAmount": null, "cleaningFee": 40, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nBOOKING NOTE : Payment charge is EUR 1.3454", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": null, "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 86084809, "accountId": 181258, "listingMapId": 493047, "reservationId": 60539937, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 40, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-06-06 08:45:52", "updatedOn": "2026-06-06 08:45:52"}, {"id": 86084810, "accountId": 181258, "listingMapId": 493047, "reservationId": 60539937, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 5.1, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-06-06 08:45:52", "updatedOn": "2026-06-06 08:45:52"}, {"id": 86084811, "accountId": 181258, "listingMapId": 493047, "reservationId": 60539937, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 3.67, "currency": "EUR", "percentage": 7.2, "isIncluded": 1, "isPerNight"</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026-06-08T11:44:04+00:00</t>
+          <t>2026-08-17T05:25:44+00:00</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>970f702e31c16900</t>
+          <t>828148afb8e19205</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>57142306</v>
+        <v>58132903</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>{"id": 57142306, "listingMapId": 493047, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5996054807", "hostawayReservationId": "57142306", "channelReservationId": "5996054807", "externalPropertyId": "15480052", "externalUnitId": "1548005201", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "DO-n9jMt", "guestPortalUrl": "https://guest-portal.hostaway.com/57142306/DO-n9jMt", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-04-01 16:27:11", "pendingExpireDate": null, "guestName": "leidy jhoana caicedo victoria", "guestFirstName": "leidy", "guestLastName": "jhoana caicedo victoria", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "ES", "guestEmail": "lvicto.549055@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 2, "adults": 2, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-04-03", "departureDate": "2026-04-05", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 2, "phone": "+34602505317", "totalPrice": 110.64, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 18.07, "hostawayCommissionAmount": null, "cleaningFee": 40, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\n\nBOOKING NOTE : Payment charge is EUR 1.5489544", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 79343263, "accountId": 181258, "listingMapId": 493047, "reservationId": 57142306, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 40, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-01 16:28:35", "updatedOn": "2026-04-01 16:28:35"}, {"id": 79343265, "accountId": 181258, "listingMapId": 493047, "reservationId": 57142306, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 6.03, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-01 16:28:35", "updatedOn": "2026-04-01 16:28:35"}, {"id": 79343267, "accountId": 181258, "listingMapId": 493047, "reservationId": 57142306, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 4.34, "currency": "EUR", "percentage": 7.2, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-01 16:28:35", "updatedOn": "202</t>
+          <t>{"id": 58132903, "listingMapId": 493047, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5364586891", "hostawayReservationId": "58132903", "channelReservationId": "5364586891", "externalPropertyId": "15480052", "externalUnitId": "1548005201", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "NksQNUyb", "guestPortalUrl": "https://guest-portal.hostaway.com/58132903/NksQNUyb", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-04-21 15:09:00", "pendingExpireDate": null, "guestName": "Takahiro Sasaki", "guestFirstName": "Takahiro", "guestLastName": "Sasaki", "guestExternalAccountId": null, "guestZipCode": "049712", "guestAddress": "30 08 Prudential Tower, 19 Cecil St", "guestCity": "bangkok", "guestCountry": "JP", "guestEmail": "tsasak.194672@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 1, "adults": 1, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-05-31", "departureDate": "2026-06-06", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 6, "phone": "+812035640799", "totalPrice": 273.65, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 44.08, "hostawayCommissionAmount": null, "cleaningFee": 40, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nBOOKING NOTE : Payment charge is EUR 3.6302\nArrivalTime: 23 00 - 24 00", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": null, "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 82118118, "accountId": 181258, "listingMapId": 493047, "reservationId": 58132903, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 40, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-21 15:10:27", "updatedOn": "2026-04-21 15:10:27"}, {"id": 82118119, "accountId": 181258, "listingMapId": 493047, "reservationId": 58132903, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 19.94, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-21 15:10:27", "updatedOn": "2026-04-21 15:10:27"}, {"id": 82118120, "accountId": 181258, "listingMapId": 493047, "reservationId": 58132903, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": n</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-06-08T11:44:07+00:00</t>
+          <t>2026-08-17T05:25:45+00:00</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>e85d2ed5076ceb5a</t>
+          <t>f7d24d1af8342e1f</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>56842443</v>
+        <v>59977743</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>{"id": 56842443, "listingMapId": 480140, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5476072668", "hostawayReservationId": "56842443", "channelReservationId": "5476072668", "externalPropertyId": "15500360", "externalUnitId": "1550036001", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "TJfXfbsj", "guestPortalUrl": "https://guest-portal.hostaway.com/56842443/TJfXfbsj", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-03-28 03:09:35", "pendingExpireDate": null, "guestName": "Fernandez Alvaro", "guestFirstName": "Fernandez", "guestLastName": "Alvaro", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "ES", "guestEmail": "falvar.726911@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 5, "adults": 5, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-04-01", "departureDate": "2026-04-03", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 2, "phone": "+34658185121", "totalPrice": 183.88, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 29.91, "hostawayCommissionAmount": null, "cleaningFee": 55, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nReservation has a cancellation grace period. Do not charge if cancelled before 2026-03-29 05:09:35\n\nBOOKING NOTE : Payment charge is EUR 2.5742836", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "There is no meal option with this room.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 78938752, "accountId": 181258, "listingMapId": 480140, "reservationId": 56842443, "name": "Cleaning fee", "feeType": "guest", "externalReservationUnitId": null, "amount": 55, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-28 03:10:52", "updatedOn": "2026-03-28 03:10:52"}, {"id": 78938753, "accountId": 181258, "listingMapId": 480140, "reservationId": 56842443, "name": "VAT", "feeType": "guest", "externalReservationUnitId": null, "amount": 11, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-28 03:10:52", "updatedOn": "2026-03-28 03:10:52"}, {"id": 78938754, "accountId": 181258, "listingMapId": 480140, "reservationId": 56842443, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 7.92, "currency": "EUR", "percentage": 7.2, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "ins</t>
+          <t>{"id": 59977743, "listingMapId": 480140, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5304346991", "hostawayReservationId": "59977743", "channelReservationId": "5304346991", "externalPropertyId": "15500360", "externalUnitId": "1550036001", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "fUb0eqVA", "guestPortalUrl": "https://guest-portal.hostaway.com/59977743/fUb0eqVA", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-05-26 10:58:58", "pendingExpireDate": null, "guestName": "Arsinoe BERNARD-BRUNEL", "guestFirstName": "Arsinoe", "guestLastName": "BERNARD-BRUNEL", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": "", "guestCountry": "FR", "guestEmail": "aberna.109417@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 3, "adults": 3, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-06-01", "departureDate": "2026-06-05", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 4, "phone": "+33672232083", "totalPrice": 406.39, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 65.42, "hostawayCommissionAmount": null, "cleaningFee": 55, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nReservation has a cancellation grace period. Do not charge if cancelled before 2026-05-27 12:58:58\nApproximate time of arrival: between 19:00 and 20:00\nBOOKING NOTE : Payment charge is EUR 5.3872", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "There is no meal option with this room.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": "16", "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": {"name": "Moderate", "channelId": 2005, "channelSpecificCode": "16", "longTerm": false, "cancellationPolicyItem": [{"refundAmount": 100, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": -432000, "event": "arrival"}]}, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 85119741, "accountId": 181258, "listingMapId": 480140, "reservationId": 59977743, "name": "Cleaning fee", "feeType": "guest", "externalReservationUnitId": null, "amount": 55, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-05-26 11:01:35", "updatedOn": "2026-05-26 11:01:35"}, {"id": 85119742, "accountId": 181258, "listingMapId": 480140, "reservationId": 59977743, "name": "VAT", "feeType": "guest", "externalReservationUnitId": null, "amount": 29.98, "currency": "EUR", "percentage": 10, "isIncluded": 1</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2026-06-08T11:44:08+00:00</t>
+          <t>2026-08-17T05:25:46+00:00</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>0fa40846dc1a0000</t>
+          <t>538de935abc7f712</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>56713083</v>
+        <v>56445297</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>{"id": 56713083, "listingMapId": 480139, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6695268135", "hostawayReservationId": "56713083", "channelReservationId": "6695268135", "externalPropertyId": "15499360", "externalUnitId": "1549936001", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "Qx0bqLw3", "guestPortalUrl": "https://guest-portal.hostaway.com/56713083/Qx0bqLw3", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-03-25 22:28:45", "pendingExpireDate": null, "guestName": "Isabel Munoz Benitez", "guestFirstName": "Isabel", "guestLastName": "Munoz Benitez", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "ES", "guestEmail": "ibenit.649681@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 4, "adults": 4, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-04-01", "departureDate": "2026-04-03", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 2, "phone": "+34635252822", "totalPrice": 173.14, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 28.2, "hostawayCommissionAmount": null, "cleaningFee": 55, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nReservation has a cancellation grace period. Do not charge if cancelled before 2026-03-26 23:28:45\nBOOKING NOTE : Payment charge is EUR 2.4239264", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "There is no meal option with this room.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 78759795, "accountId": 181258, "listingMapId": 480139, "reservationId": 56713083, "name": "Cleaning fee", "feeType": "guest", "externalReservationUnitId": null, "amount": 55, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-25 22:30:49", "updatedOn": "2026-03-25 22:30:49"}, {"id": 78759796, "accountId": 181258, "listingMapId": 480139, "reservationId": 56713083, "name": "VAT", "feeType": "guest", "externalReservationUnitId": null, "amount": 10.08, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-25 22:30:49", "updatedOn": "2026-03-25 22:30:49"}, {"id": 78759797, "accountId": 181258, "listingMapId": 480139, "reservationId": 56713083, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 7.26, "currency": "EUR", "percentage": 7.2, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported":</t>
+          <t>{"id": 56445297, "listingMapId": 480139, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5331465465", "hostawayReservationId": "56445297", "channelReservationId": "5331465465", "externalPropertyId": "15499360", "externalUnitId": "1549936001", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "QwtvUoF1", "guestPortalUrl": "https://guest-portal.hostaway.com/56445297/QwtvUoF1", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-03-21 10:34:33", "pendingExpireDate": null, "guestName": "Jean-Pierre GOURAUD", "guestFirstName": "Jean-Pierre", "guestLastName": "GOURAUD", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": "", "guestCountry": "FR", "guestEmail": "jgoura.517236@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 5, "adults": 5, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-05-29", "departureDate": "2026-06-01", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 3, "phone": "+33787279502", "totalPrice": 366.54, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 59.06, "hostawayCommissionAmount": null, "cleaningFee": 55, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\n\nBOOKING NOTE : Payment charge is EUR 5.1315446", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "There is no meal option with this room.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": "16", "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": {"name": "Moderate", "channelId": 2005, "channelSpecificCode": "16", "longTerm": false, "cancellationPolicyItem": [{"refundAmount": 100, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": -432000, "event": "arrival"}]}, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 78324438, "accountId": 181258, "listingMapId": 480139, "reservationId": 56445297, "name": "Cleaning fee", "feeType": "guest", "externalReservationUnitId": null, "amount": 55, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-21 10:35:55", "updatedOn": "2026-03-21 10:35:55"}, {"id": 78324439, "accountId": 181258, "listingMapId": 480139, "reservationId": 56445297, "name": "VAT", "feeType": "guest", "externalReservationUnitId": null, "amount": 26.58, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-21 10:35:55", "updatedOn": "2026-03-21 10:35:55"}, {"id": 78324440, "accountId</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2026-06-08T11:44:09+00:00</t>
+          <t>2026-08-17T05:25:46+00:00</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>4ceffd91079419d6</t>
+          <t>6f53b74dd01c1755</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>56587223</v>
+        <v>55377365</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>{"id": 56587223, "listingMapId": 493047, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6592305464", "hostawayReservationId": "56587223", "channelReservationId": "6592305464", "externalPropertyId": "15480052", "externalUnitId": "1548005201", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "pR0GJV2C", "guestPortalUrl": "https://guest-portal.hostaway.com/56587223/pR0GJV2C", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-03-23 22:25:05", "pendingExpireDate": null, "guestName": "Miah Nayeem", "guestFirstName": "Miah", "guestLastName": "Nayeem", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "FR", "guestEmail": "mnayee.310819@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 2, "adults": 2, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-03-29", "departureDate": "2026-04-03", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 5, "phone": "+33753789108", "totalPrice": 219.32, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 35.41, "hostawayCommissionAmount": null, "cleaningFee": 40, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nBOOKING NOTE : Payment charge is EUR 3.070424", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 78562315, "accountId": 181258, "listingMapId": 493047, "reservationId": 56587223, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 40, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-23 22:26:26", "updatedOn": "2026-03-23 22:26:26"}, {"id": 78562316, "accountId": 181258, "listingMapId": 493047, "reservationId": 56587223, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 15.3, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-23 22:26:26", "updatedOn": "2026-03-23 22:26:26"}, {"id": 78562317, "accountId": 181258, "listingMapId": 493047, "reservationId": 56587223, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 11.02, "currency": "EUR", "percentage": 7.2, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-23 22:26:26", "updatedOn": "2026-03-23 22:26:26"}, {"id": 78562318, "</t>
+          <t>{"id": 55377365, "listingMapId": 493047, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5742761102", "hostawayReservationId": "55377365", "channelReservationId": "5742761102", "externalPropertyId": "15480052", "externalUnitId": "1548005201", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "l_qoqGTo", "guestPortalUrl": "https://guest-portal.hostaway.com/55377365/l_qoqGTo", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 1, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-01-14 21:19:48", "pendingExpireDate": null, "guestName": "DANILA DALL&amp;#39;OPPIO", "guestFirstName": "DANILA", "guestLastName": "DALL&amp;#39;OPPIO", "guestExternalAccountId": null, "guestZipCode": null, "guestAddress": null, "guestCity": null, "guestCountry": null, "guestEmail": null, "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 2, "adults": 2, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-05-28", "departureDate": "2026-05-31", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 3, "phone": null, "totalPrice": 145.8, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": null, "hostawayCommissionAmount": null, "cleaningFee": null, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Unknown", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": null, "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": null, "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [], "reservationUnit": [], "insertedOn": "2026-03-02 23:46:45", "updatedOn": "2026-05-31 07:06:52", "latestActivityOn": "2026-05-31 07:06:52", "customerUserId": null, "guestLocale": null, "localeForMessaging": null, "localeForMessagingSource": null, "listingCustomFields": null, "rentalAgreementFileUrl": null, "reservationAgreement": "not_required", "financeField": [{"id": 226915513, "units": 1, "listingFeeSettingId": null, "type": "accommodation", "name": "baseRate", "title": "Base rate", "alias": null, "quantity": null, "value": 145.8, "isIncludedInTotalPrice": 1, "isOverriddenByUser": 0, "isMandatory": 1, "isQuantitySelectable": 0, "isDeleted": 0, "total": 145.8}, {"id": 226915514, "units": 1, "listingFeeSettingId": null, "type": "totals", "name": "totalPriceFromChannel", "title": "Total price from channel", "alias": null, "quantity": null, "value": 145.8, "isIncludedInTotalPrice": 0, "isOverriddenByUser": 0, "isMandatory": 0, "isQuantitySelectable": 0, "isDeleted": 0, "total": 145.8}], "guestPaymentCardIsVirtual": null, "insuranceStatus": "not_eligible", "c</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-06-08T11:44:10+00:00</t>
+          <t>2026-08-17T05:25:47+00:00</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>c70e654a200f018e</t>
+          <t>5afeb3fb2c183bbd</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>56814094</v>
+        <v>55733615</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>{"id": 56814094, "listingMapId": 480137, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5765483815", "hostawayReservationId": "56814094", "channelReservationId": "5765483815", "externalPropertyId": "15950709", "externalUnitId": "1595070901", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "eQ1I9oVf", "guestPortalUrl": "https://guest-portal.hostaway.com/56814094/eQ1I9oVf", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-03-27 16:54:48", "pendingExpireDate": null, "guestName": "Samuel Jolbit", "guestFirstName": "Samuel", "guestLastName": "Jolbit", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "FR", "guestEmail": "sjolbi.717567@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 2, "adults": 2, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-03-27", "departureDate": "2026-03-29", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 2, "phone": "+33628762338", "totalPrice": 113.53, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 18.12, "hostawayCommissionAmount": null, "cleaningFee": null, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "modified", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\n\nBOOKING NOTE : Payment charge is EUR 1.5894872", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 79326041, "accountId": 181258, "listingMapId": 480137, "reservationId": 56814094, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 9.69, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-01 12:33:54", "updatedOn": "2026-04-01 12:33:54"}, {"id": 79326042, "accountId": 181258, "listingMapId": 480137, "reservationId": 56814094, "name": "taxe de séjour", "feeType": "guest", "externalReservationUnitId": null, "amount": 6.97, "currency": "EUR", "percentage": 7.2, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-01 12:33:54", "updatedOn": "2026-04-01 12:33:54"}, {"id": 79326043, "accountId": 181258, "listingMapId": 480137, "reservationId": 56814094, "name": "TVA", "feeType": "hotel", "externalReservationUnitId": null, "amount": 9.69, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-01 12:33:54", "updatedOn": "2026-04-01 12:33:54"}, {"id": 79326044, "accountI</t>
+          <t xml:space="preserve">{"id": 55733615, "listingMapId": 480139, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5970827724", "hostawayReservationId": "55733615", "channelReservationId": "5970827724", "externalPropertyId": "15499360", "externalUnitId": "1549936001", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "pJ5qPBKG", "guestPortalUrl": "https://guest-portal.hostaway.com/55733615/pJ5qPBKG", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-03-08 20:40:04", "pendingExpireDate": null, "guestName": "Mateusz Daniol", "guestFirstName": "Mateusz", "guestLastName": "Daniol", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": "", "guestCountry": "PL", "guestEmail": "mdanio.200875@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 5, "adults": 5, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-04-15", "departureDate": "2026-04-20", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 5, "phone": "+48603760773", "totalPrice": 595.19, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 95.54, "hostawayCommissionAmount": null, "cleaningFee": 55, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\n\nBOOKING NOTE : Payment charge is EUR 8.332597", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "There is no meal option with this room.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": "16", "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": {"name": "Moderate", "channelId": 2005, "channelSpecificCode": "16", "longTerm": false, "cancellationPolicyItem": [{"refundAmount": 100, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": -432000, "event": "arrival"}]}, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 77133527, "accountId": 181258, "listingMapId": 480139, "reservationId": 55733615, "name": "Cleaning fee", "feeType": "guest", "externalReservationUnitId": null, "amount": 55, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-08 20:41:43", "updatedOn": "2026-03-08 20:41:43"}, {"id": 77133528, "accountId": 181258, "listingMapId": 480139, "reservationId": 55733615, "name": "VAT", "feeType": "guest", "externalReservationUnitId": null, "amount": 46.09, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-08 20:41:43", "updatedOn": "2026-03-08 20:41:43"}, {"id": 77133529, "accountId": 181258, </t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026-06-08T11:44:11+00:00</t>
+          <t>2026-08-17T05:25:48+00:00</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>7050a1cba42fead3</t>
+          <t>2545d37d80f8571d</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>56124039</v>
+        <v>58720999</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>{"id": 56124039, "listingMapId": 480140, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5971651562", "hostawayReservationId": "56124039", "channelReservationId": "5971651562", "externalPropertyId": "15500360", "externalUnitId": "1550036001", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "a-yRbAUU", "guestPortalUrl": "https://guest-portal.hostaway.com/56124039/a-yRbAUU", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-03-15 19:04:53", "pendingExpireDate": null, "guestName": "Andrey Sosnikhin", "guestFirstName": "Andrey", "guestLastName": "Sosnikhin", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": "", "guestCountry": "GB", "guestEmail": "asosni.233988@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 4, "adults": 2, "children": 2, "infants": null, "pets": null, "arrivalDate": "2026-03-30", "departureDate": "2026-04-01", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 2, "phone": "+447586557087", "totalPrice": 213.89, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 35.5, "hostawayCommissionAmount": null, "cleaningFee": 55, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nReservation has a cancellation grace period. Do not charge if cancelled before 2026-03-16 20:04:53\nBOOKING NOTE : Payment charge is EUR 2.9943914", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "There is no meal option with this room.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 77830125, "accountId": 181258, "listingMapId": 480140, "reservationId": 56124039, "name": "Cleaning fee", "feeType": "guest", "externalReservationUnitId": null, "amount": 55, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-15 19:06:16", "updatedOn": "2026-03-15 19:06:16"}, {"id": 77830126, "accountId": 181258, "listingMapId": 480140, "reservationId": 56124039, "name": "VAT", "feeType": "guest", "externalReservationUnitId": null, "amount": 13.99, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-15 19:06:16", "updatedOn": "2026-03-15 19:06:16"}, {"id": 77830127, "accountId": 181258, "listingMapId": 480140, "reservationId": 56124039, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 5.04, "currency": "EUR", "percentage": 7.21, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "inser</t>
+          <t>{"id": 58720999, "listingMapId": 480137, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6413954681", "hostawayReservationId": "58720999", "channelReservationId": "6413954681", "externalPropertyId": "15950709", "externalUnitId": "1595070901", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "vMSmLUAw", "guestPortalUrl": "https://guest-portal.hostaway.com/58720999/vMSmLUAw", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-05-03 23:57:44", "pendingExpireDate": null, "guestName": "Ianko Jose Perea", "guestFirstName": "Ianko", "guestLastName": "Jose Perea", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": "", "guestCountry": "AR", "guestEmail": "iperea.465062@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 4, "adults": 4, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-05-24", "departureDate": "2026-05-26", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 2, "phone": "+5491154730938", "totalPrice": 235.77, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 38.32, "hostawayCommissionAmount": null, "cleaningFee": 67, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\n\nBOOKING NOTE : Payment charge is EUR 3.30078", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": "16", "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": {"name": "Moderate", "channelId": 2005, "channelSpecificCode": "16", "longTerm": false, "cancellationPolicyItem": [{"refundAmount": 100, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": -432000, "event": "arrival"}]}, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 83151493, "accountId": 181258, "listingMapId": 480137, "reservationId": 58720999, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 67, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-05-03 23:59:04", "updatedOn": "2026-05-03 23:59:04"}, {"id": 83151494, "accountId": 181258, "listingMapId": 480137, "reservationId": 58720999, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 14.4, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-05-03 23:59:04", "updatedOn": "2026-05-03 23:59:04"}, {"id": 83151</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026-06-08T11:44:12+00:00</t>
+          <t>2026-08-17T05:25:50+00:00</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>074242815e619cca</t>
+          <t>2f46dd1900cb2584</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>54376756</v>
+        <v>59144154</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>{"id": 54376756, "listingMapId": 480139, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6672470205", "hostawayReservationId": "54376756", "channelReservationId": "6672470205", "externalPropertyId": "15499360", "externalUnitId": "1549936001", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "gP_MTj43", "guestPortalUrl": "https://guest-portal.hostaway.com/54376756/gP_MTj43", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 1, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-02-14 22:00:57", "pendingExpireDate": null, "guestName": "Olga Correia", "guestFirstName": "Olga", "guestLastName": "Correia", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "PT", "guestEmail": "ocorre.915879@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 5, "adults": 5, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-03-29", "departureDate": "2026-03-31", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 2, "phone": "+351919764669", "totalPrice": 223.45, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 36.23, "hostawayCommissionAmount": null, "cleaningFee": 55, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nReservation has a cancellation grace period. Do not charge if cancelled before 2026-02-15 23:00:57\n\nBOOKING NOTE : Payment charge is EUR 3.1282776", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "There is no meal option with this room.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 76637602, "accountId": 181258, "listingMapId": 480139, "reservationId": 54376756, "name": "Cleaning fee", "feeType": "guest", "externalReservationUnitId": null, "amount": 55, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-03 00:00:02", "updatedOn": "2026-03-03 00:00:02"}, {"id": 76637604, "accountId": 181258, "listingMapId": 480139, "reservationId": 54376756, "name": "VAT", "feeType": "guest", "externalReservationUnitId": null, "amount": 14.37, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-03 00:00:02", "updatedOn": "2026-03-03 00:00:02"}, {"id": 76637606, "accountId": 181258, "listingMapId": 480139, "reservationId": 54376756, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 10.35, "currency": "EUR", "percentage": 7.2, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insert</t>
+          <t xml:space="preserve">{"id": 59144154, "listingMapId": 480139, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6057496813", "hostawayReservationId": "59144154", "channelReservationId": "6057496813", "externalPropertyId": "15499360", "externalUnitId": "1549936001", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "c82qy9Vz", "guestPortalUrl": "https://guest-portal.hostaway.com/59144154/c82qy9Vz", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-05-12 05:50:37", "pendingExpireDate": null, "guestName": "Leyla Oualichane", "guestFirstName": "Leyla", "guestLastName": "Oualichane", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "FR", "guestEmail": "louali.122874@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 6, "adults": 1, "children": 5, "infants": null, "pets": null, "arrivalDate": "2026-05-22", "departureDate": "2026-05-25", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 3, "phone": "+33773681838", "totalPrice": 317.94, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 53.57, "hostawayCommissionAmount": null, "cleaningFee": 55, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nReservation has a cancellation grace period. Do not charge if cancelled before 2026-05-13 07:50:37\nBOOKING NOTE : Payment charge is EUR 4.4114", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "There is no meal option with this room.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": "16", "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": {"name": "Moderate", "channelId": 2005, "channelSpecificCode": "16", "longTerm": false, "cancellationPolicyItem": [{"refundAmount": 100, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": -432000, "event": "arrival"}]}, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 83854533, "accountId": 181258, "listingMapId": 480139, "reservationId": 59144154, "name": "Cleaning fee", "feeType": "guest", "externalReservationUnitId": null, "amount": 55, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-05-12 05:52:05", "updatedOn": "2026-05-12 05:52:05"}, {"id": 83854534, "accountId": 181258, "listingMapId": 480139, "reservationId": 59144154, "name": "VAT", "feeType": "guest", "externalReservationUnitId": null, "amount": 23.65, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": </t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026-06-08T11:44:13+00:00</t>
+          <t>2026-08-17T05:25:51+00:00</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>9add502b652ffebe</t>
+          <t>74b220848c2d3c4f</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>57066128</v>
+        <v>55377361</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>{"id": 57066128, "listingMapId": 480140, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5022726075", "hostawayReservationId": "57066128", "channelReservationId": "5022726075", "externalPropertyId": "15500360", "externalUnitId": "1550036001", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "tjurDQuN", "guestPortalUrl": "https://guest-portal.hostaway.com/57066128/tjurDQuN", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-03-31 03:40:57", "pendingExpireDate": null, "guestName": "Suzy LAROCHELLE", "guestFirstName": "Suzy", "guestLastName": "LAROCHELLE", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": "", "guestCountry": "GP", "guestEmail": "slaroc.136698@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 4, "adults": 4, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-07-08", "departureDate": "2026-07-11", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 3, "phone": "+594694904580", "totalPrice": 365.63, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 58.91, "hostawayCommissionAmount": null, "cleaningFee": 55, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\n\nBOOKING NOTE : Payment charge is EUR 5.1188662", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "There is no meal option with this room.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 79204868, "accountId": 181258, "listingMapId": 480140, "reservationId": 57066128, "name": "Cleaning fee", "feeType": "guest", "externalReservationUnitId": null, "amount": 55, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-31 03:42:24", "updatedOn": "2026-03-31 03:42:24"}, {"id": 79204869, "accountId": 181258, "listingMapId": 480140, "reservationId": 57066128, "name": "VAT", "feeType": "guest", "externalReservationUnitId": null, "amount": 26.5, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-31 03:42:24", "updatedOn": "2026-03-31 03:42:24"}, {"id": 79204870, "accountId": 181258, "listingMapId": 480140, "reservationId": 57066128, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 19.08, "currency": "EUR", "percentage": 7.2, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-31 03:42:24", "updatedOn": "2026-03-31 03:42:24"}, {"id": 79204871, "accountId":</t>
+          <t>{"id": 55377361, "listingMapId": 493047, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5381723020", "hostawayReservationId": "55377361", "channelReservationId": "5381723020", "externalPropertyId": "15480052", "externalUnitId": "1548005201", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "ztYU8i_E", "guestPortalUrl": "https://guest-portal.hostaway.com/55377361/ztYU8i_E", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 1, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-02-11 22:12:29", "pendingExpireDate": null, "guestName": "Rosa Goldie", "guestFirstName": "Rosa", "guestLastName": "Goldie", "guestExternalAccountId": null, "guestZipCode": "049712", "guestAddress": "30 08 Prudential Tower, 19 Cecil St", "guestCity": "bangkok", "guestCountry": "GB", "guestEmail": "rgoldi.406294@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 2, "adults": 2, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-05-18", "departureDate": "2026-05-22", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 4, "phone": "+442035640799", "totalPrice": 136.66, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": null, "hostawayCommissionAmount": null, "cleaningFee": null, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": null, "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": null, "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 76637488, "accountId": 181258, "listingMapId": 493047, "reservationId": 55377361, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 40, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-02 23:58:26", "updatedOn": "2026-03-02 23:58:26"}, {"id": 76637489, "accountId": 181258, "listingMapId": 493047, "reservationId": 55377361, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 8.25, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-02 23:58:26", "updatedOn": "2026-03-02 23:58:26"}, {"id": 76637490, "accountId": 181258, "listingMapId": 493047, "reservationId": 55377361, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 5.94, "currency": "EUR", "percentage": 7.2, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImpor</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2026-06-08T11:44:14+00:00</t>
+          <t>2026-08-17T05:25:52+00:00</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>6da2176203049d7b</t>
+          <t>ec83dca0dc86e082</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>56576707</v>
+        <v>59259973</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t xml:space="preserve">{"id": 56576707, "listingMapId": 493047, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6158482386", "hostawayReservationId": "56576707", "channelReservationId": "6158482386", "externalPropertyId": "15480052", "externalUnitId": "1548005201", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "pghrgw8R", "guestPortalUrl": "https://guest-portal.hostaway.com/56576707/pghrgw8R", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-03-23 19:10:46", "pendingExpireDate": null, "guestName": "chenyi Wang", "guestFirstName": "chenyi", "guestLastName": "Wang", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "FR", "guestEmail": "czvflw.450356@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 1, "adults": 1, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-03-27", "departureDate": "2026-03-29", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 2, "phone": "+33782125837", "totalPrice": 101.58, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 16.63, "hostawayCommissionAmount": null, "cleaningFee": 40, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nBOOKING NOTE : Payment charge is EUR 1.4221662", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 78543573, "accountId": 181258, "listingMapId": 493047, "reservationId": 56576707, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 40, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-23 19:12:15", "updatedOn": "2026-03-23 19:12:15"}, {"id": 78543574, "accountId": 181258, "listingMapId": 493047, "reservationId": 56576707, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 5.25, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-23 19:12:15", "updatedOn": "2026-03-23 19:12:15"}, {"id": 78543575, "accountId": 181258, "listingMapId": 493047, "reservationId": 56576707, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 3.78, "currency": "EUR", "percentage": 7.19, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-23 19:12:15", "updatedOn": "2026-03-23 19:12:15"}, {"id": 78543576, </t>
+          <t>{"id": 59259973, "listingMapId": 480137, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5401750056", "hostawayReservationId": "59259973", "channelReservationId": "5401750056", "externalPropertyId": "15950709", "externalUnitId": "1595070901", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "MrSbsffa", "guestPortalUrl": "https://guest-portal.hostaway.com/59259973/MrSbsffa", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-05-14 13:55:33", "pendingExpireDate": null, "guestName": "Barraud Arthur", "guestFirstName": "Barraud", "guestLastName": "Arthur", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": "", "guestCountry": "FR", "guestEmail": "barthu.283998@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 2, "adults": 2, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-05-17", "departureDate": "2026-05-21", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 4, "phone": "+33780408841", "totalPrice": 332.62, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 53.77, "hostawayCommissionAmount": null, "cleaningFee": 67, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nJe voyage pour affaires et il est possible que j'utilise la carte de crédit de ma société.\nCe client souhaiterait avoir une facture pour son séjour.\n\nApproximate time of arrival: between 17:00 and 18:00\nBOOKING NOTE : Payment charge is EUR 4.65668", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": "16", "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": {"name": "Moderate", "channelId": 2005, "channelSpecificCode": "16", "longTerm": false, "cancellationPolicyItem": [{"refundAmount": 100, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": -432000, "event": "arrival"}]}, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 84084097, "accountId": 181258, "listingMapId": 480137, "reservationId": 59259973, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 67, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-05-14 14:00:40", "updatedOn": "2026-05-14 14:00:40"}, {"id": 84084098, "accountId": 181258, "listingMapId": 480137, "reservationId": 59259973, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount":</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026-06-08T11:44:15+00:00</t>
+          <t>2026-08-17T05:25:53+00:00</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>6ae58fe359df858f</t>
+          <t>40b62416f7081c19</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>56908103</v>
+        <v>59544415</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>{"id": 56908103, "listingMapId": 480140, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6378353908", "hostawayReservationId": "56908103", "channelReservationId": "6378353908", "externalPropertyId": "15500360", "externalUnitId": "1550036001", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "05lcaLo7", "guestPortalUrl": "https://guest-portal.hostaway.com/56908103/05lcaLo7", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-03-29 09:18:31", "pendingExpireDate": null, "guestName": "Patrick COLIN", "guestFirstName": "Patrick", "guestLastName": "COLIN", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": "", "guestCountry": "FR", "guestEmail": "pcolin.401170@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 5, "adults": 5, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-09-18", "departureDate": "2026-09-20", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 2, "phone": "+33616371171", "totalPrice": 276.88, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 44.75, "hostawayCommissionAmount": null, "cleaningFee": 55, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\n\nBOOKING NOTE : Payment charge is EUR 3.8763326", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "There is no meal option with this room.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 79026391, "accountId": 181258, "listingMapId": 480140, "reservationId": 56908103, "name": "Cleaning fee", "feeType": "guest", "externalReservationUnitId": null, "amount": 55, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-29 09:19:53", "updatedOn": "2026-03-29 09:19:53"}, {"id": 79026392, "accountId": 181258, "listingMapId": 480140, "reservationId": 56908103, "name": "VAT", "feeType": "guest", "externalReservationUnitId": null, "amount": 18.93, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-29 09:19:53", "updatedOn": "2026-03-29 09:19:53"}, {"id": 79026393, "accountId": 181258, "listingMapId": 480140, "reservationId": 56908103, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 13.63, "currency": "EUR", "percentage": 7.2, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-29 09:19:53", "updatedOn": "2026-03-29 09:19:53"}, {"id": 79026394, "accountId": 181</t>
+          <t>{"id": 59544415, "listingMapId": 480139, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6496345089", "hostawayReservationId": "59544415", "channelReservationId": "6496345089", "externalPropertyId": "15499360", "externalUnitId": "1549936001", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "tOJ0MpZN", "guestPortalUrl": "https://guest-portal.hostaway.com/59544415/tOJ0MpZN", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-05-17 09:43:29", "pendingExpireDate": null, "guestName": "Olteanuu ELENA", "guestFirstName": "Olteanuu", "guestLastName": "ELENA", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "FR", "guestEmail": "oelena.333989@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 2, "adults": 2, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-05-17", "departureDate": "2026-05-19", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 2, "phone": "+393895344387", "totalPrice": 182.15, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 29.64, "hostawayCommissionAmount": null, "cleaningFee": 55, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\n\nBOOKING NOTE : Payment charge is EUR 2.44076", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "There is no meal option with this room.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": "16", "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": {"name": "Moderate", "channelId": 2005, "channelSpecificCode": "16", "longTerm": false, "cancellationPolicyItem": [{"refundAmount": 100, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": -432000, "event": "arrival"}]}, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 84328836, "accountId": 181258, "listingMapId": 480139, "reservationId": 59544415, "name": "Cleaning fee", "feeType": "guest", "externalReservationUnitId": null, "amount": 55, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-05-17 09:44:50", "updatedOn": "2026-05-17 09:44:50"}, {"id": 84328837, "accountId": 181258, "listingMapId": 480139, "reservationId": 59544415, "name": "VAT", "feeType": "guest", "externalReservationUnitId": null, "amount": 10.85, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-05-17 09:44:50", "updatedOn": "2026-05-17 09:44:50"}, {"id": 84328838, "accountId": 181258,</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026-06-08T11:44:16+00:00</t>
+          <t>2026-08-17T05:25:53+00:00</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2d6e773c49b6ea7a</t>
+          <t>bbd03b1f0e834b21</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>55918531</v>
+        <v>58169437</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>{"id": 55918531, "listingMapId": 493047, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6034886110", "hostawayReservationId": "55918531", "channelReservationId": "6034886110", "externalPropertyId": "15480052", "externalUnitId": "1548005201", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "S14uha1x", "guestPortalUrl": "https://guest-portal.hostaway.com/55918531/S14uha1x", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-03-12 00:58:03", "pendingExpireDate": null, "guestName": "Manal Hammoun", "guestFirstName": "Manal", "guestLastName": "Hammoun", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "MA", "guestEmail": "mhammo.966493@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 1, "adults": 1, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-03-22", "departureDate": "2026-03-26", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 4, "phone": "+212663703339", "totalPrice": 163.17, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 26.45, "hostawayCommissionAmount": null, "cleaningFee": 40, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\n\nBOOKING NOTE : Payment charge is EUR 2.2843324", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 77526915, "accountId": 181258, "listingMapId": 493047, "reservationId": 55918531, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 40, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-12 00:59:22", "updatedOn": "2026-03-12 00:59:22"}, {"id": 77526916, "accountId": 181258, "listingMapId": 493047, "reservationId": 55918531, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 10.51, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-12 00:59:22", "updatedOn": "2026-03-12 00:59:22"}, {"id": 77526917, "accountId": 181258, "listingMapId": 493047, "reservationId": 55918531, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 7.57, "currency": "EUR", "percentage": 7.2, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-12 00:59:22", "updatedOn": "2026-03-12 00:59:22"}, {"id": 775</t>
+          <t>{"id": 58169437, "listingMapId": 480137, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6927414258", "hostawayReservationId": "58169437", "channelReservationId": "6927414258", "externalPropertyId": "15950709", "externalUnitId": "1595070901", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "l0wbpCDh", "guestPortalUrl": "https://guest-portal.hostaway.com/58169437/l0wbpCDh", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-04-22 10:37:47", "pendingExpireDate": null, "guestName": "Gwen Gwen", "guestFirstName": "Gwen", "guestLastName": "Gwen", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": "", "guestCountry": "FR", "guestEmail": "ggwen.980317@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 5, "adults": 2, "children": 3, "infants": null, "pets": null, "arrivalDate": "2026-05-14", "departureDate": "2026-05-17", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 3, "phone": "+33664108642", "totalPrice": 320.98, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 53.47, "hostawayCommissionAmount": null, "cleaningFee": 67, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nBOOKING NOTE : Payment charge is EUR 4.49372\nApproximate time of arrival: between 10:00 and 11:00", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": "16", "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": {"name": "Moderate", "channelId": 2005, "channelSpecificCode": "16", "longTerm": false, "cancellationPolicyItem": [{"refundAmount": 100, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": -432000, "event": "arrival"}]}, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 82183968, "accountId": 181258, "listingMapId": 480137, "reservationId": 58169437, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 67, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-22 10:39:38", "updatedOn": "2026-04-22 10:39:38"}, {"id": 82183969, "accountId": 181258, "listingMapId": 480137, "reservationId": 58169437, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 22.5, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-22 10:39:38", "updatedOn": "202</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026-06-08T11:44:17+00:00</t>
+          <t>2026-08-17T05:25:54+00:00</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>6fbf90f66e405181</t>
+          <t>17f315d38a1a5c18</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>55377369</v>
+        <v>59228822</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>{"id": 55377369, "listingMapId": 493047, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5899222328", "hostawayReservationId": "55377369", "channelReservationId": "5899222328", "externalPropertyId": "15480052", "externalUnitId": "1548005201", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "h_H8fRtS", "guestPortalUrl": "https://guest-portal.hostaway.com/55377369/h_H8fRtS", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 1, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-02-14 18:10:02", "pendingExpireDate": null, "guestName": "Beatriz Gómez Ortiz", "guestFirstName": "Beatriz", "guestLastName": "Gómez Ortiz", "guestExternalAccountId": null, "guestZipCode": null, "guestAddress": null, "guestCity": ".", "guestCountry": "ES", "guestEmail": "bortiz.362186@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 2, "adults": 2, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-03-20", "departureDate": "2026-03-22", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 2, "phone": "+34608241102", "totalPrice": 92.16, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": null, "hostawayCommissionAmount": null, "cleaningFee": null, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": null, "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 76637512, "accountId": 181258, "listingMapId": 493047, "reservationId": 55377369, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 40, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-02 23:58:27", "updatedOn": "2026-03-02 23:58:27"}, {"id": 76637513, "accountId": 181258, "listingMapId": 493047, "reservationId": 55377369, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 4.45, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-02 23:58:27", "updatedOn": "2026-03-02 23:58:27"}, {"id": 76637514, "accountId": 181258, "listingMapId": 493047, "reservationId": 55377369, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 3.2, "currency": "EUR", "percentage": 7.19, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-02 23:58:27", "updatedOn": "2026-03-02 23:58:27"}, {"id": 76637515, "accountId": 181258, "listingMapId": 493047, "reservationId": 55377</t>
+          <t>{"id": 59228822, "listingMapId": 493047, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5166918968", "hostawayReservationId": "59228822", "channelReservationId": "5166918968", "externalPropertyId": "15480052", "externalUnitId": "1548005201", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "TUPVuiZ1", "guestPortalUrl": "https://guest-portal.hostaway.com/59228822/TUPVuiZ1", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-05-13 21:18:55", "pendingExpireDate": null, "guestName": "Amadou Kane", "guestFirstName": "Amadou", "guestLastName": "Kane", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "FR", "guestEmail": "akane.595278@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 2, "adults": 2, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-05-14", "departureDate": "2026-05-17", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 3, "phone": "+33783712651", "totalPrice": 145.96, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 23.71, "hostawayCommissionAmount": null, "cleaningFee": 40, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\n\nBOOKING NOTE : Payment charge is EUR 1.9523", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": null, "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 84027857, "accountId": 181258, "listingMapId": 493047, "reservationId": 59228822, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 40, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-05-13 21:20:21", "updatedOn": "2026-05-13 21:20:21"}, {"id": 84027858, "accountId": 181258, "listingMapId": 493047, "reservationId": 59228822, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 9.04, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-05-13 21:20:21", "updatedOn": "2026-05-13 21:20:21"}, {"id": 84027859, "accountId": 181258, "listingMapId": 493047, "reservationId": 59228822, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 6.51, "currency": "EUR", "percentage": 7.2, "isIncluded": 1, "isPerNi</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2026-06-08T11:44:18+00:00</t>
+          <t>2026-08-17T05:25:55+00:00</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>7eb71dcfd51c5074</t>
+          <t>3fa3be538da5ac11</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>55293664</v>
+        <v>58503136</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>{"id": 55293664, "listingMapId": 480140, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6777615695", "hostawayReservationId": "55293664", "channelReservationId": "6777615695", "externalPropertyId": "15500360", "externalUnitId": "1550036001", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "wZg-ea_v", "guestPortalUrl": "https://guest-portal.hostaway.com/55293664/wZg-ea_v", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 1, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-03-01 17:32:06", "pendingExpireDate": null, "guestName": "Cindy Dupont", "guestFirstName": "Cindy", "guestLastName": "Dupont", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "FR", "guestEmail": "cdupon.197857@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 4, "adults": 4, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-03-17", "departureDate": "2026-03-20", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 3, "phone": "+33645566738", "totalPrice": 301.44, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 48.67, "hostawayCommissionAmount": null, "cleaningFee": 55, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nReservation has a cancellation grace period. Do not charge if cancelled before 2026-03-02 18:32:06\nBOOKING NOTE : Payment charge is EUR 4.2201544", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "There is no meal option with this room.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 76753882, "accountId": 181258, "listingMapId": 480140, "reservationId": 55293664, "name": "Cleaning fee", "feeType": "guest", "externalReservationUnitId": null, "amount": 55, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-04 09:52:44", "updatedOn": "2026-03-04 09:52:44"}, {"id": 76753883, "accountId": 181258, "listingMapId": 480140, "reservationId": 55293664, "name": "VAT", "feeType": "guest", "externalReservationUnitId": null, "amount": 21.03, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-04 09:52:44", "updatedOn": "2026-03-04 09:52:44"}, {"id": 76753884, "accountId": 181258, "listingMapId": 480140, "reservationId": 55293664, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 15.14, "currency": "EUR", "percentage": 7.2, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedO</t>
+          <t>{"id": 58503136, "listingMapId": 480139, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5792769705", "hostawayReservationId": "58503136", "channelReservationId": "5792769705", "externalPropertyId": "15499360", "externalUnitId": "1549936001", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "7PFGDvh5", "guestPortalUrl": "https://guest-portal.hostaway.com/58503136/7PFGDvh5", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-04-29 17:42:34", "pendingExpireDate": null, "guestName": "Pereira Ismael", "guestFirstName": "Pereira", "guestLastName": "Ismael", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": "", "guestCountry": "CL", "guestEmail": "pismae.413046@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 6, "adults": 2, "children": 4, "infants": null, "pets": null, "arrivalDate": "2026-05-15", "departureDate": "2026-05-17", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 2, "phone": null, "totalPrice": 232.18, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 38.83, "hostawayCommissionAmount": null, "cleaningFee": 55, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nReservation has a cancellation grace period. Do not charge if cancelled before 2026-04-30 19:42:34\nBOOKING NOTE : Payment charge is EUR 3.1976\nApproximate time of arrival: between 00:00 and 01:00", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "There is no meal option with this room.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": "16", "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": {"name": "Moderate", "channelId": 2005, "channelSpecificCode": "16", "longTerm": false, "cancellationPolicyItem": [{"refundAmount": 100, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": -432000, "event": "arrival"}]}, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 82811710, "accountId": 181258, "listingMapId": 480139, "reservationId": 58503136, "name": "Cleaning fee", "feeType": "guest", "externalReservationUnitId": null, "amount": 55, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-29 17:44:04", "updatedOn": "2026-04-29 17:44:04"}, {"id": 82811711, "accountId": 181258, "listingMapId": 480139, "reservationId": 58503136, "name": "VAT", "feeType": "guest", "externalReservationUnitId": null, "amount": 15.76, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPers</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2026-06-08T11:44:19+00:00</t>
+          <t>2026-08-17T05:25:56+00:00</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>c317f0687e0fd4c5</t>
+          <t>08f28882fbcebee5</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>56355565</v>
+        <v>58992171</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>{"id": 56355565, "listingMapId": 480139, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6953045275", "hostawayReservationId": "56355565", "channelReservationId": "6953045275", "externalPropertyId": "15499360", "externalUnitId": "1549936001", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "IMd-Tq7Y", "guestPortalUrl": "https://guest-portal.hostaway.com/56355565/IMd-Tq7Y", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-03-19 18:35:16", "pendingExpireDate": null, "guestName": "Noelia Rico", "guestFirstName": "Noelia", "guestLastName": "Rico", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "ES", "guestEmail": "nrico.125777@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 5, "adults": 2, "children": 3, "infants": null, "pets": null, "arrivalDate": "2026-07-20", "departureDate": "2026-07-22", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 2, "phone": "+34686150316", "totalPrice": 233.81, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 38.97, "hostawayCommissionAmount": null, "cleaningFee": 55, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nAn extra bed/crib was requested.\nBOOKING NOTE : Payment charge is EUR 3.2733708", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "There is no meal option with this room.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 78188459, "accountId": 181258, "listingMapId": 480139, "reservationId": 56355565, "name": "Cleaning fee", "feeType": "guest", "externalReservationUnitId": null, "amount": 55, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-19 18:36:35", "updatedOn": "2026-03-19 18:36:35"}, {"id": 78188460, "accountId": 181258, "listingMapId": 480139, "reservationId": 56355565, "name": "VAT", "feeType": "guest", "externalReservationUnitId": null, "amount": 15.84, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-19 18:36:35", "updatedOn": "2026-03-19 18:36:35"}, {"id": 78188461, "accountId": 181258, "listingMapId": 480139, "reservationId": 56355565, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 4.56, "currency": "EUR", "percentage": 7.2, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-19 18:36:35", "updatedOn": "2026-03-19 18:36:35"}, {"id": 78</t>
+          <t>{"id": 58992171, "listingMapId": 493047, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5092918242", "hostawayReservationId": "58992171", "channelReservationId": "5092918242", "externalPropertyId": "15480052", "externalUnitId": "1548005201", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "f5w9mPrJ", "guestPortalUrl": "https://guest-portal.hostaway.com/58992171/f5w9mPrJ", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-05-08 18:49:43", "pendingExpireDate": null, "guestName": "Amadou Kane", "guestFirstName": "Amadou", "guestLastName": "Kane", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "FR", "guestEmail": "akane.548585@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 2, "adults": 2, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-05-10", "departureDate": "2026-05-14", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 4, "phone": "+33783712651", "totalPrice": 181.28, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 29.34, "hostawayCommissionAmount": null, "cleaningFee": 40, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nBOOKING NOTE : Payment charge is EUR 2.4164", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": null, "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 83571710, "accountId": 181258, "listingMapId": 493047, "reservationId": 58992171, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 40, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-05-08 18:51:09", "updatedOn": "2026-05-08 18:51:09"}, {"id": 83571711, "accountId": 181258, "listingMapId": 493047, "reservationId": 58992171, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 12.05, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-05-08 18:51:09", "updatedOn": "2026-05-08 18:51:09"}, {"id": 83571712, "accountId": 181258, "listingMapId": 493047, "reservationId": 58992171, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 8.68, "currency": "EUR", "percentage": 7.2, "isIncluded": 1, "isPerNig</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2026-06-08T11:44:20+00:00</t>
+          <t>2026-08-17T05:25:57+00:00</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>a16a6de43aa15027</t>
+          <t>f3f99dc5d0e6cf88</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>55556631</v>
+        <v>58552963</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>{"id": 55556631, "listingMapId": 493047, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6706469653", "hostawayReservationId": "55556631", "channelReservationId": "6706469653", "externalPropertyId": "15480052", "externalUnitId": "1548005201", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "aibDuLHl", "guestPortalUrl": "https://guest-portal.hostaway.com/55556631/aibDuLHl", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-03-05 17:32:45", "pendingExpireDate": null, "guestName": "Barbas Valeria", "guestFirstName": "Barbas", "guestLastName": "Valeria", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": "", "guestCountry": "FR", "guestEmail": "bvaler.881655@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 2, "adults": 2, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-03-11", "departureDate": "2026-03-16", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 5, "phone": "+33641540805", "totalPrice": 193.96, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 31.36, "hostawayCommissionAmount": null, "cleaningFee": 40, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nBOOKING NOTE : Payment charge is EUR 2.7154148\nApproximate time of arrival: between 11:00 and 12:00", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 76874263, "accountId": 181258, "listingMapId": 493047, "reservationId": 55556631, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 40, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-05 17:34:01", "updatedOn": "2026-03-05 17:34:01"}, {"id": 76874264, "accountId": 181258, "listingMapId": 493047, "reservationId": 55556631, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 13.14, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-05 17:34:01", "updatedOn": "2026-03-05 17:34:01"}, {"id": 76874265, "accountId": 181258, "listingMapId": 493047, "reservationId": 55556631, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 9.46, "currency": "EUR", "percentage": 7.2, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-05 17:34:</t>
+          <t xml:space="preserve">{"id": 58552963, "listingMapId": 480137, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5319386045", "hostawayReservationId": "58552963", "channelReservationId": "5319386045", "externalPropertyId": "15950709", "externalUnitId": "1595070901", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "yPeJdRTj", "guestPortalUrl": "https://guest-portal.hostaway.com/58552963/yPeJdRTj", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-04-30 15:27:49", "pendingExpireDate": null, "guestName": "Astrid Demilly", "guestFirstName": "Astrid", "guestLastName": "Demilly", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "FR", "guestEmail": "ademil.297249@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 3, "adults": 2, "children": 1, "infants": null, "pets": null, "arrivalDate": "2026-05-12", "departureDate": "2026-05-14", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 2, "phone": "+33612812077", "totalPrice": 193.8, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 32.05, "hostawayCommissionAmount": null, "cleaningFee": 67, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nReservation has a cancellation grace period. Do not charge if cancelled before 2026-05-01 17:27:49\nBOOKING NOTE : Payment charge is EUR 2.7132", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": "16", "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": {"name": "Moderate", "channelId": 2005, "channelSpecificCode": "16", "longTerm": false, "cancellationPolicyItem": [{"refundAmount": 100, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": -432000, "event": "arrival"}]}, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 82888389, "accountId": 181258, "listingMapId": 480137, "reservationId": 58552963, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 67, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-30 15:29:13", "updatedOn": "2026-04-30 15:29:13"}, {"id": 82888390, "accountId": 181258, "listingMapId": 480137, "reservationId": 58552963, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 11.05, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": </t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2026-06-08T11:44:21+00:00</t>
+          <t>2026-08-17T05:25:58+00:00</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>fd28285f72fb1ba4</t>
+          <t>316fce907ed1f461</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>56220639</v>
+        <v>58442275</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>{"id": 56220639, "listingMapId": 493047, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5373020142", "hostawayReservationId": "56220639", "channelReservationId": "5373020142", "externalPropertyId": "15480052", "externalUnitId": "1548005201", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "9DvvkJYB", "guestPortalUrl": "https://guest-portal.hostaway.com/56220639/9DvvkJYB", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-03-17 11:57:49", "pendingExpireDate": null, "guestName": "Jil Cortes", "guestFirstName": "Jil", "guestLastName": "Cortes", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "FR", "guestEmail": "jcorte.739502@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 2, "adults": 2, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-03-17", "departureDate": "2026-03-19", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 2, "phone": "+33773803367", "totalPrice": 94.34, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 15.47, "hostawayCommissionAmount": null, "cleaningFee": 40, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\n\nBOOKING NOTE : Payment charge is EUR 1.3207348", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 77978915, "accountId": 181258, "listingMapId": 493047, "reservationId": 56220639, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 40, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-17 11:59:12", "updatedOn": "2026-03-17 11:59:12"}, {"id": 77978916, "accountId": 181258, "listingMapId": 493047, "reservationId": 56220639, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 4.64, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-17 11:59:12", "updatedOn": "2026-03-17 11:59:12"}, {"id": 77978917, "accountId": 181258, "listingMapId": 493047, "reservationId": 56220639, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 3.34, "currency": "EUR", "percentage": 7.2, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-17 11:59:12", "updatedOn": "2026-03-17 11:59:12"}, {"id": 77978918, "a</t>
+          <t>{"id": 58442275, "listingMapId": 480137, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6103870189", "hostawayReservationId": "58442275", "channelReservationId": "6103870189", "externalPropertyId": "15950709", "externalUnitId": "1595070901", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "1cG-SOdQ", "guestPortalUrl": "https://guest-portal.hostaway.com/58442275/1cG-SOdQ", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-04-28 12:08:33", "pendingExpireDate": null, "guestName": "Ihsan Alami Messaoudi", "guestFirstName": "Ihsan", "guestLastName": "Alami Messaoudi", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "MA", "guestEmail": "imessa.543436@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 3, "adults": 1, "children": 2, "infants": null, "pets": null, "arrivalDate": "2026-05-08", "departureDate": "2026-05-12", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 4, "phone": "+212659299684", "totalPrice": 360.36, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 60.2, "hostawayCommissionAmount": null, "cleaningFee": 67, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nReservation has a cancellation grace period. Do not charge if cancelled before 2026-04-29 14:08:33\nBOOKING NOTE : Payment charge is EUR 5.22046", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": "16", "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": {"name": "Moderate", "channelId": 2005, "channelSpecificCode": "16", "longTerm": false, "cancellationPolicyItem": [{"refundAmount": 100, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": -432000, "event": "arrival"}]}, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 82687825, "accountId": 181258, "listingMapId": 480137, "reservationId": 58442275, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 67, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-28 12:09:57", "updatedOn": "2026-04-28 12:09:57"}, {"id": 82687826, "accountId": 181258, "listingMapId": 480137, "reservationId": 58442275, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 26.1, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0,</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2026-06-08T11:44:22+00:00</t>
+          <t>2026-08-17T05:25:59+00:00</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>8a4aa0765873ccf6</t>
+          <t>c4ddfc9e517834ee</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>56167448</v>
+        <v>58969166</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>{"id": 56167448, "listingMapId": 493047, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6894463465", "hostawayReservationId": "56167448", "channelReservationId": "6894463465", "externalPropertyId": "15480052", "externalUnitId": "1548005201", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "PuIcjz6c", "guestPortalUrl": "https://guest-portal.hostaway.com/56167448/PuIcjz6c", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-03-16 14:11:11", "pendingExpireDate": null, "guestName": "Enola Kilo", "guestFirstName": "Enola", "guestLastName": "Kilo", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "FR", "guestEmail": "ekilo.328159@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 2, "adults": 2, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-03-16", "departureDate": "2026-03-17", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 1, "phone": "+33782072206", "totalPrice": 67.17, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 11.13, "hostawayCommissionAmount": null, "cleaningFee": 40, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nBOOKING NOTE : Payment charge is EUR 0.9403674", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 77897488, "accountId": 181258, "listingMapId": 493047, "reservationId": 56167448, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 40, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-16 14:12:33", "updatedOn": "2026-03-16 14:12:33"}, {"id": 77897489, "accountId": 181258, "listingMapId": 493047, "reservationId": 56167448, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 2.32, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-16 14:12:34", "updatedOn": "2026-03-16 14:12:34"}, {"id": 77897490, "accountId": 181258, "listingMapId": 493047, "reservationId": 56167448, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 1.67, "currency": "EUR", "percentage": 7.2, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-16 14:12:34", "updatedOn": "2026-03-16 14:12:34"}, {"id": 77897491, "acco</t>
+          <t>{"id": 58969166, "listingMapId": 493047, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6259089014", "hostawayReservationId": "58969166", "channelReservationId": "6259089014", "externalPropertyId": "15480052", "externalUnitId": "1548005201", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "rwQAiUZR", "guestPortalUrl": "https://guest-portal.hostaway.com/58969166/rwQAiUZR", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-05-08 08:03:53", "pendingExpireDate": null, "guestName": "Wissal Ejjbari", "guestFirstName": "Wissal", "guestLastName": "Ejjbari", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "FR", "guestEmail": "wejjba.386487@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 1, "adults": 1, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-05-08", "departureDate": "2026-05-10", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 2, "phone": "+33650171208", "totalPrice": 110.64, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 18.07, "hostawayCommissionAmount": null, "cleaningFee": 40, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\n\nBOOKING NOTE : Payment charge is EUR 1.4882", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": null, "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 83525986, "accountId": 181258, "listingMapId": 493047, "reservationId": 58969166, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 40, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-05-08 08:05:17", "updatedOn": "2026-05-08 08:05:17"}, {"id": 83525987, "accountId": 181258, "listingMapId": 493047, "reservationId": 58969166, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 6.03, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-05-08 08:05:17", "updatedOn": "2026-05-08 08:05:17"}, {"id": 83525988, "accountId": 181258, "listingMapId": 493047, "reservationId": 58969166, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 4.34, "currency": "EUR", "percentage": 7.2, "isIncluded": 1, "</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026-06-08T11:44:25+00:00</t>
+          <t>2026-08-17T05:25:59+00:00</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>bbc7607ea901c768</t>
+          <t>96af8bf61bc1ed96</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>55184639</v>
+        <v>58613637</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>{"id": 55184639, "listingMapId": 480139, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6569613796", "hostawayReservationId": "55184639", "channelReservationId": "6569613796", "externalPropertyId": "15499360", "externalUnitId": "1549936001", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "fVTFodjT", "guestPortalUrl": "https://guest-portal.hostaway.com/55184639/fVTFodjT", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 1, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-02-27 21:10:39", "pendingExpireDate": null, "guestName": "Enrique Orts", "guestFirstName": "Enrique", "guestLastName": "Orts", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "ES", "guestEmail": "eorts.176965@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 2, "adults": 2, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-03-12", "departureDate": "2026-03-15", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 3, "phone": "+34667950235", "totalPrice": 287.75, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 46.49, "hostawayCommissionAmount": null, "cleaningFee": 55, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nReservation has a cancellation grace period. Do not charge if cancelled before 2026-02-28 22:10:39\nBOOKING NOTE : Payment charge is EUR 4.0284804", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "There is no meal option with this room.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 76637617, "accountId": 181258, "listingMapId": 480139, "reservationId": 55184639, "name": "Cleaning fee", "feeType": "guest", "externalReservationUnitId": null, "amount": 55, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-03 00:00:02", "updatedOn": "2026-03-03 00:00:02"}, {"id": 76637618, "accountId": 181258, "listingMapId": 480139, "reservationId": 55184639, "name": "VAT", "feeType": "guest", "externalReservationUnitId": null, "amount": 19.86, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-03 00:00:02", "updatedOn": "2026-03-03 00:00:02"}, {"id": 76637619, "accountId": 181258, "listingMapId": 480139, "reservationId": 55184639, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 14.3, "currency": "EUR", "percentage": 7.2, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn"</t>
+          <t>{"id": 58613637, "listingMapId": 480137, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6575979377", "hostawayReservationId": "58613637", "channelReservationId": "6575979377", "externalPropertyId": "15950709", "externalUnitId": "1595070901", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "RfZCVNy9", "guestPortalUrl": "https://guest-portal.hostaway.com/58613637/RfZCVNy9", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-05-01 17:29:18", "pendingExpireDate": null, "guestName": "Xavier Chaumette", "guestFirstName": "Xavier", "guestLastName": "Chaumette", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "FR", "guestEmail": "xchaum.310083@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 5, "adults": 5, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-05-04", "departureDate": "2026-05-07", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 3, "phone": "+33631914266", "totalPrice": 254.95, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 41.38, "hostawayCommissionAmount": null, "cleaningFee": 67, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nBOOKING NOTE : Payment charge is EUR 3.5693", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": "16", "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": {"name": "Moderate", "channelId": 2005, "channelSpecificCode": "16", "longTerm": false, "cancellationPolicyItem": [{"refundAmount": 100, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": -432000, "event": "arrival"}]}, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 82973714, "accountId": 181258, "listingMapId": 480137, "reservationId": 58613637, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 67, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-05-01 17:32:38", "updatedOn": "2026-05-01 17:32:38"}, {"id": 82973715, "accountId": 181258, "listingMapId": 480137, "reservationId": 58613637, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 16.04, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-05-01 17:32:38", "updatedOn": "2026-05-01 17:32:38"}, {"id": 82973716</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2026-06-08T11:44:26+00:00</t>
+          <t>2026-08-17T05:26:02+00:00</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>6f9da309a84237e3</t>
+          <t>bb9643bc60da189f</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>53502324</v>
+        <v>58515565</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>{"id": 53502324, "listingMapId": 480140, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6580611978", "hostawayReservationId": "53502324", "channelReservationId": "6580611978", "externalPropertyId": "15500360", "externalUnitId": "1550036001", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "1766LAdh", "guestPortalUrl": "https://guest-portal.hostaway.com/53502324/1766LAdh", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 1, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-01-16 00:00:00", "pendingExpireDate": null, "guestName": "Damien Terral", "guestFirstName": "Damien", "guestLastName": "Terral", "guestExternalAccountId": null, "guestZipCode": null, "guestAddress": null, "guestCity": null, "guestCountry": "FR", "guestEmail": "dterra.496348@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 7, "adults": 4, "children": 3, "infants": null, "pets": null, "arrivalDate": "2026-03-13", "departureDate": "2026-03-15", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 2, "phone": "+33689045359", "totalPrice": 237.52, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": null, "hostawayCommissionAmount": null, "cleaningFee": null, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": null, "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "There is no meal option with this room.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 76753876, "accountId": 181258, "listingMapId": 480140, "reservationId": 53502324, "name": "Cleaning fee", "feeType": "guest", "externalReservationUnitId": null, "amount": 50, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-04 09:52:44", "updatedOn": "2026-03-04 09:52:44"}, {"id": 76753877, "accountId": 181258, "listingMapId": 480140, "reservationId": 53502324, "name": "VAT", "feeType": "guest", "externalReservationUnitId": null, "amount": 16, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-04 09:52:44", "updatedOn": "2026-03-04 09:52:44"}, {"id": 76753878, "accountId": 181258, "listingMapId": 480140, "reservationId": 53502324, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 11.52, "currency": "EUR", "percentage": 7.2, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-04 09:52:44", "updatedOn": "2026-03-04 09:52:44"}, {"id": 76753879, "accountId": 181258, "listingMapId": 480140, "reservationId": 53502324, "name": "Cleaning fee", "feeTyp</t>
+          <t>{"id": 58515565, "listingMapId": 493047, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5112492307", "hostawayReservationId": "58515565", "channelReservationId": "5112492307", "externalPropertyId": "15480052", "externalUnitId": "1548005201", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "9oChM-lF", "guestPortalUrl": "https://guest-portal.hostaway.com/58515565/9oChM-lF", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-04-29 21:31:39", "pendingExpireDate": null, "guestName": "Paul Ulvoas", "guestFirstName": "Paul", "guestLastName": "Ulvoas", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "FR", "guestEmail": "pulvoa.469155@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 1, "adults": 1, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-04-30", "departureDate": "2026-05-03", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 3, "phone": "+33750034873", "totalPrice": 137.81, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 22.41, "hostawayCommissionAmount": null, "cleaningFee": 40, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "modified", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\n\nBOOKING NOTE : Payment charge is EUR 1.8452", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": null, "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 83120434, "accountId": 181258, "listingMapId": 493047, "reservationId": 58515565, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 40, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-05-03 17:08:49", "updatedOn": "2026-05-03 17:08:49"}, {"id": 83120435, "accountId": 181258, "listingMapId": 493047, "reservationId": 58515565, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 8.35, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-05-03 17:08:49", "updatedOn": "2026-05-03 17:08:49"}, {"id": 83120436, "accountId": 181258, "listingMapId": 493047, "reservationId": 58515565, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 6.01, "currency": "EUR", "percentage": 7.2, "isIncluded": 1, "i</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2026-06-08T11:44:27+00:00</t>
+          <t>2026-08-17T05:26:02+00:00</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2c8088de740d692d</t>
+          <t>9c869629de3096f1</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>55803010</v>
+        <v>53502338</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>{"id": 55803010, "listingMapId": 493047, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6079715383", "hostawayReservationId": "55803010", "channelReservationId": "6079715383", "externalPropertyId": "15480052", "externalUnitId": "1548005201", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "4xIOJbGq", "guestPortalUrl": "https://guest-portal.hostaway.com/55803010/4xIOJbGq", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-03-10 01:09:36", "pendingExpireDate": null, "guestName": "OLUWATOBI OYEDELE OYEBIYI", "guestFirstName": "OLUWATOBI", "guestLastName": "OYEDELE OYEBIYI", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": "", "guestCountry": "NG", "guestEmail": "ooyebi.690989@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 1, "adults": 1, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-07-04", "departureDate": "2026-07-12", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 8, "phone": "+234907987309", "totalPrice": 337.05, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 54.2, "hostawayCommissionAmount": null, "cleaningFee": 40, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\n\nBOOKING NOTE : Payment charge is EUR 4.7186818", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 77244630, "accountId": 181258, "listingMapId": 493047, "reservationId": 55803010, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 40, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-10 01:10:56", "updatedOn": "2026-03-10 01:10:56"}, {"id": 77244631, "accountId": 181258, "listingMapId": 493047, "reservationId": 55803010, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 25.35, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-10 01:10:56", "updatedOn": "2026-03-10 01:10:56"}, {"id": 77244632, "accountId": 181258, "listingMapId": 493047, "reservationId": 55803010, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 18.25, "currency": "EUR", "percentage": 7.2, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-10 01:10:56", "updatedOn": "2026-03-10</t>
+          <t>{"id": 53502338, "listingMapId": 480139, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5383925091", "hostawayReservationId": "53502338", "channelReservationId": "5383925091", "externalPropertyId": "15499360", "externalUnitId": "1549936001", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "nMR3Iuvx", "guestPortalUrl": "https://guest-portal.hostaway.com/53502338/nMR3Iuvx", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 1, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2025-12-28 00:00:00", "pendingExpireDate": null, "guestName": "Núria Aquilué Junyent", "guestFirstName": "Núria", "guestLastName": "Aquilué Junyent", "guestExternalAccountId": null, "guestZipCode": null, "guestAddress": null, "guestCity": null, "guestCountry": null, "guestEmail": null, "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 5, "adults": 3, "children": 2, "infants": null, "pets": null, "arrivalDate": "2026-04-30", "departureDate": "2026-05-03", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 3, "phone": null, "totalPrice": 300, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": null, "hostawayCommissionAmount": null, "cleaningFee": null, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "modified", "paymentStatus": "Unknown", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": null, "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "There is no meal option with this room.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": "16", "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": {"name": "Moderate", "channelId": 2005, "channelSpecificCode": "16", "longTerm": false, "cancellationPolicyItem": [{"refundAmount": 100, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": -432000, "event": "arrival"}]}, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [], "reservationUnit": [], "insertedOn": "2026-01-31 13:04:29", "updatedOn": "2026-05-03 08:54:04", "latestActivityOn": "2026-05-03 08:54:03", "customerUserId": null, "guestLocale": null, "localeForMessaging": null, "localeForMessagingSource": null, "listingCustomFields": null, "rentalAgreementFileUrl": null, "reservationAgreement": "not_required", "financeField": [{"id": 218021622, "units": 1, "listingFeeSettingId": null, "type": "accommodation", "name": "baseRate", "title": "Base rate", "alias": null, "quantity": null, "value": 300, "isIncludedInTotalPrice": 1, "isOverriddenByUser": 0, "isMandatory": 1, "isQuantitySelectable": 0, "isDeleted": 0, "total": 300}, {"id": 218021623, "units": 1, "listingFeeSettingId": null, "type": "totals", "name": "totalPriceFromChannel", "title": "Total price from channel", "alias": null, "quantity": null, "value": 30</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2026-06-08T11:44:28+00:00</t>
+          <t>2026-08-17T05:26:03+00:00</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>dc32ab03e3907d4f</t>
+          <t>4493011ea6242a6e</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>55728634</v>
+        <v>53743611</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>{"id": 55728634, "listingMapId": 480139, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5970804562", "hostawayReservationId": "55728634", "channelReservationId": "5970804562", "externalPropertyId": "15499360", "externalUnitId": "1549936001", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "c2cgtFLt", "guestPortalUrl": "https://guest-portal.hostaway.com/55728634/c2cgtFLt", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-03-08 19:04:14", "pendingExpireDate": null, "guestName": "Patricia Berasaluce", "guestFirstName": "Patricia", "guestLastName": "Berasaluce", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "ES", "guestEmail": "pberas.876254@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 4, "adults": 4, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-07-06", "departureDate": "2026-07-11", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 5, "phone": "+34637762925", "totalPrice": 560.35, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 89.98, "hostawayCommissionAmount": null, "cleaningFee": 55, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\n\nBOOKING NOTE : Payment charge is EUR 7.8448314", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "There is no meal option with this room.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 77123741, "accountId": 181258, "listingMapId": 480139, "reservationId": 55728634, "name": "Cleaning fee", "feeType": "guest", "externalReservationUnitId": null, "amount": 55, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-08 19:05:42", "updatedOn": "2026-03-08 19:05:42"}, {"id": 77123742, "accountId": 181258, "listingMapId": 480139, "reservationId": 55728634, "name": "VAT", "feeType": "guest", "externalReservationUnitId": null, "amount": 43.12, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-08 19:05:42", "updatedOn": "2026-03-08 19:05:42"}, {"id": 77123743, "accountId": 181258, "listingMapId": 480139, "reservationId": 55728634, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 31.05, "currency": "EUR", "percentage": 7.2, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-08 19:05:42", "updatedOn": "2026-03-08 19:05:42"}, {"id": 77123744, "ac</t>
+          <t>{"id": 53743611, "listingMapId": 480140, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6990197423", "hostawayReservationId": "53743611", "channelReservationId": "6990197423", "externalPropertyId": "15500360", "externalUnitId": "1550036001", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "pJJXykUt", "guestPortalUrl": "https://guest-portal.hostaway.com/53743611/pJJXykUt", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 1, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-02-04 09:27:07", "pendingExpireDate": null, "guestName": "Samantha Simon", "guestFirstName": "Samantha", "guestLastName": "Simon", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": "", "guestCountry": "BE", "guestEmail": "ssimon.966720@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 6, "adults": 2, "children": 4, "infants": null, "pets": null, "arrivalDate": "2026-04-28", "departureDate": "2026-05-03", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 5, "phone": "+32470079549", "totalPrice": 598.5, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 96.02, "hostawayCommissionAmount": null, "cleaningFee": 50, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "modified", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nApproximate time of arrival: between 19:00 and 20:00\nBOOKING NOTE : Payment charge is EUR 8.378944", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "There is no meal option with this room.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": "16", "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": {"name": "Moderate", "channelId": 2005, "channelSpecificCode": "16", "longTerm": false, "cancellationPolicyItem": [{"refundAmount": 100, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": -432000, "event": "arrival"}]}, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 82954360, "accountId": 181258, "listingMapId": 480140, "reservationId": 53743611, "name": "Cleaning fee", "feeType": "guest", "externalReservationUnitId": null, "amount": 50, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-05-01 13:00:34", "updatedOn": "2026-05-01 13:00:34"}, {"id": 82954361, "accountId": 181258, "listingMapId": 480140, "reservationId": 53743611, "name": "VAT", "feeType": "guest", "externalReservationUnitId": null, "amount": 46.8, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-05-01 13:00:34", "updatedOn": "2026-05-0</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026-06-08T11:44:29+00:00</t>
+          <t>2026-08-17T05:26:04+00:00</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>c08c73d0a3d04a05</t>
+          <t>28c80d99278146f3</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>55377376</v>
+        <v>56885582</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>{"id": 55377376, "listingMapId": 493047, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6990148941", "hostawayReservationId": "55377376", "channelReservationId": "6990148941", "externalPropertyId": "15480052", "externalUnitId": "1548005201", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "WdRgMaOK", "guestPortalUrl": "https://guest-portal.hostaway.com/55377376/WdRgMaOK", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 1, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-02-04 15:35:13", "pendingExpireDate": null, "guestName": "Juliane DELEBARRE", "guestFirstName": "Juliane", "guestLastName": "DELEBARRE", "guestExternalAccountId": null, "guestZipCode": null, "guestAddress": null, "guestCity": null, "guestCountry": null, "guestEmail": null, "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 1, "adults": 1, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-03-05", "departureDate": "2026-03-08", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 3, "phone": null, "totalPrice": 129.6, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": null, "hostawayCommissionAmount": null, "cleaningFee": null, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Unknown", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": null, "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [], "reservationUnit": [], "insertedOn": "2026-03-02 23:46:49", "updatedOn": "2026-03-09 15:31:21", "latestActivityOn": "2026-03-09 15:31:21", "customerUserId": null, "guestLocale": null, "localeForMessaging": null, "localeForMessagingSource": null, "listingCustomFields": null, "rentalAgreementFileUrl": null, "reservationAgreement": "not_required", "financeField": [{"id": 226915584, "units": 1, "listingFeeSettingId": null, "type": "accommodation", "name": "baseRate", "title": "Base rate", "alias": null, "quantity": null, "value": 129.6, "isIncludedInTotalPrice": 1, "isOverriddenByUser": 0, "isMandatory": 1, "isQuantitySelectable": 0, "isDeleted": 0, "total": 129.6}, {"id": 226915585, "units": 1, "listingFeeSettingId": null, "type": "totals", "name": "totalPriceFromChannel", "title": "Total price from channel", "alias": null, "quantity": null, "value": 129.6, "isIncludedInTotalPrice": 0, "isOverriddenByUser": 0, "isMandatory": 0, "isQuantitySelectable": 0, "isDeleted": 0, "total": 129.6}], "guestPaymentCardIsVirtual": null, "insuranceStatus": "not_eligible", "claimStatus": null, "insurancePolicyId": null, "insuranceCoverageStart": null, "insuranceCoverageEnd": null, "cancellationPolicyId": null, "cancell</t>
+          <t>{"id": 56885582, "listingMapId": 485104, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5176698850", "hostawayReservationId": "56885582", "channelReservationId": "5176698850", "externalPropertyId": "16046812", "externalUnitId": "1604681201", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "QKQe3kgN", "guestPortalUrl": "https://guest-portal.hostaway.com/56885582/QKQe3kgN", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-03-28 20:35:48", "pendingExpireDate": null, "guestName": "Valerie Blier", "guestFirstName": "Valerie", "guestLastName": "Blier", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "FR", "guestEmail": "vblier.632926@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 4, "adults": 3, "children": 1, "infants": null, "pets": null, "arrivalDate": "2026-04-20", "departureDate": "2026-04-24", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 4, "phone": "+33616916975", "totalPrice": 244.54, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 39.63, "hostawayCommissionAmount": null, "cleaningFee": null, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nBOOKING NOTE : Payment charge is EUR 3.4236034", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": "16", "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": {"name": "Moderate", "channelId": 2005, "channelSpecificCode": "16", "longTerm": false, "cancellationPolicyItem": [{"refundAmount": 100, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": -432000, "event": "arrival"}]}, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 78997386, "accountId": 181258, "listingMapId": 485104, "reservationId": 56885582, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 21.19, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-28 20:37:10", "updatedOn": "2026-03-28 20:37:10"}, {"id": 78997387, "accountId": 181258, "listingMapId": 485104, "reservationId": 56885582, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 11.44, "currency": "EUR", "percentage": 7.2, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-28 20:37:10", "updatedOn": "2026-03-28 20:37:10"}, {"id": 78</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026-06-08T11:44:29+00:00</t>
+          <t>2026-08-17T05:26:05+00:00</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2b700b9fcd9b0911</t>
+          <t>ee326159b2c59afe</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>55377364</v>
+        <v>56765333</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>{"id": 55377364, "listingMapId": 493047, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5666901021", "hostawayReservationId": "55377364", "channelReservationId": "5666901021", "externalPropertyId": "15480052", "externalUnitId": "1548005201", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "GTX2dUOH", "guestPortalUrl": "https://guest-portal.hostaway.com/55377364/GTX2dUOH", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 1, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-02-12 13:47:57", "pendingExpireDate": null, "guestName": "Luciana Cengarle", "guestFirstName": "Luciana", "guestLastName": "Cengarle", "guestExternalAccountId": null, "guestZipCode": null, "guestAddress": null, "guestCity": null, "guestCountry": "FR", "guestEmail": "lcenga.152631@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 2, "adults": 2, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-02-27", "departureDate": "2026-03-05", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 6, "phone": "+33775795260", "totalPrice": 168.88, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": null, "hostawayCommissionAmount": null, "cleaningFee": null, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": null, "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 76637494, "accountId": 181258, "listingMapId": 493047, "reservationId": 55377364, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 40, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-02 23:58:27", "updatedOn": "2026-03-02 23:58:27"}, {"id": 76637495, "accountId": 181258, "listingMapId": 493047, "reservationId": 55377364, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 11, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-02 23:58:27", "updatedOn": "2026-03-02 23:58:27"}, {"id": 76637496, "accountId": 181258, "listingMapId": 493047, "reservationId": 55377364, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 7.92, "currency": "EUR", "percentage": 7.2, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-02 23:58:27", "updatedOn": "2026-03-02 23:58:27"}, {"id": 76637497, "accountId": 181258, "listingMapId": 493047, "reservationId": 55377364, "</t>
+          <t>{"id": 56765333, "listingMapId": 485104, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6174292312", "hostawayReservationId": "56765333", "channelReservationId": "6174292312", "externalPropertyId": "16046812", "externalUnitId": "1604681201", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "ym9d9YSi", "guestPortalUrl": "https://guest-portal.hostaway.com/56765333/ym9d9YSi", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-03-26 19:05:27", "pendingExpireDate": null, "guestName": "Amjhadi Youssef", "guestFirstName": "Amjhadi", "guestLastName": "Youssef", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": "", "guestCountry": "FR", "guestEmail": "ayouss.162491@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 2, "adults": 2, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-03-27", "departureDate": "2026-03-29", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 2, "phone": "+33651159183", "totalPrice": 62.9, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 10.04, "hostawayCommissionAmount": null, "cleaningFee": null, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "modified", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nApproximate time of arrival: between 16:00 and 17:00\nBOOKING NOTE : Payment charge is EUR 0.8806616", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": "16", "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": {"name": "Moderate", "channelId": 2005, "channelSpecificCode": "16", "longTerm": false, "cancellationPolicyItem": [{"refundAmount": 100, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": -432000, "event": "arrival"}]}, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 79325736, "accountId": 181258, "listingMapId": 485104, "reservationId": 56765333, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 5.37, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-01 12:32:26", "updatedOn": "2026-04-01 12:32:26"}, {"id": 79325737, "accountId": 181258, "listingMapId": 485104, "reservationId": 56765333, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 3.86, "currency": "EUR", "percentage": 7.19, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-0</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2026-06-08T11:44:31+00:00</t>
+          <t>2026-08-17T05:26:06+00:00</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>40e187a3fa933dd2</t>
+          <t>4ea38c4a23310e3f</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>55148902</v>
+        <v>57242598</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>{"id": 55148902, "listingMapId": 480139, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6549001488", "hostawayReservationId": "55148902", "channelReservationId": "6549001488", "externalPropertyId": "15499360", "externalUnitId": "1549936001", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "CxwUYvyR", "guestPortalUrl": "https://guest-portal.hostaway.com/55148902/CxwUYvyR", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 1, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-02-27 06:42:37", "pendingExpireDate": null, "guestName": "Maria Beltran", "guestFirstName": "Maria", "guestLastName": "Beltran", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "ES", "guestEmail": "mbeltr.191851@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 5, "adults": 4, "children": 1, "infants": null, "pets": null, "arrivalDate": "2026-12-31", "departureDate": "2027-01-03", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 3, "phone": "+34650371805", "totalPrice": 411.71, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 66.27, "hostawayCommissionAmount": null, "cleaningFee": 55, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nBOOKING NOTE : Payment charge is EUR 5.7639988", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "There is no meal option with this room.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 76637599, "accountId": 181258, "listingMapId": 480139, "reservationId": 55148902, "name": "Cleaning fee", "feeType": "guest", "externalReservationUnitId": null, "amount": 55, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-03 00:00:02", "updatedOn": "2026-03-03 00:00:02"}, {"id": 76637600, "accountId": 181258, "listingMapId": 480139, "reservationId": 55148902, "name": "VAT", "feeType": "guest", "externalReservationUnitId": null, "amount": 30.44, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-03 00:00:02", "updatedOn": "2026-03-03 00:00:02"}, {"id": 76637601, "accountId": 181258, "listingMapId": 480139, "reservationId": 55148902, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 21.91, "currency": "EUR", "percentage": 7.2, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-03 00:00:02", "updatedOn": "2026-03-03 00:00:02"}, {"id": 76637603, "accountId": 181258,</t>
+          <t>{"id": 57242598, "listingMapId": 480139, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6614587583", "hostawayReservationId": "57242598", "channelReservationId": "6614587583", "externalPropertyId": "15499360", "externalUnitId": "1549936001", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "kTQGEiLf", "guestPortalUrl": "https://guest-portal.hostaway.com/57242598/kTQGEiLf", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-04-03 19:11:37", "pendingExpireDate": null, "guestName": "INES MARIA NOGALES FLORES", "guestFirstName": "INES", "guestLastName": "MARIA NOGALES FLORES", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": "", "guestCountry": "ES", "guestEmail": "iflore.270703@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 4, "adults": 2, "children": 2, "infants": null, "pets": null, "arrivalDate": "2026-04-23", "departureDate": "2026-04-28", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 5, "phone": "+34652486712", "totalPrice": 477.82, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 79.02, "hostawayCommissionAmount": null, "cleaningFee": 67, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nBOOKING NOTE : Payment charge is EUR 6.6894646", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "There is no meal option with this room.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": "16", "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": {"name": "Moderate", "channelId": 2005, "channelSpecificCode": "16", "longTerm": false, "cancellationPolicyItem": [{"refundAmount": 100, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": -432000, "event": "arrival"}]}, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 79560356, "accountId": 181258, "listingMapId": 480139, "reservationId": 57242598, "name": "Cleaning fee", "feeType": "guest", "externalReservationUnitId": null, "amount": 67, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-03 19:12:58", "updatedOn": "2026-04-03 19:12:58"}, {"id": 79560357, "accountId": 181258, "listingMapId": 480139, "reservationId": 57242598, "name": "VAT", "feeType": "guest", "externalReservationUnitId": null, "amount": 36.16, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-03 19:12:58", "updatedOn": "2026-04-03 19:12:58"}, {"id": 79560358, "ac</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2026-06-08T11:44:31+00:00</t>
+          <t>2026-08-17T05:26:08+00:00</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>f71319ac3e165dca</t>
+          <t>6db223f213995422</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>55377370</v>
+        <v>58269316</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>{"id": 55377370, "listingMapId": 493047, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6425195360", "hostawayReservationId": "55377370", "channelReservationId": "6425195360", "externalPropertyId": "15480052", "externalUnitId": "1548005201", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "bPNo7xlT", "guestPortalUrl": "https://guest-portal.hostaway.com/55377370/bPNo7xlT", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 1, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-02-08 18:38:01", "pendingExpireDate": null, "guestName": "Margaux Klawitter", "guestFirstName": "Margaux", "guestLastName": "Klawitter", "guestExternalAccountId": null, "guestZipCode": null, "guestAddress": null, "guestCity": ".", "guestCountry": "FR", "guestEmail": "mklawi.527718@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 2, "adults": 2, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-08-26", "departureDate": "2026-08-30", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 4, "phone": "+33762261107", "totalPrice": 157.37, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": null, "hostawayCommissionAmount": null, "cleaningFee": null, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": null, "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 76637524, "accountId": 181258, "listingMapId": 493047, "reservationId": 55377370, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 40, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-02 23:58:28", "updatedOn": "2026-03-02 23:58:28"}, {"id": 76637525, "accountId": 181258, "listingMapId": 493047, "reservationId": 55377370, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 10.01, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-02 23:58:28", "updatedOn": "2026-03-02 23:58:28"}, {"id": 76637526, "accountId": 181258, "listingMapId": 493047, "reservationId": 55377370, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 7.21, "currency": "EUR", "percentage": 7.2, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-02 23:58:28", "updatedOn": "2026-03-02 23:58:28"}, {"id": 76637527, "accountId": 181258, "listingMapId": 493047, "reservationId": 5537737</t>
+          <t>{"id": 58269316, "listingMapId": 493047, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6942565816", "hostawayReservationId": "58269316", "channelReservationId": "6942565816", "externalPropertyId": "15480052", "externalUnitId": "1548005201", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "6DpKf0Bj", "guestPortalUrl": "https://guest-portal.hostaway.com/58269316/6DpKf0Bj", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-04-24 12:15:48", "pendingExpireDate": null, "guestName": "Antoine Kaikilekofe", "guestFirstName": "Antoine", "guestLastName": "Kaikilekofe", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "FR", "guestEmail": "akaiki.295425@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 2, "adults": 2, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-04-24", "departureDate": "2026-04-26", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 2, "phone": "+33662201326", "totalPrice": 110.64, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 18.07, "hostawayCommissionAmount": null, "cleaningFee": 40, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nBOOKING NOTE : Payment charge is EUR 1.4882", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": null, "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 82355613, "accountId": 181258, "listingMapId": 493047, "reservationId": 58269316, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 40, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-24 12:17:12", "updatedOn": "2026-04-24 12:17:12"}, {"id": 82355614, "accountId": 181258, "listingMapId": 493047, "reservationId": 58269316, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 6.03, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-24 12:17:12", "updatedOn": "2026-04-24 12:17:12"}, {"id": 82355615, "accountId": 181258, "listingMapId": 493047, "reservationId": 58269316, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 4.34, "currency": "EUR", "percentage": 7.2, "isInclude</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2026-06-08T11:44:32+00:00</t>
+          <t>2026-08-17T05:26:09+00:00</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>f7b09780255219cc</t>
+          <t>84f431e0575b9c67</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
+        <v>57301034</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>{"id": 57301034, "listingMapId": 493047, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6460756517", "hostawayReservationId": "57301034", "channelReservationId": "6460756517", "externalPropertyId": "15480052", "externalUnitId": "1548005201", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "ditoz8G4", "guestPortalUrl": "https://guest-portal.hostaway.com/57301034/ditoz8G4", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-04-05 11:51:14", "pendingExpireDate": null, "guestName": "Lamnaddaf Rania", "guestFirstName": "Lamnaddaf", "guestLastName": "Rania", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": "", "guestCountry": "FR", "guestEmail": "lrania.690109@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 2, "adults": 1, "children": 1, "infants": null, "pets": null, "arrivalDate": "2026-04-19", "departureDate": "2026-04-24", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 5, "phone": "+33754879782", "totalPrice": 212.05, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 35.12, "hostawayCommissionAmount": null, "cleaningFee": 40, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nBOOKING NOTE : Payment charge is EUR 2.9687336\nApproximate time of arrival: between 16:00 and 17:00", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": null, "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 79744013, "accountId": 181258, "listingMapId": 493047, "reservationId": 57301034, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 40, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-05 11:52:38", "updatedOn": "2026-04-05 11:52:38"}, {"id": 79744014, "accountId": 181258, "listingMapId": 493047, "reservationId": 57301034, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 15.15, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-05 11:52:38", "updatedOn": "2026-04-05 11:52:38"}, {"id": 79744015, "accountId": 181258, "listingMapId": 493047, "reservationId": 57301034, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 5.45, "c</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>2026-08-17T05:26:10+00:00</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>20b589c45bd0aa08</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>56163020</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>{"id": 56163020, "listingMapId": 493047, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5177336485", "hostawayReservationId": "56163020", "channelReservationId": "5177336485", "externalPropertyId": "15480052", "externalUnitId": "1548005201", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "g19FJnTa", "guestPortalUrl": "https://guest-portal.hostaway.com/56163020/g19FJnTa", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-03-16 12:23:41", "pendingExpireDate": null, "guestName": "Nelly Tuffreau", "guestFirstName": "Nelly", "guestLastName": "Tuffreau", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "FR", "guestEmail": "ntuffr.226196@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 2, "adults": 2, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-04-16", "departureDate": "2026-04-19", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 3, "phone": "+33698479128", "totalPrice": 145.05, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 23.56, "hostawayCommissionAmount": null, "cleaningFee": 40, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\n\nBOOKING NOTE : Payment charge is EUR 2.0307532", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": null, "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 77888422, "accountId": 181258, "listingMapId": 493047, "reservationId": 56163020, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 40, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-16 12:25:03", "updatedOn": "2026-03-16 12:25:03"}, {"id": 77888423, "accountId": 181258, "listingMapId": 493047, "reservationId": 56163020, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 8.96, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-16 12:25:03", "updatedOn": "2026-03-16 12:25:03"}, {"id": 77888424, "accountId": 181258, "listingMapId": 493047, "reservationId": 56163020, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 6.45, "currency": "EUR", "percentage": 7.2, "isIncluded": 1</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>2026-08-17T05:26:11+00:00</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>07db7b06ecbcbd8e</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>56052100</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>{"id": 56052100, "listingMapId": 480139, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5385306861", "hostawayReservationId": "56052100", "channelReservationId": "5385306861", "externalPropertyId": "15499360", "externalUnitId": "1549936001", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "Xmn9RdqR", "guestPortalUrl": "https://guest-portal.hostaway.com/56052100/Xmn9RdqR", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-03-14 12:16:27", "pendingExpireDate": null, "guestName": "Gillian Douglass", "guestFirstName": "Gillian", "guestLastName": "Douglass", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "GB", "guestEmail": "gdougl.477450@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 2, "adults": 2, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-04-11", "departureDate": "2026-04-14", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 3, "phone": "+447878620366", "totalPrice": 361.85, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 58.31, "hostawayCommissionAmount": null, "cleaningFee": 55, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\n\nBOOKING NOTE : Payment charge is EUR 5.0659126", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "There is no meal option with this room.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": "16", "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": {"name": "Moderate", "channelId": 2005, "channelSpecificCode": "16", "longTerm": false, "cancellationPolicyItem": [{"refundAmount": 100, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": -432000, "event": "arrival"}]}, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 77716640, "accountId": 181258, "listingMapId": 480139, "reservationId": 56052100, "name": "Cleaning fee", "feeType": "guest", "externalReservationUnitId": null, "amount": 55, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-14 12:33:45", "updatedOn": "2026-03-14 12:33:45"}, {"id": 77716641, "accountId": 181258, "listingMapId": 480139, "reservationId": 56052100, "name": "VAT", "feeType": "guest", "externalReservationUnitId": null, "amount": 26.18, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-14 12:33:45", "updatedOn": "2026-03-14 12:33:45"}, {"id": 77716642, "accountId": 1</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>2026-08-17T05:26:13+00:00</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>8560ed14c2f934dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>56916115</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>{"id": 56916115, "listingMapId": 480137, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6962385915", "hostawayReservationId": "56916115", "channelReservationId": "6962385915", "externalPropertyId": "15950709", "externalUnitId": "1595070901", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "SAYBl6Pk", "guestPortalUrl": "https://guest-portal.hostaway.com/56916115/SAYBl6Pk", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-03-29 13:37:24", "pendingExpireDate": null, "guestName": "Patrick BOURGON", "guestFirstName": "Patrick", "guestLastName": "BOURGON", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": "", "guestCountry": "FR", "guestEmail": "pbourg.657327@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 2, "adults": 2, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-04-10", "departureDate": "2026-04-13", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 3, "phone": "+33681453845", "totalPrice": 216.33, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 34.52, "hostawayCommissionAmount": null, "cleaningFee": null, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nReservation has a cancellation grace period. Do not charge if cancelled before 2026-03-30 15:37:24\nBOOKING NOTE : Payment charge is EUR 3.0286186\nApproximate time of arrival: between 16:00 and 17:00", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": "16", "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": {"name": "Moderate", "channelId": 2005, "channelSpecificCode": "16", "longTerm": false, "cancellationPolicyItem": [{"refundAmount": 100, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": -432000, "event": "arrival"}]}, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 79045657, "accountId": 181258, "listingMapId": 480137, "reservationId": 56916115, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 18.46, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-29 13:39:00", "updatedOn": "2026-03-29 13:39:00"}, {"id": 79045658, "accountId": 181258, "listingMapId": 480137, "reservationId": 56916115, "name": "taxe de séjour", "feeType": "guest", "externalReservationUnitId": null, "amount": 13.29, "currency": "EUR", "percentage": 7.2, "</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>2026-08-17T05:26:14+00:00</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>95e1e6530d6c1fe9</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>57280196</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>{"id": 57280196, "listingMapId": 493047, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5221473980", "hostawayReservationId": "57280196", "channelReservationId": "5221473980", "externalPropertyId": "15480052", "externalUnitId": "1548005201", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "GdhXR44d", "guestPortalUrl": "https://guest-portal.hostaway.com/57280196/GdhXR44d", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-04-04 19:51:07", "pendingExpireDate": null, "guestName": "Andrea MANIVONG", "guestFirstName": "Andrea", "guestLastName": "MANIVONG", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": "", "guestCountry": "FR", "guestEmail": "amaniv.555116@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 2, "adults": 2, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-04-06", "departureDate": "2026-04-12", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 6, "phone": "+33760437425", "totalPrice": 251.92, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 40.61, "hostawayCommissionAmount": null, "cleaningFee": 40, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\n\nBOOKING NOTE : Payment charge is EUR 3.5268646", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": null, "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 79666912, "accountId": 181258, "listingMapId": 493047, "reservationId": 57280196, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 40, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-04 19:52:24", "updatedOn": "2026-04-04 19:52:24"}, {"id": 79666913, "accountId": 181258, "listingMapId": 493047, "reservationId": 57280196, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 18.08, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-04 19:52:24", "updatedOn": "2026-04-04 19:52:24"}, {"id": 79666914, "accountId": 181258, "listingMapId": 493047, "reservationId": 57280196, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 13.02, "currency": "EUR", "percentage": 7.2, "isIncluded"</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>2026-08-17T05:26:15+00:00</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>5c0c797cc559f1fb</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>57088437</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>{"id": 57088437, "listingMapId": 480137, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5931665862", "hostawayReservationId": "57088437", "channelReservationId": "5931665862", "externalPropertyId": "15950709", "externalUnitId": "1595070901", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "PY_HxToc", "guestPortalUrl": "https://guest-portal.hostaway.com/57088437/PY_HxToc", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-03-31 15:55:34", "pendingExpireDate": null, "guestName": "SOULIE ANTHONY GUILLAUME CHOQUEREAU", "guestFirstName": "SOULIE", "guestLastName": "ANTHONY GUILLAUME CHOQUEREAU", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "FR", "guestEmail": "santho.342426@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 2, "adults": 2, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-04-07", "departureDate": "2026-04-09", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 2, "phone": "+33612571421", "totalPrice": 140, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 22.34, "hostawayCommissionAmount": null, "cleaningFee": null, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\n\nBOOKING NOTE : Payment charge is EUR 1.9600098", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": "16", "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": {"name": "Moderate", "channelId": 2005, "channelSpecificCode": "16", "longTerm": false, "cancellationPolicyItem": [{"refundAmount": 100, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": -432000, "event": "arrival"}]}, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 79247757, "accountId": 181258, "listingMapId": 480137, "reservationId": 57088437, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 11.95, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-31 15:56:59", "updatedOn": "2026-03-31 15:56:59"}, {"id": 79247758, "accountId": 181258, "listingMapId": 480137, "reservationId": 57088437, "name": "taxe de séjour", "feeType": "guest", "externalReservationUnitId": null, "amount": 8.6, "currency": "EUR", "percentage": 7.2, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-31 15:56:59", "updatedOn"</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>2026-08-17T05:26:15+00:00</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>18045de1450a7091</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>55669313</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>{"id": 55669313, "listingMapId": 480139, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6598251257", "hostawayReservationId": "55669313", "channelReservationId": "6598251257", "externalPropertyId": "15499360", "externalUnitId": "1549936001", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "SOo-lIN9", "guestPortalUrl": "https://guest-portal.hostaway.com/55669313/SOo-lIN9", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-03-07 16:49:25", "pendingExpireDate": null, "guestName": "Andoni Iztueta Villar", "guestFirstName": "Andoni", "guestLastName": "Iztueta Villar", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "ES", "guestEmail": "avilla.130389@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 5, "adults": 2, "children": 3, "infants": null, "pets": null, "arrivalDate": "2026-04-06", "departureDate": "2026-04-08", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 2, "phone": "+34615786412", "totalPrice": 259.25, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 41.94, "hostawayCommissionAmount": null, "cleaningFee": 55, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nBOOKING NOTE : Payment charge is EUR 3.6294664", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "There is no meal option with this room.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": "16", "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": {"name": "Moderate", "channelId": 2005, "channelSpecificCode": "16", "longTerm": false, "cancellationPolicyItem": [{"refundAmount": 100, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": -432000, "event": "arrival"}]}, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 77029925, "accountId": 181258, "listingMapId": 480139, "reservationId": 55669313, "name": "Cleaning fee", "feeType": "guest", "externalReservationUnitId": null, "amount": 55, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-07 16:50:56", "updatedOn": "2026-03-07 16:50:56"}, {"id": 77029926, "accountId": 181258, "listingMapId": 480139, "reservationId": 55669313, "name": "VAT", "feeType": "guest", "externalReservationUnitId": null, "amount": 17.43, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-07 16:50:56", "updatedOn": "2026-03-07 16:50:56"}, {"id": 77029927, "accountId</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>2026-08-17T05:26:16+00:00</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>970f702e31c16900</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>57142306</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>{"id": 57142306, "listingMapId": 493047, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5996054807", "hostawayReservationId": "57142306", "channelReservationId": "5996054807", "externalPropertyId": "15480052", "externalUnitId": "1548005201", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "DO-n9jMt", "guestPortalUrl": "https://guest-portal.hostaway.com/57142306/DO-n9jMt", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-04-01 16:27:11", "pendingExpireDate": null, "guestName": "leidy jhoana caicedo victoria", "guestFirstName": "leidy", "guestLastName": "jhoana caicedo victoria", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "ES", "guestEmail": "lvicto.549055@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 2, "adults": 2, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-04-03", "departureDate": "2026-04-05", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 2, "phone": "+34602505317", "totalPrice": 110.64, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 18.07, "hostawayCommissionAmount": null, "cleaningFee": 40, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\n\nBOOKING NOTE : Payment charge is EUR 1.5489544", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": null, "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 79343263, "accountId": 181258, "listingMapId": 493047, "reservationId": 57142306, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 40, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-01 16:28:35", "updatedOn": "2026-04-01 16:28:35"}, {"id": 79343265, "accountId": 181258, "listingMapId": 493047, "reservationId": 57142306, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 6.03, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-01 16:28:35", "updatedOn": "2026-04-01 16:28:35"}, {"id": 79343267, "accountId": 181258, "listingMapId": 493047, "reservationId": 57142306, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 4.34, "currency": "EUR", "per</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>2026-08-17T05:26:17+00:00</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>e85d2ed5076ceb5a</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>56842443</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>{"id": 56842443, "listingMapId": 480140, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5476072668", "hostawayReservationId": "56842443", "channelReservationId": "5476072668", "externalPropertyId": "15500360", "externalUnitId": "1550036001", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "TJfXfbsj", "guestPortalUrl": "https://guest-portal.hostaway.com/56842443/TJfXfbsj", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-03-28 03:09:35", "pendingExpireDate": null, "guestName": "Fernandez Alvaro", "guestFirstName": "Fernandez", "guestLastName": "Alvaro", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "ES", "guestEmail": "falvar.726911@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 5, "adults": 5, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-04-01", "departureDate": "2026-04-03", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 2, "phone": "+34658185121", "totalPrice": 183.88, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 29.91, "hostawayCommissionAmount": null, "cleaningFee": 55, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nReservation has a cancellation grace period. Do not charge if cancelled before 2026-03-29 05:09:35\n\nBOOKING NOTE : Payment charge is EUR 2.5742836", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "There is no meal option with this room.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": "16", "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": {"name": "Moderate", "channelId": 2005, "channelSpecificCode": "16", "longTerm": false, "cancellationPolicyItem": [{"refundAmount": 100, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": -432000, "event": "arrival"}]}, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 78938752, "accountId": 181258, "listingMapId": 480140, "reservationId": 56842443, "name": "Cleaning fee", "feeType": "guest", "externalReservationUnitId": null, "amount": 55, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-28 03:10:52", "updatedOn": "2026-03-28 03:10:52"}, {"id": 78938753, "accountId": 181258, "listingMapId": 480140, "reservationId": 56842443, "name": "VAT", "feeType": "guest", "externalReservationUnitId": null, "amount": 11, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "inserted</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>2026-08-17T05:26:18+00:00</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>0fa40846dc1a0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>56713083</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>{"id": 56713083, "listingMapId": 480139, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6695268135", "hostawayReservationId": "56713083", "channelReservationId": "6695268135", "externalPropertyId": "15499360", "externalUnitId": "1549936001", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "Qx0bqLw3", "guestPortalUrl": "https://guest-portal.hostaway.com/56713083/Qx0bqLw3", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-03-25 22:28:45", "pendingExpireDate": null, "guestName": "Isabel Munoz Benitez", "guestFirstName": "Isabel", "guestLastName": "Munoz Benitez", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "ES", "guestEmail": "ibenit.649681@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 4, "adults": 4, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-04-01", "departureDate": "2026-04-03", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 2, "phone": "+34635252822", "totalPrice": 173.14, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 28.2, "hostawayCommissionAmount": null, "cleaningFee": 55, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nReservation has a cancellation grace period. Do not charge if cancelled before 2026-03-26 23:28:45\nBOOKING NOTE : Payment charge is EUR 2.4239264", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "There is no meal option with this room.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": "16", "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": {"name": "Moderate", "channelId": 2005, "channelSpecificCode": "16", "longTerm": false, "cancellationPolicyItem": [{"refundAmount": 100, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": -432000, "event": "arrival"}]}, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 78759795, "accountId": 181258, "listingMapId": 480139, "reservationId": 56713083, "name": "Cleaning fee", "feeType": "guest", "externalReservationUnitId": null, "amount": 55, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-25 22:30:49", "updatedOn": "2026-03-25 22:30:49"}, {"id": 78759796, "accountId": 181258, "listingMapId": 480139, "reservationId": 56713083, "name": "VAT", "feeType": "guest", "externalReservationUnitId": null, "amount": 10.08, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>2026-08-17T05:26:19+00:00</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>4ceffd91079419d6</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>56587223</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>{"id": 56587223, "listingMapId": 493047, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6592305464", "hostawayReservationId": "56587223", "channelReservationId": "6592305464", "externalPropertyId": "15480052", "externalUnitId": "1548005201", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "pR0GJV2C", "guestPortalUrl": "https://guest-portal.hostaway.com/56587223/pR0GJV2C", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-03-23 22:25:05", "pendingExpireDate": null, "guestName": "Miah Nayeem", "guestFirstName": "Miah", "guestLastName": "Nayeem", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "FR", "guestEmail": "mnayee.310819@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 2, "adults": 2, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-03-29", "departureDate": "2026-04-03", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 5, "phone": "+33753789108", "totalPrice": 219.32, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 35.41, "hostawayCommissionAmount": null, "cleaningFee": 40, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nBOOKING NOTE : Payment charge is EUR 3.070424", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": null, "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 78562315, "accountId": 181258, "listingMapId": 493047, "reservationId": 56587223, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 40, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-23 22:26:26", "updatedOn": "2026-03-23 22:26:26"}, {"id": 78562316, "accountId": 181258, "listingMapId": 493047, "reservationId": 56587223, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 15.3, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-23 22:26:26", "updatedOn": "2026-03-23 22:26:26"}, {"id": 78562317, "accountId": 181258, "listingMapId": 493047, "reservationId": 56587223, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 11.02, "currency": "EUR", "percentage": 7.2, "isIncluded": 1, "isPer</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>2026-08-17T05:26:19+00:00</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>c70e654a200f018e</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>56814094</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>{"id": 56814094, "listingMapId": 480137, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5765483815", "hostawayReservationId": "56814094", "channelReservationId": "5765483815", "externalPropertyId": "15950709", "externalUnitId": "1595070901", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "eQ1I9oVf", "guestPortalUrl": "https://guest-portal.hostaway.com/56814094/eQ1I9oVf", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-03-27 16:54:48", "pendingExpireDate": null, "guestName": "Samuel Jolbit", "guestFirstName": "Samuel", "guestLastName": "Jolbit", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "FR", "guestEmail": "sjolbi.717567@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 2, "adults": 2, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-03-27", "departureDate": "2026-03-29", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 2, "phone": "+33628762338", "totalPrice": 113.53, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 18.12, "hostawayCommissionAmount": null, "cleaningFee": null, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "modified", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\n\nBOOKING NOTE : Payment charge is EUR 1.5894872", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": "16", "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": {"name": "Moderate", "channelId": 2005, "channelSpecificCode": "16", "longTerm": false, "cancellationPolicyItem": [{"refundAmount": 100, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": -432000, "event": "arrival"}]}, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 79326041, "accountId": 181258, "listingMapId": 480137, "reservationId": 56814094, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 9.69, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-01 12:33:54", "updatedOn": "2026-04-01 12:33:54"}, {"id": 79326042, "accountId": 181258, "listingMapId": 480137, "reservationId": 56814094, "name": "taxe de séjour", "feeType": "guest", "externalReservationUnitId": null, "amount": 6.97, "currency": "EUR", "percentage": 7.2, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-04-01 12:33:54", "updatedOn": "2026-04-01 12:33:54"}, {"id": 793</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>2026-08-17T05:26:20+00:00</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>7050a1cba42fead3</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>56124039</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>{"id": 56124039, "listingMapId": 480140, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5971651562", "hostawayReservationId": "56124039", "channelReservationId": "5971651562", "externalPropertyId": "15500360", "externalUnitId": "1550036001", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "a-yRbAUU", "guestPortalUrl": "https://guest-portal.hostaway.com/56124039/a-yRbAUU", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-03-15 19:04:53", "pendingExpireDate": null, "guestName": "Andrey Sosnikhin", "guestFirstName": "Andrey", "guestLastName": "Sosnikhin", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": "", "guestCountry": "GB", "guestEmail": "asosni.233988@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 4, "adults": 2, "children": 2, "infants": null, "pets": null, "arrivalDate": "2026-03-30", "departureDate": "2026-04-01", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 2, "phone": "+447586557087", "totalPrice": 213.89, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 35.5, "hostawayCommissionAmount": null, "cleaningFee": 55, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nReservation has a cancellation grace period. Do not charge if cancelled before 2026-03-16 20:04:53\nBOOKING NOTE : Payment charge is EUR 2.9943914", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "There is no meal option with this room.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": "16", "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": {"name": "Moderate", "channelId": 2005, "channelSpecificCode": "16", "longTerm": false, "cancellationPolicyItem": [{"refundAmount": 100, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": -432000, "event": "arrival"}]}, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 77830125, "accountId": 181258, "listingMapId": 480140, "reservationId": 56124039, "name": "Cleaning fee", "feeType": "guest", "externalReservationUnitId": null, "amount": 55, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-15 19:06:16", "updatedOn": "2026-03-15 19:06:16"}, {"id": 77830126, "accountId": 181258, "listingMapId": 480140, "reservationId": 56124039, "name": "VAT", "feeType": "guest", "externalReservationUnitId": null, "amount": 13.99, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn"</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>2026-08-17T05:26:21+00:00</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>074242815e619cca</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>54376756</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>{"id": 54376756, "listingMapId": 480139, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6672470205", "hostawayReservationId": "54376756", "channelReservationId": "6672470205", "externalPropertyId": "15499360", "externalUnitId": "1549936001", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "gP_MTj43", "guestPortalUrl": "https://guest-portal.hostaway.com/54376756/gP_MTj43", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 1, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-02-14 22:00:57", "pendingExpireDate": null, "guestName": "Olga Correia", "guestFirstName": "Olga", "guestLastName": "Correia", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "PT", "guestEmail": "ocorre.915879@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 5, "adults": 5, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-03-29", "departureDate": "2026-03-31", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 2, "phone": "+351919764669", "totalPrice": 223.45, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 36.23, "hostawayCommissionAmount": null, "cleaningFee": 55, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nReservation has a cancellation grace period. Do not charge if cancelled before 2026-02-15 23:00:57\n\nBOOKING NOTE : Payment charge is EUR 3.1282776", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "There is no meal option with this room.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": "16", "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": {"name": "Moderate", "channelId": 2005, "channelSpecificCode": "16", "longTerm": false, "cancellationPolicyItem": [{"refundAmount": 100, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": -432000, "event": "arrival"}]}, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 76637602, "accountId": 181258, "listingMapId": 480139, "reservationId": 54376756, "name": "Cleaning fee", "feeType": "guest", "externalReservationUnitId": null, "amount": 55, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-03 00:00:02", "updatedOn": "2026-03-03 00:00:02"}, {"id": 76637604, "accountId": 181258, "listingMapId": 480139, "reservationId": 54376756, "name": "VAT", "feeType": "guest", "externalReservationUnitId": null, "amount": 14.37, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn":</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>2026-08-17T05:26:22+00:00</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>9add502b652ffebe</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>56576707</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>{"id": 56576707, "listingMapId": 493047, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6158482386", "hostawayReservationId": "56576707", "channelReservationId": "6158482386", "externalPropertyId": "15480052", "externalUnitId": "1548005201", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "pghrgw8R", "guestPortalUrl": "https://guest-portal.hostaway.com/56576707/pghrgw8R", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-03-23 19:10:46", "pendingExpireDate": null, "guestName": "chenyi Wang", "guestFirstName": "chenyi", "guestLastName": "Wang", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "FR", "guestEmail": "czvflw.450356@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 1, "adults": 1, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-03-27", "departureDate": "2026-03-29", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 2, "phone": "+33782125837", "totalPrice": 101.58, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 16.63, "hostawayCommissionAmount": null, "cleaningFee": 40, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nBOOKING NOTE : Payment charge is EUR 1.4221662", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": null, "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 78543573, "accountId": 181258, "listingMapId": 493047, "reservationId": 56576707, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 40, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-23 19:12:15", "updatedOn": "2026-03-23 19:12:15"}, {"id": 78543574, "accountId": 181258, "listingMapId": 493047, "reservationId": 56576707, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 5.25, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-23 19:12:15", "updatedOn": "2026-03-23 19:12:15"}, {"id": 78543575, "accountId": 181258, "listingMapId": 493047, "reservationId": 56576707, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 3.78, "currency": "EUR", "percentage": 7.19, "isIncluded": 1, "isPe</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>2026-08-17T05:26:23+00:00</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>6ae58fe359df858f</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>56908103</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>{"id": 56908103, "listingMapId": 480140, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6378353908", "hostawayReservationId": "56908103", "channelReservationId": "6378353908", "externalPropertyId": "15500360", "externalUnitId": "1550036001", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "05lcaLo7", "guestPortalUrl": "https://guest-portal.hostaway.com/56908103/05lcaLo7", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-03-29 09:18:31", "pendingExpireDate": null, "guestName": "Patrick COLIN", "guestFirstName": "Patrick", "guestLastName": "COLIN", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": "", "guestCountry": "FR", "guestEmail": "pcolin.401170@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 5, "adults": 5, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-09-18", "departureDate": "2026-09-20", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 2, "phone": "+33616371171", "totalPrice": 276.88, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 44.75, "hostawayCommissionAmount": null, "cleaningFee": 55, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\n\nBOOKING NOTE : Payment charge is EUR 3.8763326", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "There is no meal option with this room.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": "16", "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": {"name": "Moderate", "channelId": 2005, "channelSpecificCode": "16", "longTerm": false, "cancellationPolicyItem": [{"refundAmount": 100, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": -432000, "event": "arrival"}]}, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 79026391, "accountId": 181258, "listingMapId": 480140, "reservationId": 56908103, "name": "Cleaning fee", "feeType": "guest", "externalReservationUnitId": null, "amount": 55, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-29 09:19:53", "updatedOn": "2026-03-29 09:19:53"}, {"id": 79026392, "accountId": 181258, "listingMapId": 480140, "reservationId": 56908103, "name": "VAT", "feeType": "guest", "externalReservationUnitId": null, "amount": 18.93, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-29 09:19:53", "updatedOn": "2026-03-29 09:19:53"}, {"id": 79026393, "accountId": 181258, "</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>2026-08-17T05:26:25+00:00</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>2d6e773c49b6ea7a</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>55918531</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>{"id": 55918531, "listingMapId": 493047, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6034886110", "hostawayReservationId": "55918531", "channelReservationId": "6034886110", "externalPropertyId": "15480052", "externalUnitId": "1548005201", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "S14uha1x", "guestPortalUrl": "https://guest-portal.hostaway.com/55918531/S14uha1x", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-03-12 00:58:03", "pendingExpireDate": null, "guestName": "Manal Hammoun", "guestFirstName": "Manal", "guestLastName": "Hammoun", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "MA", "guestEmail": "mhammo.966493@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 1, "adults": 1, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-03-22", "departureDate": "2026-03-26", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 4, "phone": "+212663703339", "totalPrice": 163.17, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 26.45, "hostawayCommissionAmount": null, "cleaningFee": 40, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\n\nBOOKING NOTE : Payment charge is EUR 2.2843324", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": null, "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 77526915, "accountId": 181258, "listingMapId": 493047, "reservationId": 55918531, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 40, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-12 00:59:22", "updatedOn": "2026-03-12 00:59:22"}, {"id": 77526916, "accountId": 181258, "listingMapId": 493047, "reservationId": 55918531, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 10.51, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-12 00:59:22", "updatedOn": "2026-03-12 00:59:22"}, {"id": 77526917, "accountId": 181258, "listingMapId": 493047, "reservationId": 55918531, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 7.57, "currency": "EUR", "percentage": 7.2, "isIncluded": 1</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>2026-08-17T05:26:26+00:00</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>6fbf90f66e405181</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>55377369</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>{"id": 55377369, "listingMapId": 493047, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5899222328", "hostawayReservationId": "55377369", "channelReservationId": "5899222328", "externalPropertyId": "15480052", "externalUnitId": "1548005201", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "h_H8fRtS", "guestPortalUrl": "https://guest-portal.hostaway.com/55377369/h_H8fRtS", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 1, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-02-14 18:10:02", "pendingExpireDate": null, "guestName": "Beatriz Gómez Ortiz", "guestFirstName": "Beatriz", "guestLastName": "Gómez Ortiz", "guestExternalAccountId": null, "guestZipCode": null, "guestAddress": null, "guestCity": ".", "guestCountry": "ES", "guestEmail": "bortiz.362186@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 2, "adults": 2, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-03-20", "departureDate": "2026-03-22", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 2, "phone": "+34608241102", "totalPrice": 92.16, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": null, "hostawayCommissionAmount": null, "cleaningFee": null, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": null, "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": null, "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 76637512, "accountId": 181258, "listingMapId": 493047, "reservationId": 55377369, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 40, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-02 23:58:27", "updatedOn": "2026-03-02 23:58:27"}, {"id": 76637513, "accountId": 181258, "listingMapId": 493047, "reservationId": 55377369, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 4.45, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-02 23:58:27", "updatedOn": "2026-03-02 23:58:27"}, {"id": 76637514, "accountId": 181258, "listingMapId": 493047, "reservationId": 55377369, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 3.2, "currency": "EUR", "percentage": 7.19, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>2026-08-17T05:26:26+00:00</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>7eb71dcfd51c5074</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>55293664</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>{"id": 55293664, "listingMapId": 480140, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6777615695", "hostawayReservationId": "55293664", "channelReservationId": "6777615695", "externalPropertyId": "15500360", "externalUnitId": "1550036001", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "wZg-ea_v", "guestPortalUrl": "https://guest-portal.hostaway.com/55293664/wZg-ea_v", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 1, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-03-01 17:32:06", "pendingExpireDate": null, "guestName": "Cindy Dupont", "guestFirstName": "Cindy", "guestLastName": "Dupont", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "FR", "guestEmail": "cdupon.197857@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 4, "adults": 4, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-03-17", "departureDate": "2026-03-20", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 3, "phone": "+33645566738", "totalPrice": 301.44, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 48.67, "hostawayCommissionAmount": null, "cleaningFee": 55, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nReservation has a cancellation grace period. Do not charge if cancelled before 2026-03-02 18:32:06\nBOOKING NOTE : Payment charge is EUR 4.2201544", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "There is no meal option with this room.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": "16", "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": {"name": "Moderate", "channelId": 2005, "channelSpecificCode": "16", "longTerm": false, "cancellationPolicyItem": [{"refundAmount": 100, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": -432000, "event": "arrival"}]}, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 76753882, "accountId": 181258, "listingMapId": 480140, "reservationId": 55293664, "name": "Cleaning fee", "feeType": "guest", "externalReservationUnitId": null, "amount": 55, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-04 09:52:44", "updatedOn": "2026-03-04 09:52:44"}, {"id": 76753883, "accountId": 181258, "listingMapId": 480140, "reservationId": 55293664, "name": "VAT", "feeType": "guest", "externalReservationUnitId": null, "amount": 21.03, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>2026-08-17T05:26:27+00:00</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>c317f0687e0fd4c5</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>55556631</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>{"id": 55556631, "listingMapId": 493047, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6706469653", "hostawayReservationId": "55556631", "channelReservationId": "6706469653", "externalPropertyId": "15480052", "externalUnitId": "1548005201", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "aibDuLHl", "guestPortalUrl": "https://guest-portal.hostaway.com/55556631/aibDuLHl", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-03-05 17:32:45", "pendingExpireDate": null, "guestName": "Barbas Valeria", "guestFirstName": "Barbas", "guestLastName": "Valeria", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": "", "guestCountry": "FR", "guestEmail": "bvaler.881655@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 2, "adults": 2, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-03-11", "departureDate": "2026-03-16", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 5, "phone": "+33641540805", "totalPrice": 193.96, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 31.36, "hostawayCommissionAmount": null, "cleaningFee": 40, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nBOOKING NOTE : Payment charge is EUR 2.7154148\nApproximate time of arrival: between 11:00 and 12:00", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": null, "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 76874263, "accountId": 181258, "listingMapId": 493047, "reservationId": 55556631, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 40, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-05 17:34:01", "updatedOn": "2026-03-05 17:34:01"}, {"id": 76874264, "accountId": 181258, "listingMapId": 493047, "reservationId": 55556631, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 13.14, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-05 17:34:01", "updatedOn": "2026-03-05 17:34:01"}, {"id": 76874265, "accountId": 181258, "listingMapId": 493047, "reservationId": 55556631, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 9.46, "</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>2026-08-17T05:26:28+00:00</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>fd28285f72fb1ba4</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>56220639</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>{"id": 56220639, "listingMapId": 493047, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5373020142", "hostawayReservationId": "56220639", "channelReservationId": "5373020142", "externalPropertyId": "15480052", "externalUnitId": "1548005201", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "9DvvkJYB", "guestPortalUrl": "https://guest-portal.hostaway.com/56220639/9DvvkJYB", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-03-17 11:57:49", "pendingExpireDate": null, "guestName": "Jil Cortes", "guestFirstName": "Jil", "guestLastName": "Cortes", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "FR", "guestEmail": "jcorte.739502@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 2, "adults": 2, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-03-17", "departureDate": "2026-03-19", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 2, "phone": "+33773803367", "totalPrice": 94.34, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 15.47, "hostawayCommissionAmount": null, "cleaningFee": 40, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\n\nBOOKING NOTE : Payment charge is EUR 1.3207348", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": null, "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 77978915, "accountId": 181258, "listingMapId": 493047, "reservationId": 56220639, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 40, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-17 11:59:12", "updatedOn": "2026-03-17 11:59:12"}, {"id": 77978916, "accountId": 181258, "listingMapId": 493047, "reservationId": 56220639, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 4.64, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-17 11:59:12", "updatedOn": "2026-03-17 11:59:12"}, {"id": 77978917, "accountId": 181258, "listingMapId": 493047, "reservationId": 56220639, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 3.34, "currency": "EUR", "percentage": 7.2, "isIncluded": 1, "isPerN</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>2026-08-17T05:26:29+00:00</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>8a4aa0765873ccf6</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>56167448</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>{"id": 56167448, "listingMapId": 493047, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6894463465", "hostawayReservationId": "56167448", "channelReservationId": "6894463465", "externalPropertyId": "15480052", "externalUnitId": "1548005201", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "PuIcjz6c", "guestPortalUrl": "https://guest-portal.hostaway.com/56167448/PuIcjz6c", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-03-16 14:11:11", "pendingExpireDate": null, "guestName": "Enola Kilo", "guestFirstName": "Enola", "guestLastName": "Kilo", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "FR", "guestEmail": "ekilo.328159@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 2, "adults": 2, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-03-16", "departureDate": "2026-03-17", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 1, "phone": "+33782072206", "totalPrice": 67.17, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 11.13, "hostawayCommissionAmount": null, "cleaningFee": 40, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nBOOKING NOTE : Payment charge is EUR 0.9403674", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": null, "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 77897488, "accountId": 181258, "listingMapId": 493047, "reservationId": 56167448, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 40, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-16 14:12:33", "updatedOn": "2026-03-16 14:12:33"}, {"id": 77897489, "accountId": 181258, "listingMapId": 493047, "reservationId": 56167448, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 2.32, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-16 14:12:34", "updatedOn": "2026-03-16 14:12:34"}, {"id": 77897490, "accountId": 181258, "listingMapId": 493047, "reservationId": 56167448, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 1.67, "currency": "EUR", "percentage": 7.2, "isIncluded": 1, "isPerNigh</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>2026-08-17T05:26:30+00:00</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>bbc7607ea901c768</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>55184639</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>{"id": 55184639, "listingMapId": 480139, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6569613796", "hostawayReservationId": "55184639", "channelReservationId": "6569613796", "externalPropertyId": "15499360", "externalUnitId": "1549936001", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "fVTFodjT", "guestPortalUrl": "https://guest-portal.hostaway.com/55184639/fVTFodjT", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 1, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-02-27 21:10:39", "pendingExpireDate": null, "guestName": "Enrique Orts", "guestFirstName": "Enrique", "guestLastName": "Orts", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "ES", "guestEmail": "eorts.176965@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 2, "adults": 2, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-03-12", "departureDate": "2026-03-15", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 3, "phone": "+34667950235", "totalPrice": 287.75, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 46.49, "hostawayCommissionAmount": null, "cleaningFee": 55, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nReservation has a cancellation grace period. Do not charge if cancelled before 2026-02-28 22:10:39\nBOOKING NOTE : Payment charge is EUR 4.0284804", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "There is no meal option with this room.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": "16", "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": {"name": "Moderate", "channelId": 2005, "channelSpecificCode": "16", "longTerm": false, "cancellationPolicyItem": [{"refundAmount": 100, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": -432000, "event": "arrival"}]}, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 76637617, "accountId": 181258, "listingMapId": 480139, "reservationId": 55184639, "name": "Cleaning fee", "feeType": "guest", "externalReservationUnitId": null, "amount": 55, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-03 00:00:02", "updatedOn": "2026-03-03 00:00:02"}, {"id": 76637618, "accountId": 181258, "listingMapId": 480139, "reservationId": 55184639, "name": "VAT", "feeType": "guest", "externalReservationUnitId": null, "amount": 19.86, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "20</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>2026-08-17T05:26:30+00:00</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>6f9da309a84237e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>53502324</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>{"id": 53502324, "listingMapId": 480140, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6580611978", "hostawayReservationId": "53502324", "channelReservationId": "6580611978", "externalPropertyId": "15500360", "externalUnitId": "1550036001", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "1766LAdh", "guestPortalUrl": "https://guest-portal.hostaway.com/53502324/1766LAdh", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 1, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-01-16 00:00:00", "pendingExpireDate": null, "guestName": "Damien Terral", "guestFirstName": "Damien", "guestLastName": "Terral", "guestExternalAccountId": null, "guestZipCode": null, "guestAddress": null, "guestCity": null, "guestCountry": "FR", "guestEmail": "dterra.496348@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 7, "adults": 4, "children": 3, "infants": null, "pets": null, "arrivalDate": "2026-03-13", "departureDate": "2026-03-15", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 2, "phone": "+33689045359", "totalPrice": 237.52, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": null, "hostawayCommissionAmount": null, "cleaningFee": null, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": null, "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "There is no meal option with this room.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": "16", "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": {"name": "Moderate", "channelId": 2005, "channelSpecificCode": "16", "longTerm": false, "cancellationPolicyItem": [{"refundAmount": 100, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": -432000, "event": "arrival"}]}, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 76753876, "accountId": 181258, "listingMapId": 480140, "reservationId": 53502324, "name": "Cleaning fee", "feeType": "guest", "externalReservationUnitId": null, "amount": 50, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-04 09:52:44", "updatedOn": "2026-03-04 09:52:44"}, {"id": 76753877, "accountId": 181258, "listingMapId": 480140, "reservationId": 53502324, "name": "VAT", "feeType": "guest", "externalReservationUnitId": null, "amount": 16, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-04 09:52:44", "updatedOn": "2026-03-04 09:52:44"}, {"id": 76753878, "accountId": 181258, "listingMapId": 480140, "reservationId": 53502324, "name": "CITY_TAX (Withheld Tax)", "f</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>2026-08-17T05:26:31+00:00</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>2c8088de740d692d</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>55377376</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>{"id": 55377376, "listingMapId": 493047, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6990148941", "hostawayReservationId": "55377376", "channelReservationId": "6990148941", "externalPropertyId": "15480052", "externalUnitId": "1548005201", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "WdRgMaOK", "guestPortalUrl": "https://guest-portal.hostaway.com/55377376/WdRgMaOK", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 1, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-02-04 15:35:13", "pendingExpireDate": null, "guestName": "Juliane DELEBARRE", "guestFirstName": "Juliane", "guestLastName": "DELEBARRE", "guestExternalAccountId": null, "guestZipCode": null, "guestAddress": null, "guestCity": null, "guestCountry": null, "guestEmail": null, "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 1, "adults": 1, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-03-05", "departureDate": "2026-03-08", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 3, "phone": null, "totalPrice": 129.6, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": null, "hostawayCommissionAmount": null, "cleaningFee": null, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Unknown", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": null, "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": null, "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [], "reservationUnit": [], "insertedOn": "2026-03-02 23:46:49", "updatedOn": "2026-03-09 15:31:21", "latestActivityOn": "2026-03-09 15:31:21", "customerUserId": null, "guestLocale": null, "localeForMessaging": null, "localeForMessagingSource": null, "listingCustomFields": null, "rentalAgreementFileUrl": null, "reservationAgreement": "not_required", "financeField": [{"id": 226915584, "units": 1, "listingFeeSettingId": null, "type": "accommodation", "name": "baseRate", "title": "Base rate", "alias": null, "quantity": null, "value": 129.6, "isIncludedInTotalPrice": 1, "isOverriddenByUser": 0, "isMandatory": 1, "isQuantitySelectable": 0, "isDeleted": 0, "total": 129.6}, {"id": 226915585, "units": 1, "listingFeeSettingId": null, "type": "totals", "name": "totalPriceFromChannel", "title": "Total price from channel", "alias": null, "quantity": null, "value": 129.6, "isIncludedInTotalPrice": 0, "isOverriddenByUser": 0, "isMandatory": 0, "isQuantitySelectable": 0, "isDeleted": 0, "total": 129.6}], "guestPaymentCardIsVirtual": null, "insuranceStatus": "not_eligible", "claimStat</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>2026-08-17T05:26:32+00:00</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>2b700b9fcd9b0911</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>55377364</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{"id": 55377364, "listingMapId": 493047, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "5666901021", "hostawayReservationId": "55377364", "channelReservationId": "5666901021", "externalPropertyId": "15480052", "externalUnitId": "1548005201", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "GTX2dUOH", "guestPortalUrl": "https://guest-portal.hostaway.com/55377364/GTX2dUOH", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 1, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-02-12 13:47:57", "pendingExpireDate": null, "guestName": "Luciana Cengarle", "guestFirstName": "Luciana", "guestLastName": "Cengarle", "guestExternalAccountId": null, "guestZipCode": null, "guestAddress": null, "guestCity": null, "guestCountry": "FR", "guestEmail": "lcenga.152631@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 2, "adults": 2, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-02-27", "departureDate": "2026-03-05", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 6, "phone": "+33775795260", "totalPrice": 168.88, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": null, "hostawayCommissionAmount": null, "cleaningFee": null, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": null, "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": null, "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 76637494, "accountId": 181258, "listingMapId": 493047, "reservationId": 55377364, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 40, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-02 23:58:27", "updatedOn": "2026-03-02 23:58:27"}, {"id": 76637495, "accountId": 181258, "listingMapId": 493047, "reservationId": 55377364, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 11, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-02 23:58:27", "updatedOn": "2026-03-02 23:58:27"}, {"id": 76637496, "accountId": 181258, "listingMapId": 493047, "reservationId": 55377364, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 7.92, "currency": "EUR", "percentage": 7.2, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-02 </t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>2026-08-17T05:26:34+00:00</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>40e187a3fa933dd2</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>55377370</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>{"id": 55377370, "listingMapId": 493047, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6425195360", "hostawayReservationId": "55377370", "channelReservationId": "6425195360", "externalPropertyId": "15480052", "externalUnitId": "1548005201", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "bPNo7xlT", "guestPortalUrl": "https://guest-portal.hostaway.com/55377370/bPNo7xlT", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 1, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-02-08 18:38:01", "pendingExpireDate": null, "guestName": "Margaux Klawitter", "guestFirstName": "Margaux", "guestLastName": "Klawitter", "guestExternalAccountId": null, "guestZipCode": null, "guestAddress": null, "guestCity": ".", "guestCountry": "FR", "guestEmail": "mklawi.527718@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 2, "adults": 2, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-08-26", "departureDate": "2026-08-30", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 4, "phone": "+33762261107", "totalPrice": 157.37, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": null, "hostawayCommissionAmount": null, "cleaningFee": null, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": null, "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "Les repas ne sont pas compris dans le tarif de la chambre.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": null, "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 76637524, "accountId": 181258, "listingMapId": 493047, "reservationId": 55377370, "name": "frais de ménage", "feeType": "guest", "externalReservationUnitId": null, "amount": 40, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-02 23:58:28", "updatedOn": "2026-03-02 23:58:28"}, {"id": 76637525, "accountId": 181258, "listingMapId": 493047, "reservationId": 55377370, "name": "TVA", "feeType": "guest", "externalReservationUnitId": null, "amount": 10.01, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03-02 23:58:28", "updatedOn": "2026-03-02 23:58:28"}, {"id": 76637526, "accountId": 181258, "listingMapId": 493047, "reservationId": 55377370, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 7.21, "currency": "EUR", "percentage": 7.2, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-03</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>2026-08-17T05:26:35+00:00</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>f7b09780255219cc</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
         <v>53624302</v>
       </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>{"id": 53624302, "listingMapId": 480139, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6246994404", "hostawayReservationId": "53624302", "channelReservationId": "6246994404", "externalPropertyId": "15499360", "externalUnitId": "1549936001", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "6zSnskqi", "guestPortalUrl": "https://guest-portal.hostaway.com/53624302/6zSnskqi", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-02-02 15:06:50", "pendingExpireDate": null, "guestName": "Hasan Ozdemir", "guestFirstName": "Hasan", "guestLastName": "Ozdemir", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "FR", "guestEmail": "hozdem.379690@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 3, "adults": 3, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-02-02", "departureDate": "2026-02-04", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 2, "phone": "+33766528351", "totalPrice": 168.64, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 27.43, "hostawayCommissionAmount": null, "cleaningFee": 50, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nBOOKING NOTE : Payment charge is EUR 2.3609376", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "There is no meal option with this room.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 73626268, "accountId": 181258, "listingMapId": 480139, "reservationId": 53624302, "name": "Cleaning fee", "feeType": "guest", "externalReservationUnitId": null, "amount": 50, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-02-02 15:08:14", "updatedOn": "2026-02-02 15:08:14"}, {"id": 73626269, "accountId": 181258, "listingMapId": 480139, "reservationId": 53624302, "name": "VAT", "feeType": "guest", "externalReservationUnitId": null, "amount": 10.12, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-02-02 15:08:14", "updatedOn": "2026-02-02 15:08:14"}, {"id": 73626270, "accountId": 181258, "listingMapId": 480139, "reservationId": 53624302, "name": "CITY_TAX (Withheld Tax)", "feeType": "guest", "externalReservationUnitId": null, "amount": 7.29, "currency": "EUR", "percentage": 7.2, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-02-02 15:08:14", "updatedOn": "2026-02-02 15:08:14"}, {"id": 73626271, "accountId": 18125</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>2026-06-08T11:44:33+00:00</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>{"id": 53624302, "listingMapId": 480139, "listingName": "", "channelId": 2005, "source": null, "channelName": "bookingcom", "reservationId": "6246994404", "hostawayReservationId": "53624302", "channelReservationId": "6246994404", "externalPropertyId": "15499360", "externalUnitId": "1549936001", "assigneeUserId": null, "customerIcalId": null, "customerIcalName": null, "guestAuthHash": "6zSnskqi", "guestPortalUrl": "https://guest-portal.hostaway.com/53624302/6zSnskqi", "guestPortalRevampUrl": null, "isProcessed": 1, "isInitial": 0, "isManuallyChecked": 0, "isInstantBooked": 0, "reservationDate": "2026-02-02 15:06:50", "pendingExpireDate": null, "guestName": "Hasan Ozdemir", "guestFirstName": "Hasan", "guestLastName": "Ozdemir", "guestExternalAccountId": null, "guestZipCode": "", "guestAddress": "", "guestCity": ".", "guestCountry": "FR", "guestEmail": "hozdem.379690@guest.booking.com", "guestPicture": null, "guestRecommendations": 0, "guestTrips": 0, "guestWork": null, "isGuestIdentityVerified": 0, "isGuestVerifiedByEmail": 0, "isGuestVerifiedByWorkEmail": 0, "isGuestVerifiedByFacebook": 0, "originalChannel": null, "isGuestVerifiedByGovernmentId": 0, "isGuestVerifiedByPhone": 0, "isGuestVerifiedByReviews": 0, "numberOfGuests": 3, "adults": 3, "children": null, "infants": null, "pets": null, "arrivalDate": "2026-02-02", "departureDate": "2026-02-04", "isDatesUnspecified": 0, "previousArrivalDate": null, "previousDepartureDate": null, "checkInTime": 16, "checkOutTime": 11, "nights": 2, "phone": "+33766528351", "totalPrice": 168.64, "remainingBalance": null, "taxAmount": null, "channelCommissionAmount": 27.43, "hostawayCommissionAmount": null, "cleaningFee": 50, "securityDepositFee": null, "isPaid": null, "ccName": null, "ccNumber": null, "ccNumberEndingDigits": null, "ccExpirationYear": null, "ccExpirationMonth": null, "cvc": null, "stripeGuestId": null, "stripeMessage": null, "braintreeGuestId": null, "braintreeMessage": null, "currency": "EUR", "status": "new", "paymentStatus": "Paid", "cancellationDate": null, "cancelledBy": null, "hostNote": null, "guestNote": "** THIS RESERVATION HAS BEEN PRE-PAID **\nBOOKING NOTE : Payment charge is EUR 2.3609376", "doorCode": null, "doorCodeVendor": null, "doorCodeInstruction": null, "comment": "There is no meal option with this room.", "confirmationCode": null, "airbnbExpectedPayoutAmount": null, "airbnbListingBasePrice": null, "airbnbListingCancellationHostFee": null, "airbnbListingCancellationPayout": null, "airbnbListingCleaningFee": null, "airbnbListingHostFee": null, "airbnbListingSecurityPrice": null, "airbnbOccupancyTaxAmountPaidToHost": null, "airbnbTotalPaidAmount": null, "airbnbTransientOccupancyTaxPaidAmount": null, "airbnbCancellationPolicy": null, "bookingCancellationPolicy": "16", "vrboCancellationPolicy": null, "marriottCancellationPolicy": null, "cancellationPolicyDetails": {"name": "Moderate", "channelId": 2005, "channelSpecificCode": "16", "longTerm": false, "cancellationPolicyItem": [{"refundAmount": 100, "refundType": "percentage", "refundField": "totalPrice", "timeDelta": -432000, "event": "arrival"}]}, "isStarred": 0, "isArchived": 0, "isPinned": 0, "reservationCouponId": null, "customFieldValues": [], "reservationFees": [{"id": 73626268, "accountId": 181258, "listingMapId": 480139, "reservationId": 53624302, "name": "Cleaning fee", "feeType": "guest", "externalReservationUnitId": null, "amount": 50, "currency": "EUR", "percentage": null, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-02-02 15:08:14", "updatedOn": "2026-02-02 15:08:14"}, {"id": 73626269, "accountId": 181258, "listingMapId": 480139, "reservationId": 53624302, "name": "VAT", "feeType": "guest", "externalReservationUnitId": null, "amount": 10.12, "currency": "EUR", "percentage": 10, "isIncluded": 1, "isPerNight": 0, "isPerPerson": 0, "isImported": 1, "insertedOn": "2026-02-02 15:08:14", "updatedOn": "2026-02-02 15:08:14"}, {"id": 73626270, "accountId": 181258, "l</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>2026-08-17T05:26:36+00:00</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
         <is>
           <t>817148d8196f8fcd</t>
         </is>
